--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-675.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.8%</t>
+          <t>434.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.7%</t>
+          <t>-658.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-270.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>103.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-260.5%</t>
+          <t>-259.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-289.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-164.7%</t>
+          <t>-146.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.8%</t>
+          <t>-217.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.1%</t>
+          <t>-173.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-135.3%</t>
+          <t>-126.8%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.7497961784502833</v>
+        <v>0.9184028726189427</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.439479989341976</v>
+        <v>3.50692266700944</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.631764624679707</v>
+        <v>1.800371318848367</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.118976717083434</v>
+        <v>4.22014073358463</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.5532457673970779</v>
+        <v>0.7218524615657371</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.359117660783038</v>
+        <v>3.426560338450502</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.668418790368211</v>
+        <v>1.83702548453687</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.139227052358882</v>
+        <v>4.240391068860077</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.3997263829116132</v>
+        <v>0.5683330770802725</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.2775351796163</v>
+        <v>3.344977857283763</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.705385264837735</v>
+        <v>1.873991959006394</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.141232209668043</v>
+        <v>4.242396226169238</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.3863265137573039</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.27266437068045</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.705385264837735</v>
+        <v>1.873991959006394</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.141721348393917</v>
+        <v>4.242885364895113</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.3381042469102203</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.257455446563283</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.657162997990651</v>
+        <v>1.825769692159311</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.116867970907334</v>
+        <v>4.218031987408529</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>0.1009727550604252</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.197543934320907</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.657162997990651</v>
+        <v>1.825769692159311</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.151809055404875</v>
+        <v>4.252973071906071</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>0.1060103457880118</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.19813641079728</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.712807454256969</v>
+        <v>1.881414148425628</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.183773169350004</v>
+        <v>4.2849371858512</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3197903830887042</v>
+        <v>-0.151183688920045</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.006562500870331</v>
+        <v>3.074005178537794</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.455613419548912</v>
+        <v>1.624220113717571</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.008203130148907</v>
+        <v>4.109367146650102</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3855577731381163</v>
+        <v>-0.216951078969457</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.981273153981036</v>
+        <v>3.048715831648499</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.455613419548912</v>
+        <v>1.624220113717571</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.009220739279377</v>
+        <v>4.110384755780572</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5908024501953608</v>
+        <v>-0.4221957560267016</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.889803315145894</v>
+        <v>2.957245992813357</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.455613419548912</v>
+        <v>1.624220113717571</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.999848771267133</v>
+        <v>4.101012787768328</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6725743506231125</v>
+        <v>-0.5039676564544533</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.847177280930031</v>
+        <v>2.914619958597495</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.482648992955049</v>
+        <v>1.651255687123708</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.006152841266053</v>
+        <v>4.107316857767248</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7397834584949903</v>
+        <v>-0.571176764326331</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.825058954614982</v>
+        <v>2.892501632282446</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.482648992955049</v>
+        <v>1.651255687123708</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.010918158099756</v>
+        <v>4.112082174600951</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9473492428866022</v>
+        <v>-0.7787425487179429</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.739857436977578</v>
+        <v>2.807300114645042</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.275083208563437</v>
+        <v>1.443689902732096</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.884203483584028</v>
+        <v>3.985367500085224</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.365103266433439</v>
+        <v>-1.19649657226478</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570682719063906</v>
+        <v>2.63812539673137</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8573291850165997</v>
+        <v>1.025935879185259</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.631477960960989</v>
+        <v>3.732641977462185</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.65523493303887</v>
+        <v>-1.486628238870211</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.454496269020656</v>
+        <v>2.521938946688119</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8814109797567796</v>
+        <v>1.050017673925439</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.645793254404019</v>
+        <v>3.746957270905215</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.863238991391948</v>
+        <v>-1.694632297223289</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.37618679023335</v>
+        <v>2.443629467900814</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8814109797567796</v>
+        <v>1.050017673925439</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.650685398957944</v>
+        <v>3.75184941545914</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.074651412279923</v>
+        <v>-1.906044718111264</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.286703278216148</v>
+        <v>2.354145955883612</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6699985588688046</v>
+        <v>0.8386052530374637</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.518919402763148</v>
+        <v>3.620083419264343</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.440720139424576</v>
+        <v>-2.272113445255917</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.133360086664736</v>
+        <v>2.2008027643322</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3039298317241519</v>
+        <v>0.472536525892811</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.292362465782805</v>
+        <v>3.393526482284</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.649210920876261</v>
+        <v>-2.480604226707601</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.07030206382283</v>
+        <v>2.137744741490294</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.09543905027246746</v>
+        <v>0.2640457444411266</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.187606286650563</v>
+        <v>3.288770303151758</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.896412105641482</v>
+        <v>-2.727805411472823</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.97952034032531</v>
+        <v>2.046963017992774</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1155924037712799</v>
+        <v>0.284199097939939</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.207797049158418</v>
+        <v>3.308961065659614</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.388797133665579</v>
+        <v>-3.22019043949692</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.783672721159404</v>
+        <v>1.851115398826867</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.2081859300841577</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.913472424387693</v>
+        <v>3.014636440888888</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.605370830426992</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.695585781267702</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.2081859300841577</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.912014963200556</v>
+        <v>3.013178979701752</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-3.949053603653655</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.559881795431653</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.484698676280035</v>
+        <v>-0.3160919821113759</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.849040455438841</v>
+        <v>2.950204471940037</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.155565380540676</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.473383143333102</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.5226037589983974</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.721239447962886</v>
+        <v>2.822403464464082</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.643516149789837</v>
+        <v>-4.474909455621178</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.279975762333697</v>
+        <v>1.347418440001161</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.5226037589983974</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.723012374663146</v>
+        <v>2.824176391164341</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.075321942939625</v>
+        <v>-4.906715248770966</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.093586332541187</v>
+        <v>1.16102901020865</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8276279496083235</v>
+        <v>-0.6590212554396644</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.62749476426579</v>
+        <v>2.728658780766986</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.310015937072177</v>
+        <v>-5.141409242903518</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9879935098902566</v>
+        <v>1.05543618755772</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.6526849882104092</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.619581299605434</v>
+        <v>2.720745316106629</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.64567858430263</v>
+        <v>-5.477071890133971</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8523090426540407</v>
+        <v>0.919751720321504</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.6526849882104092</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.618161891261399</v>
+        <v>2.719325907762594</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-5.840698135034284</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.7807887825956206</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9195133192461942</v>
+        <v>-0.750906625077535</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.565716469375365</v>
+        <v>2.666880485876561</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.205825517673031</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.6339923445459532</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.047217409376548</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.488348530302984</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.614414294853709</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.4693183776884404</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.455806186557226</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.241956808009336</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-6.890990395169542</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.3538733700335683</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.455806186557226</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.237142240480797</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.307382269456539</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1853106709276466</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.455806186557226</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.235136291089674</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.746755052717844</v>
+        <v>-7.578148358549185</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01982024829180373</v>
+        <v>0.08726292595926743</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.455806186557226</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.245394981758353</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.092629874702652</v>
+        <v>-7.924023180533993</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1224301153564245</v>
+        <v>-0.05498743768896075</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.455806186557226</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.241494546904049</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.256209752887036</v>
+        <v>-8.087603058718377</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1894571465751773</v>
+        <v>-0.1220144689077136</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.455806186557226</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.23989946695905</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552871094697235</v>
+        <v>-8.384264400528576</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3043427073700484</v>
+        <v>-0.2369000297025847</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.524549322291105</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.202432561447931</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.739590803006537</v>
+        <v>-8.570984108837878</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3830568952281723</v>
+        <v>-0.3156142175607091</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.524549322291105</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.198406256913527</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.122592191749169</v>
+        <v>-8.95398549758051</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5363595520468092</v>
+        <v>-0.4689168743793455</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.524549322291105</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.198304155591943</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.304461982734203</v>
+        <v>-9.135855288565544</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6065359524693927</v>
+        <v>-0.539093274801929</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.70641911327614</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>2.091753796972352</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.663992305238205</v>
+        <v>-9.495385611069546</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7449977781729431</v>
+        <v>-0.6775551005054794</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.70641911327614</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>2.097104100270403</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714341368692427</v>
+        <v>-9.545734674523768</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7572213835974546</v>
+        <v>-0.6897787059299909</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.756768176730362</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>2.074810682155047</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.811960646113823</v>
+        <v>-9.643353951945164</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7932273439442441</v>
+        <v>-0.7257846662767804</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-1.854387454151758</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>2.019280866323978</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-9.790880039950807</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.7819015451574653</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.001913542157402</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.933658769842164</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-9.99513821528067</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.8580916181707687</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.129552486771391</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.862588600192413</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23807788570949</v>
+        <v>-10.06947119154083</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9507849318578621</v>
+        <v>-0.8833422541903979</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.442858704874723</v>
+        <v>-2.274252010706063</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.67908742381485</v>
+        <v>1.780251440316045</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.16460805404204</v>
+        <v>-9.996001359873386</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.906025297697461</v>
+        <v>-0.8385826200299977</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.369388873207274</v>
+        <v>-2.200782179038615</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.73854102430874</v>
+        <v>1.839705040809936</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33973247142859</v>
+        <v>-10.17112577725993</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9615198439045614</v>
+        <v>-0.8940771662370981</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.544513290593818</v>
+        <v>-2.375906596425159</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.64802159462433</v>
+        <v>1.749185611125526</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57418456544308</v>
+        <v>-10.40557787127442</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.062519846411953</v>
+        <v>-0.9950771687444901</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.544513290593818</v>
+        <v>-2.375906596425159</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.640802429722734</v>
+        <v>1.74196644622393</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.86198840998032</v>
+        <v>-10.69338171581166</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.184313575000826</v>
+        <v>-1.116870897333361</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.832317135131056</v>
+        <v>-2.663710440962397</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.461447932226415</v>
+        <v>1.562611948727611</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.91477456558064</v>
+        <v>-10.74616787141198</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.2043122474024</v>
+        <v>-1.136869569734936</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.927992621713453</v>
+        <v>-2.759385927544794</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.405158430115533</v>
+        <v>1.506322446616729</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.04081135894893</v>
+        <v>-10.87220466478027</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.252033236120601</v>
+        <v>-1.184590558453137</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.902740998903711</v>
+        <v>-2.734134304735051</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.423003132430493</v>
+        <v>1.524167148931689</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.98879584498012</v>
+        <v>-10.82018915081146</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.227236694846675</v>
+        <v>-1.159794017179211</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.902740998903711</v>
+        <v>-2.734134304735051</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.426993468116894</v>
+        <v>1.52815748461809</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.13046768670424</v>
+        <v>-10.96186099253558</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.285380658435065</v>
+        <v>-1.217937980767601</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.902740998903711</v>
+        <v>-2.734134304735051</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.425518241218153</v>
+        <v>1.526682257719348</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.08087684227941</v>
+        <v>-10.91227014811075</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.250490910500258</v>
+        <v>-1.183048232832795</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.853150154478877</v>
+        <v>-2.684543460310218</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.470326158037925</v>
+        <v>1.571490174539121</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.06806944927463</v>
+        <v>-10.89946275510597</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.258419086945032</v>
+        <v>-1.190976409277568</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.902005929487778</v>
+        <v>-2.733399235319119</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.427961559385902</v>
+        <v>1.529125575887097</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.84222429655522</v>
+        <v>-10.67361760238656</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.158501952821058</v>
+        <v>-1.091059275153595</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.860079253900614</v>
+        <v>-2.691472559731955</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.462696637774409</v>
+        <v>1.563860654275604</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.71764564021763</v>
+        <v>-10.54903894604897</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.107531345729962</v>
+        <v>-1.040088668062499</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.860079253900614</v>
+        <v>-2.691472559731955</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.463835782330468</v>
+        <v>1.564999798831663</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.77054092826191</v>
+        <v>-10.60193423409325</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.12605568678557</v>
+        <v>-1.058613009118106</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.855123907812168</v>
+        <v>-2.686517213643509</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.469442764145643</v>
+        <v>1.570606780646838</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.69840775297403</v>
+        <v>-10.52980105880537</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.091468712431781</v>
+        <v>-1.024026034764317</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.855123907812168</v>
+        <v>-2.686517213643509</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.475176468384279</v>
+        <v>1.576340484885475</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.62704136036439</v>
+        <v>-10.45843466619573</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.072659417781787</v>
+        <v>-1.005216740114323</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.78375751520252</v>
+        <v>-2.615150821033861</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.508259041556203</v>
+        <v>1.609423058057398</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.36320449316032</v>
+        <v>-10.19459779899166</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9770081522130662</v>
+        <v>-0.909565474545603</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.78375751520252</v>
+        <v>-2.615150821033861</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.498375560243296</v>
+        <v>1.599539576744491</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.09596269229192</v>
+        <v>-9.927355998123259</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8719459923650814</v>
+        <v>-0.8045033146976177</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.78375751520252</v>
+        <v>-2.615150821033861</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.496540999743922</v>
+        <v>1.597705016245117</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.998055653615427</v>
+        <v>-9.829448959446768</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8330834918679457</v>
+        <v>-0.765640814200482</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.715771765341963</v>
+        <v>-2.547165071173304</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.537032134686795</v>
+        <v>1.63819615118799</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.97410211263947</v>
+        <v>-9.805495418470811</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8228335693320692</v>
+        <v>-0.7553908916646055</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.691818224366006</v>
+        <v>-2.523211530197347</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.552072765417863</v>
+        <v>1.653236781919058</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.710042174316673</v>
+        <v>-9.541435480148014</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7304699101647025</v>
+        <v>-0.6630272324972388</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.42775828604321</v>
+        <v>-2.259151591874551</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.697248412249788</v>
+        <v>1.798412428750984</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.002962550811835</v>
+        <v>-8.834355856643176</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4504250944230686</v>
+        <v>-0.3829824167556048</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.42775828604321</v>
+        <v>-2.259151591874551</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.694461378589488</v>
+        <v>1.795625395090683</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.962778252445645</v>
+        <v>-8.794171558276986</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.434007751188751</v>
+        <v>-0.3665650735212873</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.387573987677019</v>
+        <v>-2.21896729350836</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.718915581497043</v>
+        <v>1.820079597998239</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.799378381506283</v>
+        <v>-8.630771687337624</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3692809815922491</v>
+        <v>-0.3018383039247858</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.224174116737657</v>
+        <v>-2.055567422568997</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.816322325281418</v>
+        <v>1.917486341782613</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.565897159276684</v>
+        <v>-8.397290465108025</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2679640638625571</v>
+        <v>-0.2005213861950934</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.990692894508058</v>
+        <v>-1.822086200339399</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.96433548745703</v>
+        <v>2.065499503958224</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.41623076826917</v>
+        <v>-8.247624074100511</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2109897177725104</v>
+        <v>-0.1435470401050472</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.897789403265522</v>
+        <v>-1.729182709096863</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.017185371889592</v>
+        <v>2.118349388390787</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.283955294638282</v>
+        <v>-8.115348600469623</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1627120415731285</v>
+        <v>-0.09526936390566521</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.765513929634635</v>
+        <v>-1.596907235465976</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.091918142815151</v>
+        <v>2.193082159316346</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.093355619965129</v>
+        <v>-7.924748925796471</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.08365711101623052</v>
+        <v>-0.01621443334876727</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.574914254961483</v>
+        <v>-1.406307560792823</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.209093008306679</v>
+        <v>2.310257024807874</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.844355821281548</v>
+        <v>-7.67574912711289</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.02884914968086072</v>
+        <v>0.09629182734832398</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.574914254961483</v>
+        <v>-1.406307560792823</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.221999349530338</v>
+        <v>2.323163366031533</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.949945811054652</v>
+        <v>-7.781339116885994</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1413627758275999</v>
+        <v>-0.07392009816013667</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.680504244734587</v>
+        <v>-1.511897550565928</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.030669426067257</v>
+        <v>2.131833442568452</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.968680713173249</v>
+        <v>-7.800074019004591</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1003123947979523</v>
+        <v>-0.03286971713048903</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.686100254394718</v>
+        <v>-1.517493560226059</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.075856162148265</v>
+        <v>2.177020178649459</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.82074067176565</v>
+        <v>-7.652133977596992</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1610153009230801</v>
+        <v>-0.09357262325561688</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.665779338486161</v>
+        <v>-1.497172644317502</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.968169789005231</v>
+        <v>2.069333805506427</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.767771149511661</v>
+        <v>-7.599164455343003</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.148541478274963</v>
+        <v>-0.08109880060749974</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.612809816232172</v>
+        <v>-1.444203122063513</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.991237516104146</v>
+        <v>2.092401532605342</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.724222742740971</v>
+        <v>-7.555616048572313</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.13808272766178</v>
+        <v>-0.07064004999431672</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.612809816232172</v>
+        <v>-1.444203122063513</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.984276904009053</v>
+        <v>2.085440920510249</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.482074349287113</v>
+        <v>-7.313467655118455</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.02676101589909363</v>
+        <v>0.04068166176836963</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.612809816232172</v>
+        <v>-1.444203122063513</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.998739258390196</v>
+        <v>2.099903274891392</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.373815212164591</v>
+        <v>-7.205208517995933</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.01107475940911007</v>
+        <v>0.07851743707657333</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.612809816232172</v>
+        <v>-1.444203122063513</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.993271378849391</v>
+        <v>2.094435395350587</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.25052407734746</v>
+        <v>-7.081917383178802</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.05788930734653919</v>
+        <v>0.1253319850140024</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.489518681415041</v>
+        <v>-1.320911987246382</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.064744153750246</v>
+        <v>2.165908170251442</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.229374878444017</v>
+        <v>-7.060768184275359</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.07404996514524198</v>
+        <v>0.1414926428127052</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.468369482511598</v>
+        <v>-1.299762788342939</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.085134651329638</v>
+        <v>2.186298667830833</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.985609436460573</v>
+        <v>-6.817002742291915</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1673368502856705</v>
+        <v>0.2347795279531337</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.468369482511598</v>
+        <v>-1.299762788342939</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.080915359676689</v>
+        <v>2.182079376177884</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.883846616183278</v>
+        <v>-6.71523992201462</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2101662923166043</v>
+        <v>0.2776089699840676</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.455150414119169</v>
+        <v>-1.28654371995051</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.090971114632162</v>
+        <v>2.192135131133357</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.633996222234203</v>
+        <v>-6.465389528065545</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3028485248799364</v>
+        <v>0.3702912025473997</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.455150414119169</v>
+        <v>-1.28654371995051</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.083713189615864</v>
+        <v>2.184877206117059</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.45810412976677</v>
+        <v>-6.289497435598113</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3768044853875581</v>
+        <v>0.4442471630550209</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.455150414119169</v>
+        <v>-1.28654371995051</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.087312313136513</v>
+        <v>2.188476329637708</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.286657666744307</v>
+        <v>-6.11805097257565</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.458710576651097</v>
+        <v>0.5261532543185603</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.283703951096706</v>
+        <v>-1.115097256928047</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.203507697004544</v>
+        <v>2.30467171350574</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061624667075484</v>
+        <v>-5.893017972906827</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5477442541349236</v>
+        <v>0.6151869318023864</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.058670951427883</v>
+        <v>-0.890064257259224</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.337547974422135</v>
+        <v>2.43871199092333</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997988924841549</v>
+        <v>-5.829382230672892</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5778933520828144</v>
+        <v>0.6453360297502773</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9950352091939484</v>
+        <v>-0.8264285150252895</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.380424220816813</v>
+        <v>2.481588237318008</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.954226743535708</v>
+        <v>-5.785620049367051</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5765924833889469</v>
+        <v>0.6440351610564097</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9950352091939484</v>
+        <v>-0.8264285150252895</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.361618479600609</v>
+        <v>2.462782496101804</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.713796246730848</v>
+        <v>-5.54518955256219</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6745077587357682</v>
+        <v>0.741950436403231</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7546047123890881</v>
+        <v>-0.5859980182204292</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.507619854308402</v>
+        <v>2.608783870809597</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.641553678559653</v>
+        <v>-5.472946984390996</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7073340998390663</v>
+        <v>0.7747767775065291</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7546047123890881</v>
+        <v>-0.5859980182204292</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.511549168143222</v>
+        <v>2.612713184644417</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.588555356278265</v>
+        <v>-5.419948662109608</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7292120126689614</v>
+        <v>0.7966546903364242</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6992684533871493</v>
+        <v>-0.5306617592184903</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.545429507461725</v>
+        <v>2.646593523962921</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.479750470798538</v>
+        <v>-5.311143776629881</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7697320380808459</v>
+        <v>0.8371747157483087</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6992684533871493</v>
+        <v>-0.5306617592184903</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.542427578681719</v>
+        <v>2.643591595182914</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.259729672761527</v>
+        <v>-5.09112297859287</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8593193943062643</v>
+        <v>0.9267620719737271</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.558048608319169</v>
+        <v>-0.3894419141505101</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.628738522733121</v>
+        <v>2.729902539234317</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.12686198369825</v>
+        <v>-4.958255289529593</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9283606527333985</v>
+        <v>0.9958033304008613</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.558048608319169</v>
+        <v>-0.3894419141505101</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.644632705534945</v>
+        <v>2.74579672203614</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.006688900333751</v>
+        <v>-4.838082206165094</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9775757305194999</v>
+        <v>1.045018408186963</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4378755249546701</v>
+        <v>-0.2692688307860112</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.717882399993946</v>
+        <v>2.819046416495141</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.862016755234014</v>
+        <v>-4.693410061065356</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.045532691120835</v>
+        <v>1.112975368788298</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2932033798549327</v>
+        <v>-0.1245966856862737</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.814773789615228</v>
+        <v>2.915937806116423</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.921891582591706</v>
+        <v>-4.753284888423049</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.007620251579184</v>
+        <v>1.075062929246646</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3530782072126248</v>
+        <v>-0.1844715130439659</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.764886384602039</v>
+        <v>2.866050401103234</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.835092084812697</v>
+        <v>-4.66648539064404</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.064740544013353</v>
+        <v>1.132183221680816</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3530782072126248</v>
+        <v>-0.1844715130439659</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.787286877924605</v>
+        <v>2.8884508944258</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.837561791274503</v>
+        <v>-4.668955097105846</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.063825062802043</v>
+        <v>1.131267740469506</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3555479136744309</v>
+        <v>-0.186941219505772</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.785877455420933</v>
+        <v>2.887041471922128</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.905931977598513</v>
+        <v>-4.737325283429856</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.047483910747141</v>
+        <v>1.114926588414604</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.1776655204695571</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.802449797317364</v>
+        <v>2.90361381381856</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.014470158514647</v>
+        <v>-4.84586346434599</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9945053470125789</v>
+        <v>1.061948024680042</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.1776655204695571</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.792886505949256</v>
+        <v>2.894050522450451</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.045463317843352</v>
+        <v>-4.876856623674695</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8068176483214833</v>
+        <v>0.8742603259889463</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.1776655204695571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.617596070989642</v>
+        <v>2.718760087490838</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.869989058050884</v>
+        <v>-4.701382363882226</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8815745842302587</v>
+        <v>0.9490172618977217</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.1776655204695571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.62216330298143</v>
+        <v>2.723327319482626</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.980925310692133</v>
+        <v>-4.812318616523475</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8129421119349662</v>
+        <v>0.8803847896024291</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.1776655204695571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.597905331742637</v>
+        <v>2.699069348243833</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.989207384837191</v>
+        <v>-4.820600690668534</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8127606674968484</v>
+        <v>0.8802033451643112</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3545542887832744</v>
+        <v>-0.1859475946146155</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596067472475508</v>
+        <v>2.697231488976703</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.929354765633468</v>
+        <v>-4.76074807146481</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8468741016104699</v>
+        <v>0.914316779277933</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3545542887832744</v>
+        <v>-0.1859475946146155</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.60623985890764</v>
+        <v>2.707403875408835</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.84311130260709</v>
+        <v>-4.674504608438433</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8763177573948815</v>
+        <v>0.9437604350623443</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3545542887832744</v>
+        <v>-0.1859475946146155</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.6011861294815</v>
+        <v>2.702350145982696</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.88841812200607</v>
+        <v>-4.719811427837413</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8499708050798152</v>
+        <v>0.917413482747278</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3953644517925052</v>
+        <v>-0.2267577576238463</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.568475807120488</v>
+        <v>2.669639823621683</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.917451226708371</v>
+        <v>-4.748844532539714</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8389094362319962</v>
+        <v>0.906352113899459</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3953644517925052</v>
+        <v>-0.2267577576238463</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.569027680153589</v>
+        <v>2.670191696654785</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.824640745257511</v>
+        <v>-4.656034051088854</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8053063207037057</v>
+        <v>0.8727489983711685</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3025539703416458</v>
+        <v>-0.1339472761729869</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.55398666091547</v>
+        <v>2.655150677416666</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.869030214586939</v>
+        <v>-4.700423520418282</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7894240088965354</v>
+        <v>0.8568666865639984</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3469434396710735</v>
+        <v>-0.1783367455024146</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.529226455242414</v>
+        <v>2.63039047174361</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.756358996350689</v>
+        <v>-4.587752302182031</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8295682047027586</v>
+        <v>0.8970108823702214</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2342722214348233</v>
+        <v>-0.06566552726616437</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.591904894695888</v>
+        <v>2.693068911197083</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.643981995168016</v>
+        <v>-4.475375300999358</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.880010301006495</v>
+        <v>0.9474529786739578</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2342722214348233</v>
+        <v>-0.06566552726616437</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.597396190526555</v>
+        <v>2.69856020702775</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.842216564054747</v>
+        <v>-4.673609869886089</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8122136752203417</v>
+        <v>0.8796563528878045</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4325067903215539</v>
+        <v>-0.2639000961528949</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.489952650963056</v>
+        <v>2.591116667464251</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.925217845080025</v>
+        <v>-4.756611150911368</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6173688828108834</v>
+        <v>0.6848115604783462</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4510776748487276</v>
+        <v>-0.2824709806800687</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.317165840247405</v>
+        <v>2.4183298567486</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.033831923523357</v>
+        <v>-4.865225229354699</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6940729121527567</v>
+        <v>0.7615155898202195</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4510776748487276</v>
+        <v>-0.2824709806800687</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.43731550096661</v>
+        <v>2.538479517467806</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.12043050650446</v>
+        <v>-4.951823812335802</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6739465050626383</v>
+        <v>0.7413891827301013</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4510776748487276</v>
+        <v>-0.2824709806800687</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.451828527068933</v>
+        <v>2.552992543570129</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.082046843946308</v>
+        <v>-4.913440149777651</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6867194114282675</v>
+        <v>0.7541620890957303</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4126940122905765</v>
+        <v>-0.2440873181219175</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.472278165946193</v>
+        <v>2.573442182447388</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.904930513911142</v>
+        <v>-4.736323819742485</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.754294972287636</v>
+        <v>0.8217376499550988</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4126940122905765</v>
+        <v>-0.2440873181219175</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.469007194791494</v>
+        <v>2.57017121129269</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.950022758744688</v>
+        <v>-4.781416064576031</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7369414661161307</v>
+        <v>0.8043841437835937</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4745900554599662</v>
+        <v>-0.3059833612913073</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.432552960651774</v>
+        <v>2.533716977152969</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.77064733750592</v>
+        <v>-4.602040643337263</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8024786099180521</v>
+        <v>0.8699212875855151</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3178132972892476</v>
+        <v>-0.1492066031205886</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.520405990860619</v>
+        <v>2.621570007361814</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.815661551026526</v>
+        <v>-4.647054856857869</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7652803798413996</v>
+        <v>0.8327230575088624</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3481621926038522</v>
+        <v>-0.1795554984351933</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.483004109003446</v>
+        <v>2.584168125504642</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.082666061298961</v>
+        <v>-4.914059367130304</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6641701380713712</v>
+        <v>0.7316128157388342</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5425252306468007</v>
+        <v>-0.3739185364781418</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.372077848516623</v>
+        <v>2.473241865017818</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.183863842736134</v>
+        <v>-5.015257148567477</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6228949473930037</v>
+        <v>0.6903376250604665</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6109340441921198</v>
+        <v>-0.442327350023461</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.330236482285933</v>
+        <v>2.431400498787128</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.151388256565362</v>
+        <v>-4.982781562396704</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6334851434156294</v>
+        <v>0.7009278210830923</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6109340441921198</v>
+        <v>-0.442327350023461</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.327836443840249</v>
+        <v>2.429000460341445</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.132350128858064</v>
+        <v>-4.963743434689407</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6376251137067932</v>
+        <v>0.705067791374256</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6691176555233144</v>
+        <v>-0.5005109613546556</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.289450996249778</v>
+        <v>2.390615012750973</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.163476760008683</v>
+        <v>-4.994870065840026</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8027563301852263</v>
+        <v>0.8701990078526891</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6691176555233144</v>
+        <v>-0.5005109613546556</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.467032865188458</v>
+        <v>2.568196881689654</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.215797140609475</v>
+        <v>-5.047190446440817</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.782661506931043</v>
+        <v>0.8501041845985062</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6341707955144422</v>
+        <v>-0.4655641013457834</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.488834310179915</v>
+        <v>2.589998326681111</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.236054439138432</v>
+        <v>-5.067447744969775</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.780567117916386</v>
+        <v>0.8480097955838488</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6341707955144422</v>
+        <v>-0.4655641013457834</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.494842840576841</v>
+        <v>2.596006857078037</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.08831146890343</v>
+        <v>-4.919704774734773</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9188169538024087</v>
+        <v>0.9862596314698717</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4663634382795591</v>
+        <v>-0.2977567441109003</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.674679902709793</v>
+        <v>2.775843919210988</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.190326151434651</v>
+        <v>-5.021719457265994</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8808047023214014</v>
+        <v>0.9482473799888642</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4663634382795591</v>
+        <v>-0.2977567441109003</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.677473524241274</v>
+        <v>2.778637540742469</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.184173445381867</v>
+        <v>-5.01556675121321</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8839281331341735</v>
+        <v>0.9513708108016363</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4602107322267748</v>
+        <v>-0.291604038058116</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.681827496264603</v>
+        <v>2.782991512765798</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.200982743532369</v>
+        <v>-5.032376049363712</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.876284890614083</v>
+        <v>0.9437275682815458</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4770200303772764</v>
+        <v>-0.3084133362086176</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.670822394114412</v>
+        <v>2.771986410615607</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.138684744756246</v>
+        <v>-4.970078050587589</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9675396439213526</v>
+        <v>1.034982321588816</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4770200303772764</v>
+        <v>-0.3084133362086176</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.737157947911233</v>
+        <v>2.838321964412428</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.936894547091089</v>
+        <v>-4.768287852922431</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7568365953768139</v>
+        <v>0.8242792730442767</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.279001838208122</v>
+        <v>-0.1103951440394632</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.564549735602124</v>
+        <v>2.665713752103319</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.877003865448495</v>
+        <v>-4.708397171279838</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8510831003560264</v>
+        <v>0.9185257780234894</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2191111565655285</v>
+        <v>-0.05050446239686973</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.670774376909855</v>
+        <v>2.77193839341105</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.97474441007347</v>
+        <v>-4.806137715904812</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8266146186220804</v>
+        <v>0.8940572962895432</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2350004346985087</v>
+        <v>-0.06639374052984992</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.67586854614611</v>
+        <v>2.777032562647306</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.151082170196399</v>
+        <v>-4.982475476027742</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7546154953975801</v>
+        <v>0.8220581730650431</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4113381948214381</v>
+        <v>-0.2427315006527793</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.568601870897024</v>
+        <v>2.66976588739822</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.079535847419522</v>
+        <v>-4.910929153250865</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7817256425482597</v>
+        <v>0.8491683202157225</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4113381948214381</v>
+        <v>-0.2427315006527793</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.567093488936953</v>
+        <v>2.668257505438148</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.035162715780953</v>
+        <v>-4.866556021612296</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7993377626391234</v>
+        <v>0.8667804403065862</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3669650631828695</v>
+        <v>-0.1983583690142107</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.59358023535553</v>
+        <v>2.694744251856726</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.027208745486181</v>
+        <v>-4.858602051317524</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8025193507570321</v>
+        <v>0.8699620284244951</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3669650631828695</v>
+        <v>-0.1983583690142107</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.59358023535553</v>
+        <v>2.694744251856726</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.979553014925125</v>
+        <v>-4.810946320756468</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8279634000092591</v>
+        <v>0.8954060776767221</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3193093326218139</v>
+        <v>-0.1507026384531551</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.628555430719969</v>
+        <v>2.729719447221164</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.851868705130829</v>
+        <v>-4.683262010962172</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8839294973017024</v>
+        <v>0.9513721749691655</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1916250228275174</v>
+        <v>-0.02301832865885861</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.710058389971271</v>
+        <v>2.811222406472466</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.912535295533218</v>
+        <v>-4.74392860136456</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8464175336166193</v>
+        <v>0.9138602112840821</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2733233395460511</v>
+        <v>-0.1047166453773923</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.647794072416023</v>
+        <v>2.748958088917218</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.847541435599572</v>
+        <v>-4.678934741430915</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.876512780200706</v>
+        <v>0.943955457868169</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2464927249418957</v>
+        <v>-0.07788603077323691</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.667990143789145</v>
+        <v>2.76915416029034</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.94830007135657</v>
+        <v>-4.779693377187913</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8403702655289849</v>
+        <v>0.9078129431964477</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3353182936689011</v>
+        <v>-0.1667115995002423</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.61885574218402</v>
+        <v>2.720019758685215</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.90409723427067</v>
+        <v>-4.735490540102012</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8639310028911822</v>
+        <v>0.931373680558645</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2911154565830007</v>
+        <v>-0.1225087624143419</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.651257046963397</v>
+        <v>2.752421063464592</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.941076261934112</v>
+        <v>-4.772469567765455</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8475493922950526</v>
+        <v>0.9149920699625156</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.2541415547916702</v>
+        <v>-0.08553486062301136</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.671851388507443</v>
+        <v>2.773015405008638</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.961134340798953</v>
+        <v>-4.792527646630296</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8907739259321561</v>
+        <v>0.9582166035996189</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.2541415547916702</v>
+        <v>-0.08553486062301136</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.723099153690482</v>
+        <v>2.824263170191678</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.921203667621063</v>
+        <v>-4.752596973452405</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9051868997975654</v>
+        <v>0.9726295774650282</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.2142108816137798</v>
+        <v>-0.04560418744512101</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.74549826219147</v>
+        <v>2.846662278692665</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.880733320058358</v>
+        <v>-4.712126625889701</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9163232670609172</v>
+        <v>0.9837659447283802</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.1737405340510749</v>
+        <v>-0.005133839882416058</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.764728698967363</v>
+        <v>2.865892715468558</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.815509138931152</v>
+        <v>-4.646902444762495</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9596003436045044</v>
+        <v>1.027043021271967</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1085163529238692</v>
+        <v>0.06009034124478957</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.821050611736391</v>
+        <v>2.922214628237587</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.866003429288209</v>
+        <v>-4.697396735119551</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9353635997609622</v>
+        <v>1.002806277428425</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.1535370900499435</v>
+        <v>0.01506960411871533</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.789999141760027</v>
+        <v>2.891163158261222</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.886115085322917</v>
+        <v>-4.71750839115426</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9285757296783193</v>
+        <v>0.9960184073457821</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.1425097450525243</v>
+        <v>0.02609694911613453</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.797872341089719</v>
+        <v>2.899036357590914</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.983795664595563</v>
+        <v>-4.815188970426906</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.050061268990471</v>
+        <v>1.117503946657934</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.2532129403927131</v>
+        <v>-0.08460624622405427</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.892008194906817</v>
+        <v>2.993172211408011</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.96000409598942</v>
+        <v>-4.791397401820763</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.179690805650746</v>
+        <v>1.247133483318209</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.2294213717865708</v>
+        <v>-0.06081467761791198</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.026396045288319</v>
+        <v>3.127560061789514</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.996758514551143</v>
+        <v>-4.828151820382486</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.156697014239916</v>
+        <v>1.224139691907379</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.2294213717865708</v>
+        <v>-0.06081467761791198</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.018104021302178</v>
+        <v>3.119268037803373</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.846421326899819</v>
+        <v>3.844269268987958</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.990870957208248</v>
+        <v>-4.965872922371298</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.157245232760853</v>
+        <v>1.167244446695633</v>
       </c>
       <c r="F1994" t="n">
-        <v>-0.07761894864504021</v>
+        <v>0.06433675575433379</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.107378670770876</v>
+        <v>3.1925520934105</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-675.7%</t>
+          <t>-692.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>434.7%</t>
+          <t>448.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-658.2%</t>
+          <t>-683.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-270.7%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-42.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>103.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.5%</t>
+          <t>-278.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-289.3%</t>
+          <t>-306.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-146.0%</t>
+          <t>-161.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.6%</t>
+          <t>-245.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-173.9%</t>
+          <t>-184.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-126.8%</t>
+          <t>-152.0%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9184028726189427</v>
+        <v>0.7497961784502833</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.50692266700944</v>
+        <v>3.439479989341976</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.800371318848367</v>
+        <v>1.631764624679707</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.22014073358463</v>
+        <v>4.118976717083434</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.7218524615657371</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.426560338450502</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.83702548453687</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.240391068860077</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.5683330770802725</v>
+        <v>0.3997263829116132</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.344977857283763</v>
+        <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.873991959006394</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.242396226169238</v>
+        <v>4.141232209668043</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3863265137573039</v>
+        <v>0.2177198195886446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.27266437068045</v>
+        <v>3.205221693012986</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.873991959006394</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.242885364895113</v>
+        <v>4.141721348393917</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.3381042469102203</v>
+        <v>0.1694975527415611</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.257455446563283</v>
+        <v>3.19001276889582</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.825769692159311</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.218031987408529</v>
+        <v>4.116867970907334</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1009727550604252</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.197543934320907</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.825769692159311</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.252973071906071</v>
+        <v>4.151809055404875</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1060103457880118</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.19813641079728</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.881414148425628</v>
+        <v>1.712807454256969</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.2849371858512</v>
+        <v>4.183773169350004</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.151183688920045</v>
+        <v>-0.3197903830887042</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.074005178537794</v>
+        <v>3.006562500870331</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.624220113717571</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.109367146650102</v>
+        <v>4.008203130148907</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.216951078969457</v>
+        <v>-0.3855577731381163</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.048715831648499</v>
+        <v>2.981273153981036</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.624220113717571</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.110384755780572</v>
+        <v>4.009220739279377</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4221957560267016</v>
+        <v>-0.5908024501953608</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.957245992813357</v>
+        <v>2.889803315145894</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.624220113717571</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.101012787768328</v>
+        <v>3.999848771267133</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.5039676564544533</v>
+        <v>-0.6725743506231125</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.914619958597495</v>
+        <v>2.847177280930031</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.651255687123708</v>
+        <v>1.482648992955049</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.107316857767248</v>
+        <v>4.006152841266053</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.571176764326331</v>
+        <v>-0.7397834584949903</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.892501632282446</v>
+        <v>2.825058954614982</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.651255687123708</v>
+        <v>1.482648992955049</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.112082174600951</v>
+        <v>4.010918158099756</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7787425487179429</v>
+        <v>-0.9473492428866022</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.807300114645042</v>
+        <v>2.739857436977578</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.443689902732096</v>
+        <v>1.275083208563437</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.985367500085224</v>
+        <v>3.884203483584028</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.19649657226478</v>
+        <v>-1.365103266433439</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.63812539673137</v>
+        <v>2.570682719063906</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.025935879185259</v>
+        <v>0.8573291850165997</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.732641977462185</v>
+        <v>3.631477960960989</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.486628238870211</v>
+        <v>-1.65523493303887</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.521938946688119</v>
+        <v>2.454496269020656</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.050017673925439</v>
+        <v>0.8814109797567796</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.746957270905215</v>
+        <v>3.645793254404019</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.694632297223289</v>
+        <v>-1.863238991391948</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.443629467900814</v>
+        <v>2.37618679023335</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.050017673925439</v>
+        <v>0.8814109797567796</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.75184941545914</v>
+        <v>3.650685398957944</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.906044718111264</v>
+        <v>-2.074651412279923</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.354145955883612</v>
+        <v>2.286703278216148</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8386052530374637</v>
+        <v>0.6699985588688046</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.620083419264343</v>
+        <v>3.518919402763148</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.272113445255917</v>
+        <v>-2.440720139424576</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.2008027643322</v>
+        <v>2.133360086664736</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.472536525892811</v>
+        <v>0.3039298317241519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.393526482284</v>
+        <v>3.292362465782805</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.480604226707601</v>
+        <v>-2.649210920876261</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.137744741490294</v>
+        <v>2.07030206382283</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2640457444411266</v>
+        <v>0.09543905027246746</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.288770303151758</v>
+        <v>3.187606286650563</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.727805411472823</v>
+        <v>-2.896412105641482</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.046963017992774</v>
+        <v>1.97952034032531</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.284199097939939</v>
+        <v>0.1155924037712799</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.308961065659614</v>
+        <v>3.207797049158418</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.22019043949692</v>
+        <v>-3.388797133665579</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.851115398826867</v>
+        <v>1.783672721159404</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2081859300841577</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.014636440888888</v>
+        <v>2.913472424387693</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.605370830426992</v>
+        <v>-3.773977524595651</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.695585781267702</v>
+        <v>1.628143103600238</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2081859300841577</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.013178979701752</v>
+        <v>2.912014963200556</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.949053603653655</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.559881795431653</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3160919821113759</v>
+        <v>-0.484698676280035</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.950204471940037</v>
+        <v>2.849040455438841</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.155565380540676</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.473383143333102</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5226037589983974</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.822403464464082</v>
+        <v>2.721239447962886</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.474909455621178</v>
+        <v>-4.643516149789837</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.347418440001161</v>
+        <v>1.279975762333697</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5226037589983974</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.824176391164341</v>
+        <v>2.723012374663146</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.906715248770966</v>
+        <v>-5.075321942939625</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.16102901020865</v>
+        <v>1.093586332541187</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6590212554396644</v>
+        <v>-0.8276279496083235</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.728658780766986</v>
+        <v>2.62749476426579</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.141409242903518</v>
+        <v>-5.310015937072177</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.05543618755772</v>
+        <v>0.9879935098902566</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6526849882104092</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.720745316106629</v>
+        <v>2.619581299605434</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.477071890133971</v>
+        <v>-5.64567858430263</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.919751720321504</v>
+        <v>0.8523090426540407</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6526849882104092</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.719325907762594</v>
+        <v>2.618161891261399</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.840698135034284</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7807887825956206</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.750906625077535</v>
+        <v>-0.9195133192461942</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.666880485876561</v>
+        <v>2.565716469375365</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.205825517673031</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6339923445459532</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.047217409376548</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.488348530302984</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.614414294853709</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4693183776884404</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.455806186557226</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.241956808009336</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.890990395169542</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3538733700335683</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.455806186557226</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.237142240480797</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.307382269456539</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1853106709276466</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.455806186557226</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.235136291089674</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.578148358549185</v>
+        <v>-7.746755052717844</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08726292595926743</v>
+        <v>0.01982024829180373</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.455806186557226</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.245394981758353</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.924023180533993</v>
+        <v>-8.092629874702652</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05498743768896075</v>
+        <v>-0.1224301153564245</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.455806186557226</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.241494546904049</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.087603058718377</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1220144689077136</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.455806186557226</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.23989946695905</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.384264400528576</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2369000297025847</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.524549322291105</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.202432561447931</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.570984108837878</v>
+        <v>-8.739590803006537</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3156142175607091</v>
+        <v>-0.3830568952281723</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.524549322291105</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.198406256913527</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.95398549758051</v>
+        <v>-9.122592191749169</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4689168743793455</v>
+        <v>-0.5363595520468092</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.524549322291105</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.198304155591943</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.135855288565544</v>
+        <v>-9.304461982734203</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.539093274801929</v>
+        <v>-0.6065359524693927</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.70641911327614</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.091753796972352</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.495385611069546</v>
+        <v>-9.663992305238205</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6775551005054794</v>
+        <v>-0.7449977781729431</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.70641911327614</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.097104100270403</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.545734674523768</v>
+        <v>-9.714341368692427</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6897787059299909</v>
+        <v>-0.7572213835974546</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.756768176730362</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.074810682155047</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.643353951945164</v>
+        <v>-9.811960646113823</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7257846662767804</v>
+        <v>-0.7932273439442441</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.854387454151758</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.019280866323978</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.790880039950807</v>
+        <v>-9.959486734119466</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7819015451574653</v>
+        <v>-0.8493442228249291</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.001913542157402</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.933658769842164</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.99513821528067</v>
+        <v>-10.16374490944933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8580916181707687</v>
+        <v>-0.925534295838232</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.129552486771391</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.862588600192413</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06947119154083</v>
+        <v>-10.23807788570949</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8833422541903979</v>
+        <v>-0.9507849318578621</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.274252010706063</v>
+        <v>-2.442858704874723</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.780251440316045</v>
+        <v>1.67908742381485</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.996001359873386</v>
+        <v>-10.29530561288686</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8385826200299977</v>
+        <v>-0.9583043212353859</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.200782179038615</v>
+        <v>-2.500086432052085</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.839705040809936</v>
+        <v>1.660122489001854</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.17112577725993</v>
+        <v>-10.4704300302734</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8940771662370981</v>
+        <v>-1.013798867442486</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.375906596425159</v>
+        <v>-2.675210849438629</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.749185611125526</v>
+        <v>1.569603059317444</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.40557787127442</v>
+        <v>-10.70488212428789</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9950771687444901</v>
+        <v>-1.114798869949878</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.375906596425159</v>
+        <v>-2.675210849438629</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.74196644622393</v>
+        <v>1.562383894415848</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.69338171581166</v>
+        <v>-10.99268596882513</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.116870897333361</v>
+        <v>-1.23659259853875</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.663710440962397</v>
+        <v>-2.963014693975867</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.562611948727611</v>
+        <v>1.383029396919529</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.74616787141198</v>
+        <v>-11.04547212442546</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.136869569734936</v>
+        <v>-1.256591270940325</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.759385927544794</v>
+        <v>-3.058690180558264</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.506322446616729</v>
+        <v>1.326739894808647</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.87220466478027</v>
+        <v>-11.17150891779374</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.184590558453137</v>
+        <v>-1.304312259658526</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.734134304735051</v>
+        <v>-3.033438557748521</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.524167148931689</v>
+        <v>1.344584597123607</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.82018915081146</v>
+        <v>-11.11949340382493</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.159794017179211</v>
+        <v>-1.279515718384599</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.734134304735051</v>
+        <v>-3.033438557748521</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.52815748461809</v>
+        <v>1.348574932810008</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.96186099253558</v>
+        <v>-11.26116524554905</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.217937980767601</v>
+        <v>-1.337659681972989</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.734134304735051</v>
+        <v>-3.033438557748521</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.526682257719348</v>
+        <v>1.347099705911266</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.91227014811075</v>
+        <v>-11.21157440112422</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.183048232832795</v>
+        <v>-1.302769934038183</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.684543460310218</v>
+        <v>-2.983847713323688</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.571490174539121</v>
+        <v>1.391907622731039</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.89946275510597</v>
+        <v>-11.19876700811944</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.190976409277568</v>
+        <v>-1.310698110482956</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.733399235319119</v>
+        <v>-3.032703488332589</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.529125575887097</v>
+        <v>1.349543024079015</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.67361760238656</v>
+        <v>-10.97292185540003</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.091059275153595</v>
+        <v>-1.210780976358983</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.691472559731955</v>
+        <v>-2.990776812745425</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.563860654275604</v>
+        <v>1.384278102467522</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.54903894604897</v>
+        <v>-10.84834319906244</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.040088668062499</v>
+        <v>-1.159810369267887</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.691472559731955</v>
+        <v>-2.990776812745425</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.564999798831663</v>
+        <v>1.385417247023581</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.60193423409325</v>
+        <v>-10.90123848710673</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.058613009118106</v>
+        <v>-1.178334710323495</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.686517213643509</v>
+        <v>-2.985821466656979</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.570606780646838</v>
+        <v>1.391024228838756</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.52980105880537</v>
+        <v>-10.82910531181884</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.024026034764317</v>
+        <v>-1.143747735969705</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.686517213643509</v>
+        <v>-2.985821466656979</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.576340484885475</v>
+        <v>1.396757933077393</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.45843466619573</v>
+        <v>-10.7577389192092</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.005216740114323</v>
+        <v>-1.124938441319712</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.615150821033861</v>
+        <v>-2.914455074047331</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.609423058057398</v>
+        <v>1.429840506249316</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.19459779899166</v>
+        <v>-10.49390205200513</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.909565474545603</v>
+        <v>-1.029287175750991</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.615150821033861</v>
+        <v>-2.914455074047331</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.599539576744491</v>
+        <v>1.419957024936409</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.927355998123259</v>
+        <v>-10.22666025113673</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8045033146976177</v>
+        <v>-0.9242250159030063</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.615150821033861</v>
+        <v>-2.914455074047331</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.597705016245117</v>
+        <v>1.418122464437035</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.829448959446768</v>
+        <v>-10.12875321246024</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.765640814200482</v>
+        <v>-0.8853625154058702</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.547165071173304</v>
+        <v>-2.846469324186774</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.63819615118799</v>
+        <v>1.458613599379908</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.805495418470811</v>
+        <v>-10.10479967148428</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7553908916646055</v>
+        <v>-0.8751125928699941</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.523211530197347</v>
+        <v>-2.822515783210817</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.653236781919058</v>
+        <v>1.473654230110977</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.541435480148014</v>
+        <v>-9.840739733161485</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6630272324972388</v>
+        <v>-0.782748933702627</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.259151591874551</v>
+        <v>-2.558455844888021</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.798412428750984</v>
+        <v>1.618829876942902</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.834355856643176</v>
+        <v>-9.133660109656647</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3829824167556048</v>
+        <v>-0.502704117960993</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.259151591874551</v>
+        <v>-2.558455844888021</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.795625395090683</v>
+        <v>1.616042843282601</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.794171558276986</v>
+        <v>-9.093475811290457</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3665650735212873</v>
+        <v>-0.4862867747266755</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.21896729350836</v>
+        <v>-2.51827154652183</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.820079597998239</v>
+        <v>1.640497046190157</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.630771687337624</v>
+        <v>-8.930075940351095</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3018383039247858</v>
+        <v>-0.421560005130174</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.055567422568997</v>
+        <v>-2.354871675582467</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.917486341782613</v>
+        <v>1.737903789974531</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.397290465108025</v>
+        <v>-8.696594718121496</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2005213861950934</v>
+        <v>-0.320243087400482</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.822086200339399</v>
+        <v>-2.121390453352869</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.065499503958224</v>
+        <v>1.885916952150143</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.247624074100511</v>
+        <v>-8.546928327113982</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1435470401050472</v>
+        <v>-0.2632687413104353</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.729182709096863</v>
+        <v>-2.028486962110333</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.118349388390787</v>
+        <v>1.938766836582705</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.064577224836115</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.115348600469623</v>
+        <v>-8.414652853483094</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.09526936390566521</v>
+        <v>-0.3016403408708701</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.596907235465976</v>
+        <v>-1.896211488479447</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.193082159316346</v>
+        <v>1.926850331748447</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.067392285523752</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.924748925796471</v>
+        <v>-8.224053178809941</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.01621443334876727</v>
+        <v>-0.2225854103139722</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.406307560792823</v>
+        <v>-1.705611813806294</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.310257024807874</v>
+        <v>2.044025197239976</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.08029862674741</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.67574912711289</v>
+        <v>-7.97505338012636</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.09629182734832398</v>
+        <v>-0.1100791496168809</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.406307560792823</v>
+        <v>-1.705611813806294</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.323163366031533</v>
+        <v>2.056931538463634</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.952322697148191</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.781339116885994</v>
+        <v>-8.080643369899464</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.07392009816013667</v>
+        <v>-0.2802910751253416</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.511897550565928</v>
+        <v>-1.811201803579398</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.131833442568452</v>
+        <v>1.865601615000553</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.000867039025278</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.800074019004591</v>
+        <v>-8.099378272018061</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03286971713048903</v>
+        <v>-0.2392406940956944</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.517493560226059</v>
+        <v>-1.816797813239529</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.177020178649459</v>
+        <v>1.91078835108156</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.88098811633711</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.652133977596992</v>
+        <v>-7.951438230610462</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.09357262325561688</v>
+        <v>-0.2999436002208222</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.497172644317502</v>
+        <v>-1.796476897330972</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.069333805506427</v>
+        <v>1.803101977938527</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.872274130083632</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.599164455343003</v>
+        <v>-7.898468708356473</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08109880060749974</v>
+        <v>-0.2874697775727046</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.444203122063513</v>
+        <v>-1.743507375076983</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.092401532605342</v>
+        <v>1.826169705037442</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.865313517988539</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.555616048572313</v>
+        <v>-7.854920301585783</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07064004999431672</v>
+        <v>-0.2770110269595216</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.444203122063513</v>
+        <v>-1.743507375076983</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.085440920510249</v>
+        <v>1.819209092942349</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.879775872369682</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.313467655118455</v>
+        <v>-7.612771908131925</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04068166176836963</v>
+        <v>-0.1656893151968353</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.444203122063513</v>
+        <v>-1.743507375076983</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.099903274891392</v>
+        <v>1.833671447323492</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.874307992828877</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.205208517995933</v>
+        <v>-7.504512771009403</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07851743707657333</v>
+        <v>-0.1278535398886316</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.444203122063513</v>
+        <v>-1.743507375076983</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.094435395350587</v>
+        <v>1.828203567782687</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.871806086839454</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.081917383178802</v>
+        <v>-7.381221636192272</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1253319850140024</v>
+        <v>-0.08103899195120245</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.320911987246382</v>
+        <v>-1.620216240259853</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.165908170251442</v>
+        <v>1.899676342683542</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.879507065076779</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.060768184275359</v>
+        <v>-7.360072437288829</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1414926428127052</v>
+        <v>-0.06487833415250011</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.299762788342939</v>
+        <v>-1.599067041356409</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.186298667830833</v>
+        <v>1.920066840262934</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.87528777342383</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.817002742291915</v>
+        <v>-7.116306995305385</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2347795279531337</v>
+        <v>0.02840855098792838</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.299762788342939</v>
+        <v>-1.599067041356409</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.182079376177884</v>
+        <v>1.915847548609984</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.877412087343846</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.71523992201462</v>
+        <v>-7.01454417502809</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2776089699840676</v>
+        <v>0.07123799301886224</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.28654371995051</v>
+        <v>-1.585847972963981</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.192135131133357</v>
+        <v>1.925903303565458</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.870154162327548</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.465389528065545</v>
+        <v>-6.764693781079015</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3702912025473997</v>
+        <v>0.1639202255821943</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.28654371995051</v>
+        <v>-1.585847972963981</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.184877206117059</v>
+        <v>1.91864537854916</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.873753285848196</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.289497435598113</v>
+        <v>-6.588801688611582</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4442471630550209</v>
+        <v>0.2378761860898164</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.28654371995051</v>
+        <v>-1.585847972963981</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.188476329637708</v>
+        <v>1.922244502069808</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.88708079190275</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.11805097257565</v>
+        <v>-6.417355225589119</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5261532543185603</v>
+        <v>0.3197822773533554</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.115097256928047</v>
+        <v>-1.414401509941517</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.30467171350574</v>
+        <v>2.03843988593784</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.886101269519047</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.893017972906827</v>
+        <v>-6.192322225920296</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6151869318023864</v>
+        <v>0.4088159548371815</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.890064257259224</v>
+        <v>-1.189368510272694</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.43871199092333</v>
+        <v>2.172480163355431</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.890796070573364</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.829382230672892</v>
+        <v>-6.128686483686361</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6453360297502773</v>
+        <v>0.4389650527850724</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8264285150252895</v>
+        <v>-1.12573276803876</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.481588237318008</v>
+        <v>2.215356409750109</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.87199032935716</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.785620049367051</v>
+        <v>-6.08492430238052</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6440351610564097</v>
+        <v>0.4376641840912048</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8264285150252895</v>
+        <v>-1.12573276803876</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.462782496101804</v>
+        <v>2.196550668533904</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.873733405982037</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.54518955256219</v>
+        <v>-5.844493805575659</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.741950436403231</v>
+        <v>0.5355794594380265</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5859980182204292</v>
+        <v>-0.8853022712338996</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.608783870809597</v>
+        <v>2.342552043241698</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.877662719816858</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.472946984390996</v>
+        <v>-5.772251237404465</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7747767775065291</v>
+        <v>0.5684058005413246</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5859980182204292</v>
+        <v>-0.8853022712338996</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.612713184644417</v>
+        <v>2.346481357076518</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.878341303734198</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.419948662109608</v>
+        <v>-5.719252915123077</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7966546903364242</v>
+        <v>0.5902837133712198</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5306617592184903</v>
+        <v>-0.8299660122319608</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.646593523962921</v>
+        <v>2.380361696395021</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.875339374954191</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.311143776629881</v>
+        <v>-5.61044802964335</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8371747157483087</v>
+        <v>0.6308037387831038</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5306617592184903</v>
+        <v>-0.8299660122319608</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.643591595182914</v>
+        <v>2.377359767615015</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.876918411964805</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.09112297859287</v>
+        <v>-5.390427231606339</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9267620719737271</v>
+        <v>0.7203910950085222</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3894419141505101</v>
+        <v>-0.6887461671639805</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.729902539234317</v>
+        <v>2.463670711666417</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.892812594766629</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.958255289529593</v>
+        <v>-5.257559542543062</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9958033304008613</v>
+        <v>0.7894323534356564</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3894419141505101</v>
+        <v>-0.6887461671639805</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.74579672203614</v>
+        <v>2.479564894468241</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.89395843920693</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.838082206165094</v>
+        <v>-5.137386459178563</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.045018408186963</v>
+        <v>0.8386474312217578</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2692688307860112</v>
+        <v>-0.5685730837994816</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.819046416495141</v>
+        <v>2.552814588927242</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.90404654176837</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.693410061065356</v>
+        <v>-4.992714314078825</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.112975368788298</v>
+        <v>0.9066043918230928</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1245966856862737</v>
+        <v>-0.4239009386997442</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.915937806116423</v>
+        <v>2.649705978548524</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.890084033169796</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.753284888423049</v>
+        <v>-5.052589141436518</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.075062929246646</v>
+        <v>0.8686919522814418</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1844715130439659</v>
+        <v>-0.4837757660574363</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.866050401103234</v>
+        <v>2.599818573535335</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>2.912484526492362</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.66648539064404</v>
+        <v>-4.965789643657509</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.132183221680816</v>
+        <v>0.9258122447156114</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1844715130439659</v>
+        <v>-0.4837757660574363</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.8884508944258</v>
+        <v>2.622219066857901</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>2.912556927865774</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.668955097105846</v>
+        <v>-4.968259350119315</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.131267740469506</v>
+        <v>0.9248967635043013</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.186941219505772</v>
+        <v>-0.4862454725192424</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.887041471922128</v>
+        <v>2.620809644354229</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>2.923563850340476</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.737325283429856</v>
+        <v>-5.036629536443325</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.114926588414604</v>
+        <v>0.9085556114493993</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1776655204695571</v>
+        <v>-0.4769697734830275</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.90361381381856</v>
+        <v>2.63738198625066</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>2.914000558972368</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.84586346434599</v>
+        <v>-5.145167717359459</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.061948024680042</v>
+        <v>0.8555770477148368</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1776655204695571</v>
+        <v>-0.4769697734830275</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.894050522450451</v>
+        <v>2.627818694882551</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.738710124012754</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.876856623674695</v>
+        <v>-5.176160876688164</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8742603259889463</v>
+        <v>0.6678893490237416</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1776655204695571</v>
+        <v>-0.4769697734830275</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.718760087490838</v>
+        <v>2.452528259922938</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.743277356004542</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.701382363882226</v>
+        <v>-5.000686616895695</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9490172618977217</v>
+        <v>0.7426462849325168</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1776655204695571</v>
+        <v>-0.4769697734830275</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.723327319482626</v>
+        <v>2.457095491914726</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.719019384765749</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.812318616523475</v>
+        <v>-5.111622869536944</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8803847896024291</v>
+        <v>0.6740138126372242</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1776655204695571</v>
+        <v>-0.4769697734830275</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.699069348243833</v>
+        <v>2.432837520675933</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.722150769985655</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.820600690668534</v>
+        <v>-5.119904943682003</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8802033451643112</v>
+        <v>0.6738323681991063</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1859475946146155</v>
+        <v>-0.4852518476280859</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.697231488976703</v>
+        <v>2.430999661408804</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.732323156417787</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.76074807146481</v>
+        <v>-5.06005232447828</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.914316779277933</v>
+        <v>0.7079458023127283</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1859475946146155</v>
+        <v>-0.4852518476280859</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.707403875408835</v>
+        <v>2.441172047840936</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.727269426991648</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.674504608438433</v>
+        <v>-4.973808861451902</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9437604350623443</v>
+        <v>0.7373894580971396</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1859475946146155</v>
+        <v>-0.4852518476280859</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.702350145982696</v>
+        <v>2.436118318414796</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.719045202436173</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.719811427837413</v>
+        <v>-5.019115680850882</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.917413482747278</v>
+        <v>0.7110425057820731</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2267577576238463</v>
+        <v>-0.5260620106373166</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.669639823621683</v>
+        <v>2.403407996053784</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.719597075469275</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.748844532539714</v>
+        <v>-5.048148785553183</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.906352113899459</v>
+        <v>0.6999811369342543</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2267577576238463</v>
+        <v>-0.5260620106373166</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.670191696654785</v>
+        <v>2.403959869086885</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.64886976736064</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.656034051088854</v>
+        <v>-4.955338304102323</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8727489983711685</v>
+        <v>0.6663780214059638</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1339472761729869</v>
+        <v>-0.4332515291864573</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.655150677416666</v>
+        <v>2.388918849848766</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.650743243285241</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.700423520418282</v>
+        <v>-4.999727773431751</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8568666865639984</v>
+        <v>0.6504957095987935</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1783367455024146</v>
+        <v>-0.4776409985158849</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.63039047174361</v>
+        <v>2.36415864417571</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.645818951796964</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.587752302182031</v>
+        <v>-4.887056555195501</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8970108823702214</v>
+        <v>0.6906399054050167</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.06566552726616437</v>
+        <v>-0.3649697802796347</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.693068911197083</v>
+        <v>2.426837083629183</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.651310247627631</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.475375300999358</v>
+        <v>-4.774679554012828</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9474529786739578</v>
+        <v>0.7410820017087532</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.06566552726616437</v>
+        <v>-0.3649697802796347</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.69856020702775</v>
+        <v>2.432328379459851</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.66280744939617</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.673609869886089</v>
+        <v>-4.972914122899558</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8796563528878045</v>
+        <v>0.6732853759225998</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2639000961528949</v>
+        <v>-0.5632043491663653</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.591116667464251</v>
+        <v>2.324884839896352</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.501163169396824</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.756611150911368</v>
+        <v>-5.055915403924837</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6848115604783462</v>
+        <v>0.4784405835131413</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2824709806800687</v>
+        <v>-0.5817752336935391</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.4183298567486</v>
+        <v>2.152098029180701</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.621312830116029</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.865225229354699</v>
+        <v>-5.164529482368168</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7615155898202195</v>
+        <v>0.5551446128550146</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2824709806800687</v>
+        <v>-0.5817752336935391</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.538479517467806</v>
+        <v>2.272247689899906</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.635825856218352</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.951823812335802</v>
+        <v>-5.251128065349271</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7413891827301013</v>
+        <v>0.5350182057648967</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2824709806800687</v>
+        <v>-0.5817752336935391</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.552992543570129</v>
+        <v>2.286760716002229</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.633245297560721</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.913440149777651</v>
+        <v>-5.21274440279112</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7541620890957303</v>
+        <v>0.5477911121305254</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2440873181219175</v>
+        <v>-0.5433915711353879</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.573442182447388</v>
+        <v>2.307210354879488</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.629974326406023</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.736323819742485</v>
+        <v>-5.035628072755954</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8217376499550988</v>
+        <v>0.6153666729898939</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2440873181219175</v>
+        <v>-0.5433915711353879</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.57017121129269</v>
+        <v>2.30393938372479</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.630657718167936</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.781416064576031</v>
+        <v>-5.0807203175895</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8043841437835937</v>
+        <v>0.5980131668183888</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3059833612913073</v>
+        <v>-0.6052876143047777</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.533716977152969</v>
+        <v>2.26748514958507</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.62444469347435</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.602040643337263</v>
+        <v>-4.901344896350732</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8699212875855151</v>
+        <v>0.6635503106203102</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1492066031205886</v>
+        <v>-0.4485108561340591</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.621570007361814</v>
+        <v>2.355338179793915</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.60525214880594</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.647054856857869</v>
+        <v>-4.946359109871338</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8327230575088624</v>
+        <v>0.6263520805436578</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1795554984351933</v>
+        <v>-0.4788597514486637</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.584168125504642</v>
+        <v>2.317936297936742</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.610943711144886</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.914059367130304</v>
+        <v>-5.213363620143773</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7316128157388342</v>
+        <v>0.5252418387736295</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3739185364781418</v>
+        <v>-0.6732227894916123</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.473241865017818</v>
+        <v>2.207010037449919</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.610147633041387</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.015257148567477</v>
+        <v>-5.314561401580946</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6903376250604665</v>
+        <v>0.4839666480952616</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.442327350023461</v>
+        <v>-0.7416316030369314</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.431400498787128</v>
+        <v>2.165168671219229</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.607747594595704</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.982781562396704</v>
+        <v>-5.282085815410174</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7009278210830923</v>
+        <v>0.4945568441178874</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.442327350023461</v>
+        <v>-0.7416316030369314</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.429000460341445</v>
+        <v>2.162768632773545</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.604272313803949</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.963743434689407</v>
+        <v>-5.263047687702876</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.705067791374256</v>
+        <v>0.4986968144090511</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5005109613546556</v>
+        <v>-0.799815214368126</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.390615012750973</v>
+        <v>2.124383185183074</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.78185418274263</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.994870065840026</v>
+        <v>-5.294174318853495</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8701990078526891</v>
+        <v>0.6638280308874842</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5005109613546556</v>
+        <v>-0.799815214368126</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.568196881689654</v>
+        <v>2.301965054121754</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.782687511728763</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.047190446440817</v>
+        <v>-5.346494699454286</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8501041845985062</v>
+        <v>0.6437332076333013</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4655641013457834</v>
+        <v>-0.7648683543592538</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.589998326681111</v>
+        <v>2.323766499113211</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.788696042125689</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.067447744969775</v>
+        <v>-5.366751997983244</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8480097955838488</v>
+        <v>0.6416388186186439</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4655641013457834</v>
+        <v>-0.7648683543592538</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.596006857078037</v>
+        <v>2.329775029510137</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.867848689917711</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.919704774734773</v>
+        <v>-5.219009027748242</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9862596314698717</v>
+        <v>0.779888654504667</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2977567441109003</v>
+        <v>-0.5970609971243707</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.775843919210988</v>
+        <v>2.509612091643089</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.870642311449192</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.021719457265994</v>
+        <v>-5.321023710279463</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9482473799888642</v>
+        <v>0.7418764030236593</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2977567441109003</v>
+        <v>-0.5970609971243707</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.778637540742469</v>
+        <v>2.51240571317457</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.87130465984085</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.01556675121321</v>
+        <v>-5.314871004226679</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9513708108016363</v>
+        <v>0.7449998338364314</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.291604038058116</v>
+        <v>-0.5909082910715864</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.782991512765798</v>
+        <v>2.516759685197899</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.870385136580961</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.032376049363712</v>
+        <v>-5.331680302377181</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9437275682815458</v>
+        <v>0.7373565913163409</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3084133362086176</v>
+        <v>-0.6077175892220881</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.771986410615607</v>
+        <v>2.505754583047708</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.936720690377781</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.970078050587589</v>
+        <v>-5.269382303601058</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.034982321588816</v>
+        <v>0.828611344623611</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3084133362086176</v>
+        <v>-0.6077175892220881</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.838321964412428</v>
+        <v>2.572090136844529</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.645301562767179</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.768287852922431</v>
+        <v>-5.0675921059359</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8242792730442767</v>
+        <v>0.6179082960790718</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1103951440394632</v>
+        <v>-0.4096993970529337</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.665713752103319</v>
+        <v>2.39948192453542</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.715591795089355</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.708397171279838</v>
+        <v>-5.007701424293307</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9185257780234894</v>
+        <v>0.7121548010582845</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.05050446239686973</v>
+        <v>-0.3498087154103402</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.77193839341105</v>
+        <v>2.505706565843151</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.730219531205398</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.806137715904812</v>
+        <v>-5.105441968918282</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8940572962895432</v>
+        <v>0.6876863193243383</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.06639374052984992</v>
+        <v>-0.3656979935433204</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.777032562647306</v>
+        <v>2.510800735079406</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.72875551203007</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.982475476027742</v>
+        <v>-5.281779729041211</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8220581730650431</v>
+        <v>0.6156871960998385</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2427315006527793</v>
+        <v>-0.5420357536662498</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.66976588739822</v>
+        <v>2.40353405983032</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.727247130069999</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.910929153250865</v>
+        <v>-5.210233406264334</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8491683202157225</v>
+        <v>0.6427973432505176</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2427315006527793</v>
+        <v>-0.5420357536662498</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.668257505438148</v>
+        <v>2.402025677870249</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.727109997505435</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.866556021612296</v>
+        <v>-5.165860274625765</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8667804403065862</v>
+        <v>0.6604094633413813</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1983583690142107</v>
+        <v>-0.4976626220276812</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.694744251856726</v>
+        <v>2.428512424288826</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.727109997505435</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.858602051317524</v>
+        <v>-5.157906304330993</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8699620284244951</v>
+        <v>0.6635910514592904</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1983583690142107</v>
+        <v>-0.4976626220276812</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.694744251856726</v>
+        <v>2.428512424288826</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.733491754533239</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.810946320756468</v>
+        <v>-5.110250573769937</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8954060776767221</v>
+        <v>0.6890351007115174</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1507026384531551</v>
+        <v>-0.4500068914666255</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.729719447221164</v>
+        <v>2.463487619653264</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.738384127907964</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.683262010962172</v>
+        <v>-4.982566263975641</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9513721749691655</v>
+        <v>0.7450011980039606</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.02301832865885861</v>
+        <v>-0.3223225816723291</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.811222406472466</v>
+        <v>2.544990578904567</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.725138800383836</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.74392860136456</v>
+        <v>-5.043232854378029</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9138602112840821</v>
+        <v>0.7074892343188774</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1047166453773923</v>
+        <v>-0.4040208983908627</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.748958088917218</v>
+        <v>2.482726261349319</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.729236502994465</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.678934741430915</v>
+        <v>-4.978238994444384</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.943955457868169</v>
+        <v>0.7375844809029641</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.07788603077323691</v>
+        <v>-0.3771902837867074</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.76915416029034</v>
+        <v>2.502922332722441</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.733397442625543</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.779693377187913</v>
+        <v>-5.078997630201382</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9078129431964477</v>
+        <v>0.701441966231243</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1667115995002423</v>
+        <v>-0.4660158525137128</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.720019758685215</v>
+        <v>2.453787931117315</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.73927704515338</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.735490540102012</v>
+        <v>-5.034794793115482</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.931373680558645</v>
+        <v>0.7250027035934403</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1225087624143419</v>
+        <v>-0.4218130154278124</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.752421063464592</v>
+        <v>2.486189235896693</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.737687045622628</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.772469567765455</v>
+        <v>-5.071773820778924</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9149920699625156</v>
+        <v>0.7086210929973107</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.08553486062301136</v>
+        <v>-0.3848391136364818</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.773015405008638</v>
+        <v>2.506783577440739</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.788934810805667</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.792527646630296</v>
+        <v>-5.091831899643765</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9582166035996189</v>
+        <v>0.751845626634414</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.08553486062301136</v>
+        <v>-0.3848391136364818</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.824263170191678</v>
+        <v>2.558031342623778</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.78737551539992</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.752596973452405</v>
+        <v>-5.051901226465874</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9726295774650282</v>
+        <v>0.7662586004998233</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.04560418744512101</v>
+        <v>-0.3449084404585915</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.846662278692665</v>
+        <v>2.580430451124766</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232398</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.78232374363819</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.712126625889701</v>
+        <v>-5.01143087890317</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9837659447283802</v>
+        <v>0.7773949677631755</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.005133839882416058</v>
+        <v>-0.3044380928958865</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.865892715468558</v>
+        <v>2.599660887900659</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.799511147730895</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.646902444762495</v>
+        <v>-4.946206697775964</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.027043021271967</v>
+        <v>0.8206720443067623</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.06009034124478957</v>
+        <v>-0.2392139117686809</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.922214628237587</v>
+        <v>2.655982800669687</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.795472120030176</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.697396735119551</v>
+        <v>-4.99670098813302</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.002806277428425</v>
+        <v>0.7964353004632203</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.01506960411871533</v>
+        <v>-0.2842346488947551</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.891163158261222</v>
+        <v>2.624931330693323</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.796728912361416</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.71750839115426</v>
+        <v>-5.016812644167729</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9960184073457821</v>
+        <v>0.7896474303805774</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.02609694911613453</v>
+        <v>-0.2732073038973359</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.899036357590914</v>
+        <v>2.632804530023015</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>2.957286683382627</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.815188970426906</v>
+        <v>-5.114493223440375</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.117503946657934</v>
+        <v>0.9111329696927295</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.08460624622405427</v>
+        <v>-0.3839104992375247</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.993172211408011</v>
+        <v>2.726940383840112</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.077399592600444</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.791397401820763</v>
+        <v>-5.090701654834232</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.247133483318209</v>
+        <v>1.040762506353004</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.06081467761791198</v>
+        <v>-0.3601189306313825</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.127560061789514</v>
+        <v>2.861328234221615</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.069107568614303</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.828151820382486</v>
+        <v>-5.127456073395955</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.224139691907379</v>
+        <v>1.017768714942174</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.06081467761791198</v>
+        <v>-0.3601189306313825</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.119268037803373</v>
+        <v>2.853036210235474</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.844269268987958</v>
+        <v>3.468504336965036</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.067300764198083</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.965872922371298</v>
+        <v>-5.221877314695589</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.167244446695633</v>
+        <v>0.9781934140060997</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.06433675575433379</v>
+        <v>-0.211185523813981</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.1925520934105</v>
+        <v>2.940589449909694</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>453.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-683.8%</t>
+          <t>-654.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-41.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>-93.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.4%</t>
+          <t>-258.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.3%</t>
+          <t>-161.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-245.1%</t>
+          <t>-231.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.0%</t>
+          <t>-135.3%</t>
         </is>
       </c>
     </row>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.29530561288686</v>
+        <v>-10.16460805404204</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9583043212353859</v>
+        <v>-0.906025297697461</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.500086432052085</v>
+        <v>-2.369388873207274</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.660122489001854</v>
+        <v>1.73854102430874</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.4704300302734</v>
+        <v>-10.33973247142859</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.013798867442486</v>
+        <v>-0.9615198439045614</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.675210849438629</v>
+        <v>-2.544513290593818</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.569603059317444</v>
+        <v>1.64802159462433</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70488212428789</v>
+        <v>-10.57418456544308</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.114798869949878</v>
+        <v>-1.062519846411953</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.675210849438629</v>
+        <v>-2.544513290593818</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.562383894415848</v>
+        <v>1.640802429722734</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.99268596882513</v>
+        <v>-10.86198840998032</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.23659259853875</v>
+        <v>-1.184313575000826</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.963014693975867</v>
+        <v>-2.832317135131056</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.383029396919529</v>
+        <v>1.461447932226415</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.04547212442546</v>
+        <v>-10.91477456558064</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.256591270940325</v>
+        <v>-1.2043122474024</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.058690180558264</v>
+        <v>-2.927992621713453</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.326739894808647</v>
+        <v>1.405158430115533</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.17150891779374</v>
+        <v>-11.04081135894893</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.304312259658526</v>
+        <v>-1.252033236120601</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.033438557748521</v>
+        <v>-2.902740998903711</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.344584597123607</v>
+        <v>1.423003132430493</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.11949340382493</v>
+        <v>-10.98879584498012</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.279515718384599</v>
+        <v>-1.227236694846675</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.033438557748521</v>
+        <v>-2.902740998903711</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.348574932810008</v>
+        <v>1.426993468116894</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.26116524554905</v>
+        <v>-11.13046768670424</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.337659681972989</v>
+        <v>-1.285380658435065</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.033438557748521</v>
+        <v>-2.902740998903711</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.347099705911266</v>
+        <v>1.425518241218153</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21157440112422</v>
+        <v>-11.08087684227941</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.302769934038183</v>
+        <v>-1.250490910500258</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.983847713323688</v>
+        <v>-2.853150154478877</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.391907622731039</v>
+        <v>1.470326158037925</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.19876700811944</v>
+        <v>-11.06806944927463</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.310698110482956</v>
+        <v>-1.258419086945032</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.032703488332589</v>
+        <v>-2.902005929487778</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.349543024079015</v>
+        <v>1.427961559385902</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.97292185540003</v>
+        <v>-10.84222429655522</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.210780976358983</v>
+        <v>-1.158501952821058</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.990776812745425</v>
+        <v>-2.860079253900614</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.384278102467522</v>
+        <v>1.462696637774409</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.84834319906244</v>
+        <v>-10.71764564021763</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.159810369267887</v>
+        <v>-1.107531345729962</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.990776812745425</v>
+        <v>-2.860079253900614</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.385417247023581</v>
+        <v>1.463835782330468</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.90123848710673</v>
+        <v>-10.77054092826191</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.178334710323495</v>
+        <v>-1.12605568678557</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.985821466656979</v>
+        <v>-2.855123907812168</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.391024228838756</v>
+        <v>1.469442764145643</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.82910531181884</v>
+        <v>-10.69840775297403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.143747735969705</v>
+        <v>-1.091468712431781</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.985821466656979</v>
+        <v>-2.855123907812168</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.396757933077393</v>
+        <v>1.475176468384279</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.7577389192092</v>
+        <v>-10.62704136036439</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.124938441319712</v>
+        <v>-1.072659417781787</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.914455074047331</v>
+        <v>-2.78375751520252</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.429840506249316</v>
+        <v>1.508259041556203</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49390205200513</v>
+        <v>-10.36320449316032</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.029287175750991</v>
+        <v>-0.9770081522130662</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.914455074047331</v>
+        <v>-2.78375751520252</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.419957024936409</v>
+        <v>1.498375560243296</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.22666025113673</v>
+        <v>-10.09596269229192</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9242250159030063</v>
+        <v>-0.8719459923650814</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.914455074047331</v>
+        <v>-2.78375751520252</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.418122464437035</v>
+        <v>1.496540999743922</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12875321246024</v>
+        <v>-9.998055653615427</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8853625154058702</v>
+        <v>-0.8330834918679457</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.846469324186774</v>
+        <v>-2.715771765341963</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.458613599379908</v>
+        <v>1.537032134686795</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.10479967148428</v>
+        <v>-9.97410211263947</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8751125928699941</v>
+        <v>-0.8228335693320692</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.822515783210817</v>
+        <v>-2.691818224366006</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.473654230110977</v>
+        <v>1.552072765417863</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.840739733161485</v>
+        <v>-9.710042174316673</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.782748933702627</v>
+        <v>-0.7304699101647025</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.558455844888021</v>
+        <v>-2.42775828604321</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.618829876942902</v>
+        <v>1.697248412249788</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.133660109656647</v>
+        <v>-9.002962550811835</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.502704117960993</v>
+        <v>-0.4504250944230686</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.558455844888021</v>
+        <v>-2.42775828604321</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.616042843282601</v>
+        <v>1.694461378589488</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.093475811290457</v>
+        <v>-8.962778252445645</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4862867747266755</v>
+        <v>-0.434007751188751</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.51827154652183</v>
+        <v>-2.387573987677019</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.640497046190157</v>
+        <v>1.718915581497043</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.930075940351095</v>
+        <v>-8.799378381506283</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.421560005130174</v>
+        <v>-0.3692809815922491</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.354871675582467</v>
+        <v>-2.224174116737657</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.737903789974531</v>
+        <v>1.816322325281418</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.696594718121496</v>
+        <v>-8.565897159276684</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.320243087400482</v>
+        <v>-0.2679640638625571</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.121390453352869</v>
+        <v>-1.990692894508058</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.885916952150143</v>
+        <v>1.96433548745703</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.546928327113982</v>
+        <v>-8.41623076826917</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2632687413104353</v>
+        <v>-0.2109897177725104</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.028486962110333</v>
+        <v>-1.897789403265522</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.938766836582705</v>
+        <v>2.017185371889592</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.064577224836115</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.414652853483094</v>
+        <v>-8.283955294638282</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3016403408708701</v>
+        <v>-0.1627120415731285</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.896211488479447</v>
+        <v>-1.765513929634635</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.926850331748447</v>
+        <v>2.091918142815151</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.067392285523752</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.224053178809941</v>
+        <v>-8.093355619965129</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2225854103139722</v>
+        <v>-0.08365711101623052</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.705611813806294</v>
+        <v>-1.574914254961483</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.044025197239976</v>
+        <v>2.209093008306679</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.08029862674741</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.97505338012636</v>
+        <v>-7.844355821281548</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1100791496168809</v>
+        <v>0.02884914968086072</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.705611813806294</v>
+        <v>-1.574914254961483</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.056931538463634</v>
+        <v>2.221999349530338</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.952322697148191</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.080643369899464</v>
+        <v>-7.949945811054652</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2802910751253416</v>
+        <v>-0.1413627758275999</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.811201803579398</v>
+        <v>-1.680504244734587</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.865601615000553</v>
+        <v>2.030669426067257</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.000867039025278</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.099378272018061</v>
+        <v>-7.968680713173249</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2392406940956944</v>
+        <v>-0.1003123947979523</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.816797813239529</v>
+        <v>-1.686100254394718</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.91078835108156</v>
+        <v>2.075856162148265</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.88098811633711</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.951438230610462</v>
+        <v>-7.82074067176565</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2999436002208222</v>
+        <v>-0.1610153009230801</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.796476897330972</v>
+        <v>-1.665779338486161</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.803101977938527</v>
+        <v>1.968169789005231</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.872274130083632</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.898468708356473</v>
+        <v>-7.767771149511661</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2874697775727046</v>
+        <v>-0.148541478274963</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.743507375076983</v>
+        <v>-1.612809816232172</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.826169705037442</v>
+        <v>1.991237516104146</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.865313517988539</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.854920301585783</v>
+        <v>-7.724222742740971</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2770110269595216</v>
+        <v>-0.13808272766178</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.743507375076983</v>
+        <v>-1.612809816232172</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.819209092942349</v>
+        <v>1.984276904009053</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.879775872369682</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.612771908131925</v>
+        <v>-7.482074349287113</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1656893151968353</v>
+        <v>-0.02676101589909363</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.743507375076983</v>
+        <v>-1.612809816232172</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.833671447323492</v>
+        <v>1.998739258390196</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722815</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.874307992828877</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.504512771009403</v>
+        <v>-7.373815212164591</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1278535398886316</v>
+        <v>0.01107475940911007</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.743507375076983</v>
+        <v>-1.612809816232172</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.828203567782687</v>
+        <v>1.993271378849391</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.871806086839454</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.381221636192272</v>
+        <v>-7.25052407734746</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.08103899195120245</v>
+        <v>0.05788930734653919</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.620216240259853</v>
+        <v>-1.489518681415041</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.899676342683542</v>
+        <v>2.064744153750246</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.879507065076779</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.360072437288829</v>
+        <v>-7.229374878444017</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.06487833415250011</v>
+        <v>0.07404996514524198</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.599067041356409</v>
+        <v>-1.468369482511598</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.920066840262934</v>
+        <v>2.085134651329638</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.87528777342383</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.116306995305385</v>
+        <v>-6.985609436460573</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.02840855098792838</v>
+        <v>0.1673368502856705</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.599067041356409</v>
+        <v>-1.468369482511598</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.915847548609984</v>
+        <v>2.080915359676689</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.877412087343846</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.01454417502809</v>
+        <v>-6.883846616183278</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.07123799301886224</v>
+        <v>0.2101662923166043</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.585847972963981</v>
+        <v>-1.455150414119169</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.925903303565458</v>
+        <v>2.090971114632162</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.870154162327548</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.764693781079015</v>
+        <v>-6.633996222234203</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1639202255821943</v>
+        <v>0.3028485248799364</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.585847972963981</v>
+        <v>-1.455150414119169</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.91864537854916</v>
+        <v>2.083713189615864</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.873753285848196</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.588801688611582</v>
+        <v>-6.45810412976677</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2378761860898164</v>
+        <v>0.3768044853875581</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.585847972963981</v>
+        <v>-1.455150414119169</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.922244502069808</v>
+        <v>2.087312313136513</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.88708079190275</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.417355225589119</v>
+        <v>-6.286657666744307</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3197822773533554</v>
+        <v>0.458710576651097</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.414401509941517</v>
+        <v>-1.283703951096706</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.03843988593784</v>
+        <v>2.203507697004544</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.886101269519047</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.192322225920296</v>
+        <v>-6.061624667075484</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4088159548371815</v>
+        <v>0.5477442541349236</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.189368510272694</v>
+        <v>-1.058670951427883</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.172480163355431</v>
+        <v>2.337547974422135</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.890796070573364</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.128686483686361</v>
+        <v>-5.997988924841549</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4389650527850724</v>
+        <v>0.5778933520828144</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.12573276803876</v>
+        <v>-0.9950352091939484</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.215356409750109</v>
+        <v>2.380424220816813</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.87199032935716</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.08492430238052</v>
+        <v>-5.954226743535708</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4376641840912048</v>
+        <v>0.5765924833889469</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.12573276803876</v>
+        <v>-0.9950352091939484</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.196550668533904</v>
+        <v>2.361618479600609</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.873733405982037</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.844493805575659</v>
+        <v>-5.713796246730848</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5355794594380265</v>
+        <v>0.6745077587357682</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8853022712338996</v>
+        <v>-0.7546047123890881</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.342552043241698</v>
+        <v>2.507619854308402</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.877662719816858</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.772251237404465</v>
+        <v>-5.641553678559653</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5684058005413246</v>
+        <v>0.7073340998390663</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8853022712338996</v>
+        <v>-0.7546047123890881</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.346481357076518</v>
+        <v>2.511549168143222</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.878341303734198</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.719252915123077</v>
+        <v>-5.588555356278265</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5902837133712198</v>
+        <v>0.7292120126689614</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8299660122319608</v>
+        <v>-0.6992684533871493</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.380361696395021</v>
+        <v>2.545429507461725</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.875339374954191</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.61044802964335</v>
+        <v>-5.479750470798538</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6308037387831038</v>
+        <v>0.7697320380808459</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8299660122319608</v>
+        <v>-0.6992684533871493</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.377359767615015</v>
+        <v>2.542427578681719</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.876918411964805</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.390427231606339</v>
+        <v>-5.259729672761527</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7203910950085222</v>
+        <v>0.8593193943062643</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6887461671639805</v>
+        <v>-0.558048608319169</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.463670711666417</v>
+        <v>2.628738522733121</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.892812594766629</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.257559542543062</v>
+        <v>-5.12686198369825</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.7894323534356564</v>
+        <v>0.9283606527333985</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6887461671639805</v>
+        <v>-0.558048608319169</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.479564894468241</v>
+        <v>2.644632705534945</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.89395843920693</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.137386459178563</v>
+        <v>-5.006688900333751</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8386474312217578</v>
+        <v>0.9775757305194999</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5685730837994816</v>
+        <v>-0.4378755249546701</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.552814588927242</v>
+        <v>2.717882399993946</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.90404654176837</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.992714314078825</v>
+        <v>-4.862016755234014</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9066043918230928</v>
+        <v>1.045532691120835</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4239009386997442</v>
+        <v>-0.2932033798549327</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.649705978548524</v>
+        <v>2.814773789615228</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.890084033169796</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.052589141436518</v>
+        <v>-4.921891582591706</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.8686919522814418</v>
+        <v>1.007620251579184</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4837757660574363</v>
+        <v>-0.3530782072126248</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.599818573535335</v>
+        <v>2.764886384602039</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.912484526492362</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.965789643657509</v>
+        <v>-4.835092084812697</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9258122447156114</v>
+        <v>1.064740544013353</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4837757660574363</v>
+        <v>-0.3530782072126248</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.622219066857901</v>
+        <v>2.787286877924605</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.912556927865774</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.968259350119315</v>
+        <v>-4.837561791274503</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9248967635043013</v>
+        <v>1.063825062802043</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4862454725192424</v>
+        <v>-0.3555479136744309</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.620809644354229</v>
+        <v>2.785877455420933</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.923563850340476</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.036629536443325</v>
+        <v>-4.905931977598513</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9085556114493993</v>
+        <v>1.047483910747141</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4769697734830275</v>
+        <v>-0.346272214638216</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.63738198625066</v>
+        <v>2.802449797317364</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.914000558972368</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.145167717359459</v>
+        <v>-5.014470158514647</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8555770477148368</v>
+        <v>0.9945053470125789</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4769697734830275</v>
+        <v>-0.346272214638216</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.627818694882551</v>
+        <v>2.792886505949256</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.738710124012754</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.176160876688164</v>
+        <v>-5.045463317843352</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.6678893490237416</v>
+        <v>0.8068176483214833</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4769697734830275</v>
+        <v>-0.346272214638216</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.452528259922938</v>
+        <v>2.617596070989642</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.743277356004542</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.000686616895695</v>
+        <v>-4.869989058050884</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7426462849325168</v>
+        <v>0.8815745842302587</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4769697734830275</v>
+        <v>-0.346272214638216</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.457095491914726</v>
+        <v>2.62216330298143</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.719019384765749</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.111622869536944</v>
+        <v>-4.980925310692133</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.6740138126372242</v>
+        <v>0.8129421119349662</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4769697734830275</v>
+        <v>-0.346272214638216</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.432837520675933</v>
+        <v>2.597905331742637</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.722150769985655</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.119904943682003</v>
+        <v>-4.989207384837191</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6738323681991063</v>
+        <v>0.8127606674968484</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4852518476280859</v>
+        <v>-0.3545542887832744</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.430999661408804</v>
+        <v>2.596067472475508</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.732323156417787</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.06005232447828</v>
+        <v>-4.929354765633468</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7079458023127283</v>
+        <v>0.8468741016104699</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4852518476280859</v>
+        <v>-0.3545542887832744</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.441172047840936</v>
+        <v>2.60623985890764</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.727269426991648</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.973808861451902</v>
+        <v>-4.84311130260709</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7373894580971396</v>
+        <v>0.8763177573948815</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4852518476280859</v>
+        <v>-0.3545542887832744</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.436118318414796</v>
+        <v>2.6011861294815</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.719045202436173</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.019115680850882</v>
+        <v>-4.88841812200607</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7110425057820731</v>
+        <v>0.8499708050798152</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5260620106373166</v>
+        <v>-0.3953644517925052</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.403407996053784</v>
+        <v>2.568475807120488</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.719597075469275</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.048148785553183</v>
+        <v>-4.855068751789151</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.6999811369342543</v>
+        <v>0.8638624261996841</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5260620106373166</v>
+        <v>-0.3953644517925052</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.403959869086885</v>
+        <v>2.569027680153589</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.64886976736064</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.955338304102323</v>
+        <v>-4.762258270338291</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6663780214059638</v>
+        <v>0.8302593106713936</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4332515291864573</v>
+        <v>-0.3025539703416458</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.388918849848766</v>
+        <v>2.55398666091547</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.650743243285241</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.999727773431751</v>
+        <v>-4.806647739667719</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6504957095987935</v>
+        <v>0.8143769988642235</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4776409985158849</v>
+        <v>-0.3469434396710735</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.36415864417571</v>
+        <v>2.529226455242414</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.645818951796964</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.887056555195501</v>
+        <v>-4.693976521431469</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6906399054050167</v>
+        <v>0.8545211946704465</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3649697802796347</v>
+        <v>-0.2342722214348233</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.426837083629183</v>
+        <v>2.591904894695888</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.651310247627631</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.774679554012828</v>
+        <v>-4.581599520248796</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7410820017087532</v>
+        <v>0.9049632909741829</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3649697802796347</v>
+        <v>-0.2342722214348233</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.432328379459851</v>
+        <v>2.597396190526555</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.66280744939617</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.972914122899558</v>
+        <v>-4.779834089135527</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6732853759225998</v>
+        <v>0.8371666651880296</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5632043491663653</v>
+        <v>-0.4325067903215539</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.324884839896352</v>
+        <v>2.489952650963056</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.501163169396824</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.055915403924837</v>
+        <v>-4.862835370160806</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4784405835131413</v>
+        <v>0.6423218727785713</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5817752336935391</v>
+        <v>-0.4510776748487276</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.152098029180701</v>
+        <v>2.317165840247405</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.621312830116029</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.164529482368168</v>
+        <v>-4.971449448604137</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5551446128550146</v>
+        <v>0.7190259021204446</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5817752336935391</v>
+        <v>-0.4510776748487276</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.272247689899906</v>
+        <v>2.43731550096661</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.635825856218352</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.251128065349271</v>
+        <v>-5.05804803158524</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5350182057648967</v>
+        <v>0.6988994950303264</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5817752336935391</v>
+        <v>-0.4510776748487276</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.286760716002229</v>
+        <v>2.451828527068933</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.633245297560721</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.21274440279112</v>
+        <v>-5.019664369027089</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5477911121305254</v>
+        <v>0.7116724013959557</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5433915711353879</v>
+        <v>-0.4126940122905765</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.307210354879488</v>
+        <v>2.472278165946193</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.629974326406023</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.035628072755954</v>
+        <v>-4.842548038991922</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6153666729898939</v>
+        <v>0.7792479622553239</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5433915711353879</v>
+        <v>-0.4126940122905765</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.30393938372479</v>
+        <v>2.469007194791494</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.630657718167936</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.0807203175895</v>
+        <v>-4.887640283825468</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5980131668183888</v>
+        <v>0.7618944560838186</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6052876143047777</v>
+        <v>-0.4745900554599662</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.26748514958507</v>
+        <v>2.432552960651774</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.62444469347435</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.901344896350732</v>
+        <v>-4.708264862586701</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6635503106203102</v>
+        <v>0.82743159988574</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4485108561340591</v>
+        <v>-0.3178132972892476</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.355338179793915</v>
+        <v>2.520405990860619</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.60525214880594</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.946359109871338</v>
+        <v>-4.753279076107306</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6263520805436578</v>
+        <v>0.7902333698090875</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4788597514486637</v>
+        <v>-0.3481621926038522</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.317936297936742</v>
+        <v>2.483004109003446</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.610943711144886</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.213363620143773</v>
+        <v>-5.020283586379741</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5252418387736295</v>
+        <v>0.6891231280390593</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6732227894916123</v>
+        <v>-0.5425252306468007</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.207010037449919</v>
+        <v>2.372077848516623</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.610147633041387</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.314561401580946</v>
+        <v>-5.121481367816914</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4839666480952616</v>
+        <v>0.6478479373606918</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7416316030369314</v>
+        <v>-0.6109340441921198</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.165168671219229</v>
+        <v>2.330236482285933</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.607747594595704</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.282085815410174</v>
+        <v>-5.089005781646142</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4945568441178874</v>
+        <v>0.6584381333833171</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7416316030369314</v>
+        <v>-0.6109340441921198</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.162768632773545</v>
+        <v>2.327836443840249</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.604272313803949</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.263047687702876</v>
+        <v>-5.069967653938845</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4986968144090511</v>
+        <v>0.6625781036744809</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.799815214368126</v>
+        <v>-0.6691176555233144</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.124383185183074</v>
+        <v>2.289450996249778</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.78185418274263</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.294174318853495</v>
+        <v>-5.101094285089463</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6638280308874842</v>
+        <v>0.8277093201529144</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.799815214368126</v>
+        <v>-0.6691176555233144</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.301965054121754</v>
+        <v>2.467032865188458</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.782687511728763</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.346494699454286</v>
+        <v>-5.153414665690255</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6437332076333013</v>
+        <v>0.8076144968987311</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7648683543592538</v>
+        <v>-0.6341707955144422</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.323766499113211</v>
+        <v>2.488834310179915</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.788696042125689</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.366751997983244</v>
+        <v>-5.173671964219213</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6416388186186439</v>
+        <v>0.8055201078840737</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7648683543592538</v>
+        <v>-0.6341707955144422</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.329775029510137</v>
+        <v>2.494842840576841</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.867848689917711</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.219009027748242</v>
+        <v>-5.02592899398421</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.779888654504667</v>
+        <v>0.9437699437700968</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5970609971243707</v>
+        <v>-0.4663634382795591</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.509612091643089</v>
+        <v>2.674679902709793</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.870642311449192</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.321023710279463</v>
+        <v>-5.127943676515431</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7418764030236593</v>
+        <v>0.9057576922890891</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5970609971243707</v>
+        <v>-0.4663634382795591</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.51240571317457</v>
+        <v>2.677473524241274</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.87130465984085</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.314871004226679</v>
+        <v>-5.121790970462647</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7449998338364314</v>
+        <v>0.9088811231018612</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5909082910715864</v>
+        <v>-0.4602107322267748</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.516759685197899</v>
+        <v>2.681827496264603</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.870385136580961</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.331680302377181</v>
+        <v>-5.138600268613149</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7373565913163409</v>
+        <v>0.9012378805817707</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6077175892220881</v>
+        <v>-0.4770200303772764</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.505754583047708</v>
+        <v>2.670822394114412</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.936720690377781</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.269382303601058</v>
+        <v>-5.076302269837027</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.828611344623611</v>
+        <v>0.9924926338890407</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6077175892220881</v>
+        <v>-0.4770200303772764</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.572090136844529</v>
+        <v>2.737157947911233</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.645301562767179</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.0675921059359</v>
+        <v>-4.874512072171869</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6179082960790718</v>
+        <v>0.7817895853445018</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4096993970529337</v>
+        <v>-0.279001838208122</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.39948192453542</v>
+        <v>2.564549735602124</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.715591795089355</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.007701424293307</v>
+        <v>-4.814621390529275</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7121548010582845</v>
+        <v>0.8760360903237143</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3498087154103402</v>
+        <v>-0.2191111565655285</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.505706565843151</v>
+        <v>2.670774376909855</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.730219531205398</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.105441968918282</v>
+        <v>-4.91236193515425</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6876863193243383</v>
+        <v>0.8515676085897683</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3656979935433204</v>
+        <v>-0.2350004346985087</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.510800735079406</v>
+        <v>2.67586854614611</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.72875551203007</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.281779729041211</v>
+        <v>-5.088699695277179</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6156871960998385</v>
+        <v>0.7795684853652682</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5420357536662498</v>
+        <v>-0.4113381948214381</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.40353405983032</v>
+        <v>2.568601870897024</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.727247130069999</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.210233406264334</v>
+        <v>-5.017153372500302</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6427973432505176</v>
+        <v>0.8066786325159474</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5420357536662498</v>
+        <v>-0.4113381948214381</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.402025677870249</v>
+        <v>2.567093488936953</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.727109997505435</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.165860274625765</v>
+        <v>-4.972780240861733</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6604094633413813</v>
+        <v>0.8242907526068113</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4976626220276812</v>
+        <v>-0.3669650631828695</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.428512424288826</v>
+        <v>2.59358023535553</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.727109997505435</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.157906304330993</v>
+        <v>-4.964826270566961</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6635910514592904</v>
+        <v>0.8274723407247202</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4976626220276812</v>
+        <v>-0.3669650631828695</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.428512424288826</v>
+        <v>2.59358023535553</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.733491754533239</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.110250573769937</v>
+        <v>-4.917170540005905</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6890351007115174</v>
+        <v>0.8529163899769472</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4500068914666255</v>
+        <v>-0.3193093326218139</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.463487619653264</v>
+        <v>2.628555430719969</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.738384127907964</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.982566263975641</v>
+        <v>-4.789486230211609</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7450011980039606</v>
+        <v>0.9088824872693904</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3223225816723291</v>
+        <v>-0.1916250228275174</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.544990578904567</v>
+        <v>2.710058389971271</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.725138800383836</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.043232854378029</v>
+        <v>-4.850152820613998</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7074892343188774</v>
+        <v>0.8713705235843072</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4040208983908627</v>
+        <v>-0.2733233395460511</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.482726261349319</v>
+        <v>2.647794072416023</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.729236502994465</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.978238994444384</v>
+        <v>-4.785158960680352</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7375844809029641</v>
+        <v>0.9014657701683939</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3771902837867074</v>
+        <v>-0.2464927249418957</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.502922332722441</v>
+        <v>2.667990143789145</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.733397442625543</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.078997630201382</v>
+        <v>-4.88591759643735</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.701441966231243</v>
+        <v>0.8653232554966728</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4660158525137128</v>
+        <v>-0.3353182936689011</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.453787931117315</v>
+        <v>2.61885574218402</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.73927704515338</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.034794793115482</v>
+        <v>-4.84171475935145</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7250027035934403</v>
+        <v>0.8888839928588701</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4218130154278124</v>
+        <v>-0.2911154565830007</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.486189235896693</v>
+        <v>2.651257046963397</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.737687045622628</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.071773820778924</v>
+        <v>-4.878693787014893</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7086210929973107</v>
+        <v>0.8725023822627405</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.3848391136364818</v>
+        <v>-0.2541415547916702</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.506783577440739</v>
+        <v>2.671851388507443</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.788934810805667</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.091831899643765</v>
+        <v>-4.898751865879733</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.751845626634414</v>
+        <v>0.915726915899844</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.3848391136364818</v>
+        <v>-0.2541415547916702</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.558031342623778</v>
+        <v>2.723099153690482</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.78737551539992</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.051901226465874</v>
+        <v>-4.858821192701843</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7662586004998233</v>
+        <v>0.9301398897652533</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.3449084404585915</v>
+        <v>-0.2142108816137798</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.580430451124766</v>
+        <v>2.74549826219147</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232398</v>
+        <v>3.864518876232396</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.78232374363819</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.01143087890317</v>
+        <v>-4.818350845139138</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7773949677631755</v>
+        <v>0.9412762570286053</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.3044380928958865</v>
+        <v>-0.1737405340510749</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.599660887900659</v>
+        <v>2.764728698967363</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.799511147730895</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.946206697775964</v>
+        <v>-4.753126664011933</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8206720443067623</v>
+        <v>0.9845533335721923</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.2392139117686809</v>
+        <v>-0.1085163529238692</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.655982800669687</v>
+        <v>2.821050611736391</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.795472120030176</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.99670098813302</v>
+        <v>-4.803620954368989</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7964353004632203</v>
+        <v>0.9603165897286501</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.2842346488947551</v>
+        <v>-0.1535370900499435</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.624931330693323</v>
+        <v>2.789999141760027</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.796728912361416</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.016812644167729</v>
+        <v>-4.823732610403697</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.7896474303805774</v>
+        <v>0.9535287196460072</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.2732073038973359</v>
+        <v>-0.1425097450525243</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.632804530023015</v>
+        <v>2.797872341089719</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.957286683382627</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.114493223440375</v>
+        <v>-4.921413189676343</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9111329696927295</v>
+        <v>1.075014258958159</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.3839104992375247</v>
+        <v>-0.2532129403927131</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.726940383840112</v>
+        <v>2.892008194906817</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.077399592600444</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.090701654834232</v>
+        <v>-4.897621621070201</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.040762506353004</v>
+        <v>1.204643795618434</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3601189306313825</v>
+        <v>-0.2294213717865708</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.861328234221615</v>
+        <v>3.026396045288319</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756014</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.069107568614303</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.127456073395955</v>
+        <v>-4.934376039631923</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.017768714942174</v>
+        <v>1.181650004207604</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.3601189306313825</v>
+        <v>-0.2294213717865708</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.853036210235474</v>
+        <v>3.018104021302178</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.468504336965036</v>
+        <v>3.827945581456508</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.067300764198083</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-5.221877314695589</v>
+        <v>-4.930041736574875</v>
       </c>
       <c r="E1994" t="n">
-        <v>0.9781934140060997</v>
+        <v>1.181576921014202</v>
       </c>
       <c r="F1994" t="n">
-        <v>-0.211185523813981</v>
+        <v>-0.07777126846736687</v>
       </c>
       <c r="G1994" t="n">
-        <v>2.940589449909694</v>
+        <v>3.10728727887748</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>-11.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.5%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.6%</t>
+          <t>-663.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-93.3%</t>
+          <t>-93.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-258.1%</t>
+          <t>-261.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-160.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.8%</t>
+          <t>-240.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-135.3%</t>
+          <t>-146.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1994"/>
+  <dimension ref="A1:G1995"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722815</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.789486230211609</v>
+        <v>-4.874730602332986</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9088824872693904</v>
+        <v>0.8747847384208398</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1916250228275174</v>
+        <v>-0.2768693949488939</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.710058389971271</v>
+        <v>2.658911766698445</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.850152820613998</v>
+        <v>-4.935397192735374</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8713705235843072</v>
+        <v>0.8372727747357565</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2733233395460511</v>
+        <v>-0.3585677116674276</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.647794072416023</v>
+        <v>2.596647449143197</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.785158960680352</v>
+        <v>-4.870403332801729</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9014657701683939</v>
+        <v>0.8673680213198434</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2464927249418957</v>
+        <v>-0.3317370970632722</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.667990143789145</v>
+        <v>2.616843520516319</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.88591759643735</v>
+        <v>-4.971161968558727</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8653232554966728</v>
+        <v>0.831225506648122</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3353182936689011</v>
+        <v>-0.4205626657902776</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.61885574218402</v>
+        <v>2.567709118911194</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.84171475935145</v>
+        <v>-4.926959131472826</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8888839928588701</v>
+        <v>0.8547862440103193</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2911154565830007</v>
+        <v>-0.3763598287043772</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.651257046963397</v>
+        <v>2.600110423690571</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.878693787014893</v>
+        <v>-4.963938159136269</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8725023822627405</v>
+        <v>0.8384046334141899</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.2541415547916702</v>
+        <v>-0.3393859269130466</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.671851388507443</v>
+        <v>2.620704765234617</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.898751865879733</v>
+        <v>-4.98399623800111</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.915726915899844</v>
+        <v>0.8816291670512932</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.2541415547916702</v>
+        <v>-0.3393859269130466</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.723099153690482</v>
+        <v>2.671952530417657</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.858821192701843</v>
+        <v>-4.944065564823219</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9301398897652533</v>
+        <v>0.8960421409167025</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.2142108816137798</v>
+        <v>-0.2994552537351563</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.74549826219147</v>
+        <v>2.694351638918644</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232398</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.818350845139138</v>
+        <v>-4.903595217260515</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9412762570286053</v>
+        <v>0.9071785081800545</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.1737405340510749</v>
+        <v>-0.2589849061724513</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.764728698967363</v>
+        <v>2.713582075694537</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.753126664011933</v>
+        <v>-4.838371036133309</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9845533335721923</v>
+        <v>0.9504555847236416</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1085163529238692</v>
+        <v>-0.1937607250452457</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.821050611736391</v>
+        <v>2.769903988463565</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.803620954368989</v>
+        <v>-4.888865326490365</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9603165897286501</v>
+        <v>0.9262188408800995</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.1535370900499435</v>
+        <v>-0.23878146217132</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.789999141760027</v>
+        <v>2.738852518487201</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.823732610403697</v>
+        <v>-4.908976982525074</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9535287196460072</v>
+        <v>0.9194309707974564</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.1425097450525243</v>
+        <v>-0.2277541171739008</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.797872341089719</v>
+        <v>2.746725717816893</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.921413189676343</v>
+        <v>-5.00665756179772</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.075014258958159</v>
+        <v>1.040916510109609</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.2532129403927131</v>
+        <v>-0.3384573125140896</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.892008194906817</v>
+        <v>2.840861571633991</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.897621621070201</v>
+        <v>-4.982865993191577</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.204643795618434</v>
+        <v>1.170546046769883</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.2294213717865708</v>
+        <v>-0.3146657439079473</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.026396045288319</v>
+        <v>2.975249422015493</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.934376039631923</v>
+        <v>-5.0196204117533</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.181650004207604</v>
+        <v>1.147552255359053</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.2294213717865708</v>
+        <v>-0.3146657439079473</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.018104021302178</v>
+        <v>2.966957398029352</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,45 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.827945581456508</v>
+        <v>3.803426852654192</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.930041736574875</v>
+        <v>-5.015286108696252</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.181576921014202</v>
+        <v>1.147479172165652</v>
       </c>
       <c r="F1994" t="n">
-        <v>-0.07777126846736687</v>
+        <v>-0.1630156405887433</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.10728727887748</v>
+        <v>3.056140655604654</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="2" t="n">
+        <v>45457</v>
+      </c>
+      <c r="B1995" t="n">
+        <v>3.462187490314505</v>
+      </c>
+      <c r="C1995" t="n">
+        <v>3.005669454355258</v>
+      </c>
+      <c r="D1995" t="n">
+        <v>-5.015286108696252</v>
+      </c>
+      <c r="E1995" t="n">
+        <v>1.147479172165652</v>
+      </c>
+      <c r="F1995" t="n">
+        <v>-0.1630156405887433</v>
+      </c>
+      <c r="G1995" t="n">
+        <v>2.998733251341626</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>126.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-686.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>448.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-663.1%</t>
+          <t>-665.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-275.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-93.2%</t>
+          <t>-41.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-261.5%</t>
+          <t>-262.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.4%</t>
+          <t>-161.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-240.3%</t>
+          <t>-231.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-146.2%</t>
+          <t>-126.0%</t>
         </is>
       </c>
     </row>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.2777587843568389</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.229237278920264</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.2295365175097553</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.214028354803097</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>-0.007594974340039751</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.154116842560721</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>-0.002557383612453223</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.154709319037094</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3197903830887042</v>
+        <v>-0.25975141832051</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.006562500870331</v>
+        <v>3.030578086777608</v>
       </c>
       <c r="F1841" t="n">
         <v>1.455613419548912</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3855577731381163</v>
+        <v>-0.325518808369922</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.981273153981036</v>
+        <v>3.005288739888313</v>
       </c>
       <c r="F1842" t="n">
         <v>1.455613419548912</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5908024501953608</v>
+        <v>-0.5307634854271666</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.889803315145894</v>
+        <v>2.913818901053171</v>
       </c>
       <c r="F1843" t="n">
         <v>1.455613419548912</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6725743506231125</v>
+        <v>-0.6125353858549183</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.847177280930031</v>
+        <v>2.871192866837309</v>
       </c>
       <c r="F1844" t="n">
         <v>1.482648992955049</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7397834584949903</v>
+        <v>-0.679744493726796</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.825058954614982</v>
+        <v>2.84907454052226</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9473492428866022</v>
+        <v>-0.8873102781184079</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.739857436977578</v>
+        <v>2.763873022884856</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.365103266433439</v>
+        <v>-1.305064301665245</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570682719063906</v>
+        <v>2.594698304971184</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.65523493303887</v>
+        <v>-1.595195968270676</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.454496269020656</v>
+        <v>2.478511854927933</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8814109797567796</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.863238991391948</v>
+        <v>-1.803200026623754</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.37618679023335</v>
+        <v>2.400202376140628</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8814109797567796</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.074651412279923</v>
+        <v>-2.014612447511729</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.286703278216148</v>
+        <v>2.310718864123426</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6699985588688046</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.440720139424576</v>
+        <v>-2.380681174656381</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.133360086664736</v>
+        <v>2.157375672572014</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3039298317241519</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.649210920876261</v>
+        <v>-2.589171956108066</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.07030206382283</v>
+        <v>2.094317649730108</v>
       </c>
       <c r="F1852" t="n">
         <v>0.09543905027246746</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.896412105641482</v>
+        <v>-2.836373140873287</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.97952034032531</v>
+        <v>2.003535926232588</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1155924037712799</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.388797133665579</v>
+        <v>-3.328758168897384</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.783672721159404</v>
+        <v>1.807688307066682</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3767926242528168</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.713938559827457</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.652158689507516</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-4.05762133305412</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.516454703671467</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.264133109941141</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.429956051572916</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.643516149789837</v>
+        <v>-4.583477185021643</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.279975762333697</v>
+        <v>1.303991348240975</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.075321942939625</v>
+        <v>-5.01528297817143</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.093586332541187</v>
+        <v>1.117601918448464</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.310015937072177</v>
+        <v>-5.249976972303982</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9879935098902566</v>
+        <v>1.012009095797534</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.64567858430263</v>
+        <v>-5.585639619534435</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8523090426540407</v>
+        <v>0.8763246285613184</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-5.949265864434748</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.7373616908354346</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.314393247073495</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.5905652527857672</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.722982024254174</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.4258912859282549</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-6.999558124570006</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.3104462782733823</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.415949998857004</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1418835791674606</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.746755052717844</v>
+        <v>-7.686716087949649</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01982024829180373</v>
+        <v>0.04383583419908188</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.092629874702652</v>
+        <v>-8.032590909934457</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1224301153564245</v>
+        <v>-0.0984145294491463</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.256209752887036</v>
+        <v>-8.196170788118842</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1894571465751773</v>
+        <v>-0.1654415606678992</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552871094697235</v>
+        <v>-8.49283212992904</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3043427073700484</v>
+        <v>-0.2803271214627703</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.739590803006537</v>
+        <v>-8.679551838238343</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3830568952281723</v>
+        <v>-0.3590413093208946</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.122592191749169</v>
+        <v>-9.062553226980974</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5363595520468092</v>
+        <v>-0.512343966139531</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.304461982734203</v>
+        <v>-9.244423017966009</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6065359524693927</v>
+        <v>-0.582520366562115</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.663992305238205</v>
+        <v>-9.60395334047001</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7449977781729431</v>
+        <v>-0.7209821922656654</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714341368692427</v>
+        <v>-9.654302403924232</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7572213835974546</v>
+        <v>-0.7332057976901765</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.811960646113823</v>
+        <v>-9.751921681345628</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7932273439442441</v>
+        <v>-0.7692117580369664</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-9.899447769351271</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.8253286369176513</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.10370594468113</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.9015187099309543</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23807788570949</v>
+        <v>-10.1780389209413</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9507849318578621</v>
+        <v>-0.9267693459505844</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.442858704874723</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.16460805404204</v>
+        <v>-10.10456908927385</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.906025297697461</v>
+        <v>-0.8820097117901833</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.369388873207274</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33973247142859</v>
+        <v>-10.27969350666039</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9615198439045614</v>
+        <v>-0.9375042579972837</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.544513290593818</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57418456544308</v>
+        <v>-10.51414560067488</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.062519846411953</v>
+        <v>-1.038504260504676</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.544513290593818</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.86198840998032</v>
+        <v>-10.80194944521212</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.184313575000826</v>
+        <v>-1.160297989093547</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.832317135131056</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.91477456558064</v>
+        <v>-10.85473560081245</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.2043122474024</v>
+        <v>-1.180296661495122</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.927992621713453</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.04081135894893</v>
+        <v>-10.98077239418074</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.252033236120601</v>
+        <v>-1.228017650213323</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.902740998903711</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.98879584498012</v>
+        <v>-10.92875688021192</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.227236694846675</v>
+        <v>-1.203221108939396</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.902740998903711</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.13046768670424</v>
+        <v>-11.07042872193604</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.285380658435065</v>
+        <v>-1.261365072527786</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.902740998903711</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.08087684227941</v>
+        <v>-11.02083787751121</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.250490910500258</v>
+        <v>-1.22647532459298</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.853150154478877</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.06806944927463</v>
+        <v>-11.00803048450644</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.258419086945032</v>
+        <v>-1.234403501037753</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.902005929487778</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.84222429655522</v>
+        <v>-10.78218533178703</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.158501952821058</v>
+        <v>-1.134486366913781</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.860079253900614</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.71764564021763</v>
+        <v>-10.65760667544943</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.107531345729962</v>
+        <v>-1.083515759822685</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.860079253900614</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.77054092826191</v>
+        <v>-10.71050196349372</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.12605568678557</v>
+        <v>-1.102040100878292</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.855123907812168</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.69840775297403</v>
+        <v>-10.63836878820584</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.091468712431781</v>
+        <v>-1.067453126524503</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.855123907812168</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.62704136036439</v>
+        <v>-10.56700239559619</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.072659417781787</v>
+        <v>-1.04864383187451</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.78375751520252</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.36320449316032</v>
+        <v>-10.30316552839212</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9770081522130662</v>
+        <v>-0.9529925663057894</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.78375751520252</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.09596269229192</v>
+        <v>-10.03592372752373</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8719459923650814</v>
+        <v>-0.8479304064578037</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.78375751520252</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.998055653615427</v>
+        <v>-9.938016688847235</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8330834918679457</v>
+        <v>-0.8090679059606685</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.715771765341963</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.97410211263947</v>
+        <v>-9.914063147871277</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8228335693320692</v>
+        <v>-0.7988179834247919</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.691818224366006</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.710042174316673</v>
+        <v>-9.65000320954848</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7304699101647025</v>
+        <v>-0.7064543242574253</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.42775828604321</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.002962550811835</v>
+        <v>-8.942923586043642</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4504250944230686</v>
+        <v>-0.4264095085157913</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.42775828604321</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.962778252445645</v>
+        <v>-8.902739287677452</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.434007751188751</v>
+        <v>-0.4099921652814738</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.387573987677019</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.799378381506283</v>
+        <v>-8.73933941673809</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3692809815922491</v>
+        <v>-0.3452653956849723</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.224174116737657</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.565897159276684</v>
+        <v>-8.505858194508491</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2679640638625571</v>
+        <v>-0.2439484779552799</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.990692894508058</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.41623076826917</v>
+        <v>-8.356191803500977</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2109897177725104</v>
+        <v>-0.1869741318652336</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.897789403265522</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.283955294638282</v>
+        <v>-8.223916329870089</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1627120415731285</v>
+        <v>-0.1386964556658516</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.765513929634635</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.093355619965129</v>
+        <v>-8.033316655196936</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.08365711101623052</v>
+        <v>-0.05964152510895326</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.574914254961483</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.844355821281548</v>
+        <v>-7.784316856513355</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.02884914968086072</v>
+        <v>0.05286473558813798</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.574914254961483</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.949945811054652</v>
+        <v>-7.889906846286459</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1413627758275999</v>
+        <v>-0.1173471899203227</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.680504244734587</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.968680713173249</v>
+        <v>-7.908641748405056</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1003123947979523</v>
+        <v>-0.07629680889067503</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.686100254394718</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.82074067176565</v>
+        <v>-7.760701706997457</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1610153009230801</v>
+        <v>-0.1369997150158029</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.665779338486161</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.767771149511661</v>
+        <v>-7.707732184743469</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.148541478274963</v>
+        <v>-0.1245258923676857</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.612809816232172</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.724222742740971</v>
+        <v>-7.664183777972778</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.13808272766178</v>
+        <v>-0.1140671417545027</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.612809816232172</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.482074349287113</v>
+        <v>-7.533340604893681</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.02676101589909363</v>
+        <v>-0.04726751814172081</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.612809816232172</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.373815212164591</v>
+        <v>-7.425081467771159</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.01107475940911007</v>
+        <v>-0.009431742833517109</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.612809816232172</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.25052407734746</v>
+        <v>-7.301790332954028</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.05788930734653919</v>
+        <v>0.03738280510391201</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.489518681415041</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.229374878444017</v>
+        <v>-7.280641134050585</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.07404996514524198</v>
+        <v>0.0535434629026148</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.468369482511598</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.985609436460573</v>
+        <v>-7.036875692067141</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1673368502856705</v>
+        <v>0.1468303480430433</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.468369482511598</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.883846616183278</v>
+        <v>-6.935112871789846</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2101662923166043</v>
+        <v>0.1896597900739772</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.455150414119169</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.633996222234203</v>
+        <v>-6.685262477840771</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3028485248799364</v>
+        <v>0.2823420226373092</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.455150414119169</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.45810412976677</v>
+        <v>-6.509370385373339</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3768044853875581</v>
+        <v>0.3562979831449304</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.455150414119169</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.286657666744307</v>
+        <v>-6.337923922350876</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.458710576651097</v>
+        <v>0.4382040744084699</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.283703951096706</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061624667075484</v>
+        <v>-6.112890922682053</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5477442541349236</v>
+        <v>0.5272377518922959</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.058670951427883</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997988924841549</v>
+        <v>-6.049255180448118</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5778933520828144</v>
+        <v>0.5573868498401868</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.9950352091939484</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.954226743535708</v>
+        <v>-6.005492999142277</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5765924833889469</v>
+        <v>0.5560859811463192</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.9950352091939484</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.713796246730848</v>
+        <v>-5.765062502337416</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6745077587357682</v>
+        <v>0.6540012564931406</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7546047123890881</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.641553678559653</v>
+        <v>-5.692819934166222</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7073340998390663</v>
+        <v>0.6868275975964386</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7546047123890881</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.588555356278265</v>
+        <v>-5.639821611884834</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7292120126689614</v>
+        <v>0.7087055104263338</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.6992684533871493</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.479750470798538</v>
+        <v>-5.531016726405107</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7697320380808459</v>
+        <v>0.7492255358382183</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.6992684533871493</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.259729672761527</v>
+        <v>-5.310995928368096</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8593193943062643</v>
+        <v>0.8388128920636366</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.558048608319169</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.12686198369825</v>
+        <v>-5.178128239304819</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9283606527333985</v>
+        <v>0.9078541504907709</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.558048608319169</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.006688900333751</v>
+        <v>-5.05795515594032</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9775757305194999</v>
+        <v>0.9570692282768722</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4378755249546701</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.862016755234014</v>
+        <v>-4.913283010840582</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.045532691120835</v>
+        <v>1.025026188878207</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2932033798549327</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.921891582591706</v>
+        <v>-4.973157838198275</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.007620251579184</v>
+        <v>0.987113749336556</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3530782072126248</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.835092084812697</v>
+        <v>-4.886358340419266</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.064740544013353</v>
+        <v>1.044234041770726</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3530782072126248</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.837561791274503</v>
+        <v>-4.888828046881072</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.063825062802043</v>
+        <v>1.043318560559416</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3555479136744309</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.905931977598513</v>
+        <v>-4.957198233205082</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.047483910747141</v>
+        <v>1.026977408504514</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.346272214638216</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.014470158514647</v>
+        <v>-5.065736414121216</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9945053470125789</v>
+        <v>0.9739988447699512</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.346272214638216</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.045463317843352</v>
+        <v>-5.096729573449921</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8068176483214833</v>
+        <v>0.7863111460788561</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.346272214638216</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.869989058050884</v>
+        <v>-4.921255313657452</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8815745842302587</v>
+        <v>0.8610680819876313</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.346272214638216</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.980925310692133</v>
+        <v>-5.032191566298701</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8129421119349662</v>
+        <v>0.7924356096923386</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.346272214638216</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.989207384837191</v>
+        <v>-5.04047364044376</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8127606674968484</v>
+        <v>0.7922541652542208</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3545542887832744</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.929354765633468</v>
+        <v>-4.980621021240037</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8468741016104699</v>
+        <v>0.8263675993678425</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3545542887832744</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.84311130260709</v>
+        <v>-4.894377558213659</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8763177573948815</v>
+        <v>0.8558112551522539</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3545542887832744</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.88841812200607</v>
+        <v>-4.939684377612639</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8499708050798152</v>
+        <v>0.8294643028371875</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3953644517925052</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803193</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.855068751789151</v>
+        <v>-4.96871748231494</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8638624261996841</v>
+        <v>0.8184029339893686</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3953644517925052</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.762258270338291</v>
+        <v>-4.87590700086408</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8302593106713936</v>
+        <v>0.784799818461078</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3025539703416458</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.806647739667719</v>
+        <v>-4.920296470193508</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8143769988642235</v>
+        <v>0.768917506653908</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3469434396710735</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.693976521431469</v>
+        <v>-4.807625251957258</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8545211946704465</v>
+        <v>0.809061702460131</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2342722214348233</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.581599520248796</v>
+        <v>-4.695248250774585</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9049632909741829</v>
+        <v>0.8595037987638674</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2342722214348233</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.779834089135527</v>
+        <v>-4.893482819661315</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8371666651880296</v>
+        <v>0.7917071729777141</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4325067903215539</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.862835370160806</v>
+        <v>-4.976484100686594</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6423218727785713</v>
+        <v>0.5968623805682558</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.4510776748487276</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.971449448604137</v>
+        <v>-5.085098179129925</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7190259021204446</v>
+        <v>0.6735664099101291</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.4510776748487276</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.05804803158524</v>
+        <v>-5.171696762111028</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6988994950303264</v>
+        <v>0.6534400028200107</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.4510776748487276</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.019664369027089</v>
+        <v>-5.133313099552877</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7116724013959557</v>
+        <v>0.6662129091856399</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.4126940122905765</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.842548038991922</v>
+        <v>-4.956196769517711</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7792479622553239</v>
+        <v>0.7337884700450084</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.4126940122905765</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.887640283825468</v>
+        <v>-5.001289014351257</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7618944560838186</v>
+        <v>0.7164349638735032</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.4745900554599662</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.708264862586701</v>
+        <v>-4.821913593112489</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.82743159988574</v>
+        <v>0.7819721076754247</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3178132972892476</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.753279076107306</v>
+        <v>-4.866927806633095</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7902333698090875</v>
+        <v>0.744773877598772</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3481621926038522</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.020283586379741</v>
+        <v>-5.13393231690553</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6891231280390593</v>
+        <v>0.643663635828744</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5425252306468007</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.121481367816914</v>
+        <v>-5.235130098342703</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6478479373606918</v>
+        <v>0.602388445150376</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.6109340441921198</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.089005781646142</v>
+        <v>-5.202654512171931</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6584381333833171</v>
+        <v>0.6129786411730018</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.6109340441921198</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.069967653938845</v>
+        <v>-5.183616384464633</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6625781036744809</v>
+        <v>0.6171186114641656</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.6691176555233144</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.101094285089463</v>
+        <v>-5.214743015615252</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8277093201529144</v>
+        <v>0.7822498279425987</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.6691176555233144</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.153414665690255</v>
+        <v>-5.267063396216043</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8076144968987311</v>
+        <v>0.7621550046884158</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.6341707955144422</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.173671964219213</v>
+        <v>-5.287320694745001</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8055201078840737</v>
+        <v>0.7600606156737584</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.6341707955144422</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.02592899398421</v>
+        <v>-5.139577724509999</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9437699437700968</v>
+        <v>0.8983104515597815</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.4663634382795591</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.127943676515431</v>
+        <v>-5.24159240704122</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9057576922890891</v>
+        <v>0.8602982000787738</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.4663634382795591</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394733</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.121790970462647</v>
+        <v>-5.235439700988436</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9088811231018612</v>
+        <v>0.8634216308915459</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.4602107322267748</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.138600268613149</v>
+        <v>-5.252248999138938</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9012378805817707</v>
+        <v>0.8557783883714554</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.4770200303772764</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.86736263679843</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.076302269837027</v>
+        <v>-5.189951000362815</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9924926338890407</v>
+        <v>0.947033141678725</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.4770200303772764</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.874512072171869</v>
+        <v>-4.988160802697657</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7817895853445018</v>
+        <v>0.7363300931341863</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.279001838208122</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.814621390529275</v>
+        <v>-4.928270121055064</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8760360903237143</v>
+        <v>0.830576598113399</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.2191111565655285</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.91236193515425</v>
+        <v>-5.026010665680039</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8515676085897683</v>
+        <v>0.8061081163794528</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.2350004346985087</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.088699695277179</v>
+        <v>-5.202348425802968</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7795684853652682</v>
+        <v>0.7341089931549529</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.4113381948214381</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.017153372500302</v>
+        <v>-5.130802103026091</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8066786325159474</v>
+        <v>0.7612191403056321</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.4113381948214381</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.972780240861733</v>
+        <v>-5.086428971387522</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8242907526068113</v>
+        <v>0.7788312603964958</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.3669650631828695</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.964826270566961</v>
+        <v>-5.07847500109275</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8274723407247202</v>
+        <v>0.7820128485144044</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.3669650631828695</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.917170540005905</v>
+        <v>-5.030819270531694</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8529163899769472</v>
+        <v>0.8074568977666314</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.3193093326218139</v>
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.874730602332986</v>
+        <v>-4.903134960737398</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8747847384208398</v>
+        <v>0.863422995059075</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2768693949488939</v>
+        <v>-0.1916250228275174</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.658911766698445</v>
+        <v>2.710058389971271</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.935397192735374</v>
+        <v>-4.963801551139786</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8372727747357565</v>
+        <v>0.8259110313739917</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3585677116674276</v>
+        <v>-0.2733233395460511</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.596647449143197</v>
+        <v>2.647794072416023</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.870403332801729</v>
+        <v>-4.898807691206141</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8673680213198434</v>
+        <v>0.8560062779580786</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3317370970632722</v>
+        <v>-0.2464927249418957</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.616843520516319</v>
+        <v>2.667990143789145</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.971161968558727</v>
+        <v>-4.999566326963139</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.831225506648122</v>
+        <v>0.8198637632863572</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4205626657902776</v>
+        <v>-0.3353182936689011</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.567709118911194</v>
+        <v>2.61885574218402</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.926959131472826</v>
+        <v>-4.955363489877239</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8547862440103193</v>
+        <v>0.8434245006485546</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3763598287043772</v>
+        <v>-0.2911154565830007</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.600110423690571</v>
+        <v>2.651257046963397</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.963938159136269</v>
+        <v>-4.992342517540681</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8384046334141899</v>
+        <v>0.8270428900524252</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.3393859269130466</v>
+        <v>-0.2541415547916702</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.620704765234617</v>
+        <v>2.671851388507443</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.98399623800111</v>
+        <v>-5.012400596405522</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8816291670512932</v>
+        <v>0.8702674236895285</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.3393859269130466</v>
+        <v>-0.2541415547916702</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.671952530417657</v>
+        <v>2.723099153690482</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.944065564823219</v>
+        <v>-4.972469923227631</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8960421409167025</v>
+        <v>0.8846803975549378</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.2994552537351563</v>
+        <v>-0.2142108816137798</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.694351638918644</v>
+        <v>2.74549826219147</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.903595217260515</v>
+        <v>-4.931999575664927</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9071785081800545</v>
+        <v>0.8958167648182898</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.2589849061724513</v>
+        <v>-0.1737405340510749</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.713582075694537</v>
+        <v>2.764728698967363</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.838371036133309</v>
+        <v>-4.866775394537721</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9504555847236416</v>
+        <v>0.9390938413618768</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1937607250452457</v>
+        <v>-0.1085163529238692</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.769903988463565</v>
+        <v>2.821050611736391</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.888865326490365</v>
+        <v>-4.917269684894777</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9262188408800995</v>
+        <v>0.9148570975183348</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.23878146217132</v>
+        <v>-0.1535370900499435</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.738852518487201</v>
+        <v>2.789999141760027</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.908976982525074</v>
+        <v>-4.937381340929486</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9194309707974564</v>
+        <v>0.9080692274356916</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.2277541171739008</v>
+        <v>-0.1425097450525243</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.746725717816893</v>
+        <v>2.797872341089719</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.00665756179772</v>
+        <v>-5.035061920202132</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.040916510109609</v>
+        <v>1.029554766747844</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.3384573125140896</v>
+        <v>-0.2532129403927131</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.840861571633991</v>
+        <v>2.892008194906817</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.982865993191577</v>
+        <v>-5.011270351595989</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.170546046769883</v>
+        <v>1.159184303408118</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3146657439079473</v>
+        <v>-0.2294213717865708</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.975249422015493</v>
+        <v>3.026396045288319</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.0196204117533</v>
+        <v>-5.048024770157712</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.147552255359053</v>
+        <v>1.136190511997288</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.3146657439079473</v>
+        <v>-0.2294213717865708</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.966957398029352</v>
+        <v>3.018104021302178</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-5.015286108696252</v>
+        <v>-5.043690467100664</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.147479172165652</v>
+        <v>1.136117428803887</v>
       </c>
       <c r="F1994" t="n">
-        <v>-0.1630156405887433</v>
+        <v>-0.07777126846736687</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.056140655604654</v>
+        <v>3.10728727887748</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.462187490314505</v>
+        <v>3.809008178316424</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.005669454355258</v>
+        <v>3.206924726045854</v>
       </c>
       <c r="D1995" t="n">
-        <v>-5.015286108696252</v>
+        <v>-5.043690467100664</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.147479172165652</v>
+        <v>1.136117428803887</v>
       </c>
       <c r="F1995" t="n">
-        <v>-0.1630156405887433</v>
+        <v>-0.07777126846736687</v>
       </c>
       <c r="G1995" t="n">
-        <v>2.998733251341626</v>
+        <v>3.199988523032221</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-686.6%</t>
+          <t>-686.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.3%</t>
+          <t>448.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.9%</t>
+          <t>-654.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-275.0%</t>
+          <t>-274.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-41.2%</t>
+          <t>-3421.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-262.6%</t>
+          <t>-258.0%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2777587843568389</v>
+        <v>0.282369385115126</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.229237278920264</v>
+        <v>3.231081519223579</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43819,16 +43819,16 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.2295365175097553</v>
+        <v>0.2341471182680425</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.214028354803097</v>
+        <v>3.215872595106412</v>
       </c>
       <c r="F1838" t="n">
         <v>1.657162997990651</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.007594974340039751</v>
+        <v>-0.002984373581752631</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.154116842560721</v>
+        <v>3.155961082864036</v>
       </c>
       <c r="F1839" t="n">
         <v>1.657162997990651</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.002557383612453223</v>
+        <v>0.002053217145833897</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.154709319037094</v>
+        <v>3.156553559340409</v>
       </c>
       <c r="F1840" t="n">
         <v>1.712807454256969</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.25975141832051</v>
+        <v>-0.2551408175622228</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.030578086777608</v>
+        <v>3.032422327080923</v>
       </c>
       <c r="F1841" t="n">
         <v>1.455613419548912</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.325518808369922</v>
+        <v>-0.3209082076116349</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.005288739888313</v>
+        <v>3.007132980191628</v>
       </c>
       <c r="F1842" t="n">
         <v>1.455613419548912</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5307634854271666</v>
+        <v>-0.5261528846688794</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.913818901053171</v>
+        <v>2.915663141356486</v>
       </c>
       <c r="F1843" t="n">
         <v>1.455613419548912</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6125353858549183</v>
+        <v>-0.6079247850966312</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.871192866837309</v>
+        <v>2.873037107140624</v>
       </c>
       <c r="F1844" t="n">
         <v>1.482648992955049</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.679744493726796</v>
+        <v>-0.6751338929685089</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.84907454052226</v>
+        <v>2.850918780825575</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8873102781184079</v>
+        <v>-0.8826996773601208</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.763873022884856</v>
+        <v>2.76571726318817</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.305064301665245</v>
+        <v>-1.300453700906958</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.594698304971184</v>
+        <v>2.596542545274499</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.595195968270676</v>
+        <v>-1.590585367512389</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.478511854927933</v>
+        <v>2.480356095231248</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8814109797567796</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.803200026623754</v>
+        <v>-1.798589425865466</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.400202376140628</v>
+        <v>2.402046616443942</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8814109797567796</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.014612447511729</v>
+        <v>-2.010001846753442</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.310718864123426</v>
+        <v>2.312563104426741</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6699985588688046</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.380681174656381</v>
+        <v>-2.376070573898094</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.157375672572014</v>
+        <v>2.159219912875328</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3039298317241519</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.589171956108066</v>
+        <v>-2.584561355349779</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.094317649730108</v>
+        <v>2.096161890033423</v>
       </c>
       <c r="F1852" t="n">
         <v>0.09543905027246746</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.836373140873287</v>
+        <v>-2.831762540115</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.003535926232588</v>
+        <v>2.005380166535903</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1155924037712799</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.328758168897384</v>
+        <v>-3.324147568139097</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.807688307066682</v>
+        <v>1.809532547369997</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3767926242528168</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.713938559827457</v>
+        <v>-3.709327959069169</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.652158689507516</v>
+        <v>1.654002929810831</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.05762133305412</v>
+        <v>-4.053010732295832</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.516454703671467</v>
+        <v>1.518298943974782</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.264133109941141</v>
+        <v>-4.259522509182854</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.429956051572916</v>
+        <v>1.431800291876231</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.583477185021643</v>
+        <v>-4.578866584263356</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.303991348240975</v>
+        <v>1.30583558854429</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.01528297817143</v>
+        <v>-5.010672377413143</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.117601918448464</v>
+        <v>1.119446158751779</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.249976972303982</v>
+        <v>-5.245366371545695</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.012009095797534</v>
+        <v>1.013853336100849</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.585639619534435</v>
+        <v>-5.581029018776148</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8763246285613184</v>
+        <v>0.8781688688646332</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.949265864434748</v>
+        <v>-5.944655263676461</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7373616908354346</v>
+        <v>0.7392059311387493</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.314393247073495</v>
+        <v>-6.309782646315208</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5905652527857672</v>
+        <v>0.592409493089082</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.722982024254174</v>
+        <v>-6.718371423495887</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4258912859282549</v>
+        <v>0.4277355262315696</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.999558124570006</v>
+        <v>-6.994947523811719</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3104462782733823</v>
+        <v>0.3122905185766971</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.415949998857004</v>
+        <v>-7.411339398098717</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1418835791674606</v>
+        <v>0.1437278194707758</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.686716087949649</v>
+        <v>-7.682105487191362</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.04383583419908188</v>
+        <v>0.04568007450239664</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.032590909934457</v>
+        <v>-8.02798030917617</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0984145294491463</v>
+        <v>-0.09657028914583154</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.196170788118842</v>
+        <v>-8.191560187360555</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1654415606678992</v>
+        <v>-0.1635973203645844</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.49283212992904</v>
+        <v>-8.488221529170753</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2803271214627703</v>
+        <v>-0.2784828811594555</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.679551838238343</v>
+        <v>-8.674941237480056</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3590413093208946</v>
+        <v>-0.3571970690175799</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.062553226980974</v>
+        <v>-9.057942626222687</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.512343966139531</v>
+        <v>-0.5104997258362163</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.244423017966009</v>
+        <v>-9.239812417207721</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.582520366562115</v>
+        <v>-0.5806761262587998</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.60395334047001</v>
+        <v>-9.599342739711723</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7209821922656654</v>
+        <v>-0.7191379519623506</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.654302403924232</v>
+        <v>-9.649691803165945</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7332057976901765</v>
+        <v>-0.7313615573868617</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.751921681345628</v>
+        <v>-9.747311080587341</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7692117580369664</v>
+        <v>-0.7673675177336512</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.899447769351271</v>
+        <v>-9.894837168592984</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8253286369176513</v>
+        <v>-0.8234843966143361</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.10370594468113</v>
+        <v>-10.09909534392285</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9015187099309543</v>
+        <v>-0.8996744696276391</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.1780389209413</v>
+        <v>-10.17342832018301</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9267693459505844</v>
+        <v>-0.9249251056472692</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.442858704874723</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.10456908927385</v>
+        <v>-10.09995848851556</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8820097117901833</v>
+        <v>-0.8801654714868681</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.369388873207274</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.27969350666039</v>
+        <v>-10.27508290590211</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9375042579972837</v>
+        <v>-0.9356600176939693</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.544513290593818</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.51414560067488</v>
+        <v>-10.5095349999166</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.038504260504676</v>
+        <v>-1.03666002020136</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.544513290593818</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.80194944521212</v>
+        <v>-10.79733884445383</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.160297989093547</v>
+        <v>-1.158453748790233</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.832317135131056</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.85473560081245</v>
+        <v>-10.85012500005416</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.180296661495122</v>
+        <v>-1.178452421191807</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.927992621713453</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.98077239418074</v>
+        <v>-10.97616179342245</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.228017650213323</v>
+        <v>-1.226173409910008</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.902740998903711</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.92875688021192</v>
+        <v>-10.92414627945364</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.203221108939396</v>
+        <v>-1.201376868636082</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.902740998903711</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.07042872193604</v>
+        <v>-11.06581812117776</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.261365072527786</v>
+        <v>-1.259520832224472</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.902740998903711</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.02083787751121</v>
+        <v>-11.01622727675292</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.22647532459298</v>
+        <v>-1.224631084289666</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.853150154478877</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.00803048450644</v>
+        <v>-11.00341988374815</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.234403501037753</v>
+        <v>-1.232559260734439</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.902005929487778</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.78218533178703</v>
+        <v>-10.77757473102874</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.134486366913781</v>
+        <v>-1.132642126610466</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.860079253900614</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.65760667544943</v>
+        <v>-10.65299607469115</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.083515759822685</v>
+        <v>-1.08167151951937</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.860079253900614</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.71050196349372</v>
+        <v>-10.70589136273543</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.102040100878292</v>
+        <v>-1.100195860574978</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.855123907812168</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.63836878820584</v>
+        <v>-10.63375818744755</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.067453126524503</v>
+        <v>-1.065608886221189</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.855123907812168</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.56700239559619</v>
+        <v>-10.56239179483791</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.04864383187451</v>
+        <v>-1.046799591571195</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.78375751520252</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.30316552839212</v>
+        <v>-10.29855492763384</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9529925663057894</v>
+        <v>-0.9511483260024742</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.78375751520252</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.03592372752373</v>
+        <v>-10.03131312676544</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8479304064578037</v>
+        <v>-0.8460861661544894</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.78375751520252</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.938016688847235</v>
+        <v>-9.933406088088947</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8090679059606685</v>
+        <v>-0.8072236656573537</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.715771765341963</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.914063147871277</v>
+        <v>-9.90945254711299</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7988179834247919</v>
+        <v>-0.7969737431214772</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.691818224366006</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.65000320954848</v>
+        <v>-9.645392608790193</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7064543242574253</v>
+        <v>-0.7046100839541105</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.42775828604321</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.942923586043642</v>
+        <v>-8.938312985285355</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4264095085157913</v>
+        <v>-0.4245652682124765</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.42775828604321</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.902739287677452</v>
+        <v>-8.898128686919165</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4099921652814738</v>
+        <v>-0.408147924978159</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.387573987677019</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.73933941673809</v>
+        <v>-8.734728815979803</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3452653956849723</v>
+        <v>-0.3434211553816571</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.224174116737657</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.505858194508491</v>
+        <v>-8.501247593750204</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2439484779552799</v>
+        <v>-0.2421042376519651</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.990692894508058</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.356191803500977</v>
+        <v>-8.35158120274269</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1869741318652336</v>
+        <v>-0.1851298915619184</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.897789403265522</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.223916329870089</v>
+        <v>-8.219305729111802</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1386964556658516</v>
+        <v>-0.1368522153625364</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.765513929634635</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.033316655196936</v>
+        <v>-8.028706054438649</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.05964152510895326</v>
+        <v>-0.0577972848056385</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.574914254961483</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.784316856513355</v>
+        <v>-7.779706255755068</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.05286473558813798</v>
+        <v>0.05470897589145274</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.574914254961483</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.889906846286459</v>
+        <v>-7.885296245528172</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1173471899203227</v>
+        <v>-0.1155029496170079</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.680504244734587</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.908641748405056</v>
+        <v>-7.904031147646769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07629680889067503</v>
+        <v>-0.07445256858736027</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.686100254394718</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.760701706997457</v>
+        <v>-7.75609110623917</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1369997150158029</v>
+        <v>-0.1351554747124881</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.665779338486161</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.707732184743469</v>
+        <v>-7.703121583985181</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1245258923676857</v>
+        <v>-0.122681652064371</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.612809816232172</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.664183777972778</v>
+        <v>-7.659573177214491</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1140671417545027</v>
+        <v>-0.112222901451188</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.612809816232172</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.533340604893681</v>
+        <v>-7.417424783760633</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04726751814172081</v>
+        <v>-0.0009011896885016135</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.612809816232172</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.425081467771159</v>
+        <v>-7.309165646638111</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.009431742833517109</v>
+        <v>0.03693458561970209</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.612809816232172</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.301790332954028</v>
+        <v>-7.18587451182098</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.03738280510391201</v>
+        <v>0.08374913355713121</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.489518681415041</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.280641134050585</v>
+        <v>-7.164725312917537</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.0535434629026148</v>
+        <v>0.099909791355834</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.468369482511598</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.036875692067141</v>
+        <v>-6.920959870934093</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1468303480430433</v>
+        <v>0.1931966764962625</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.468369482511598</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.935112871789846</v>
+        <v>-6.819197050656798</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1896597900739772</v>
+        <v>0.2360261185271963</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.455150414119169</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.685262477840771</v>
+        <v>-6.569346656707723</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2823420226373092</v>
+        <v>0.3287083510905284</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.455150414119169</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.509370385373339</v>
+        <v>-6.39345456424029</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3562979831449304</v>
+        <v>0.4026643115981501</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.455150414119169</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.337923922350876</v>
+        <v>-6.222008101217827</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4382040744084699</v>
+        <v>0.4845704028616891</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.283703951096706</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.112890922682053</v>
+        <v>-5.996975101549004</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5272377518922959</v>
+        <v>0.5736040803455156</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.058670951427883</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.049255180448118</v>
+        <v>-5.933339359315069</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5573868498401868</v>
+        <v>0.6037531782934065</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.9950352091939484</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.005492999142277</v>
+        <v>-5.889577178009228</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5560859811463192</v>
+        <v>0.6024523095995389</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.9950352091939484</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.765062502337416</v>
+        <v>-5.649146681204368</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6540012564931406</v>
+        <v>0.7003675849463602</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7546047123890881</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.692819934166222</v>
+        <v>-5.576904113033173</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6868275975964386</v>
+        <v>0.7331939260496583</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7546047123890881</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.639821611884834</v>
+        <v>-5.523905790751785</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7087055104263338</v>
+        <v>0.7550718388795534</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.6992684533871493</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.531016726405107</v>
+        <v>-5.415100905272058</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7492255358382183</v>
+        <v>0.7955918642914379</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.6992684533871493</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.310995928368096</v>
+        <v>-5.195080107235047</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8388128920636366</v>
+        <v>0.8851792205168563</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.558048608319169</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.178128239304819</v>
+        <v>-5.06221241817177</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9078541504907709</v>
+        <v>0.9542204789439905</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.558048608319169</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.05795515594032</v>
+        <v>-4.942039334807271</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9570692282768722</v>
+        <v>1.003435556730092</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4378755249546701</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.913283010840582</v>
+        <v>-4.797367189707534</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.025026188878207</v>
+        <v>1.071392517331427</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2932033798549327</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.973157838198275</v>
+        <v>-4.857242017065226</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.987113749336556</v>
+        <v>1.033480077789776</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3530782072126248</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.886358340419266</v>
+        <v>-4.770442519286217</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.044234041770726</v>
+        <v>1.090600370223946</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3530782072126248</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.888828046881072</v>
+        <v>-4.772912225748023</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.043318560559416</v>
+        <v>1.089684889012635</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3555479136744309</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.957198233205082</v>
+        <v>-4.841282412072033</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.026977408504514</v>
+        <v>1.073343736957733</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.346272214638216</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.065736414121216</v>
+        <v>-4.949820592988167</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9739988447699512</v>
+        <v>1.020365173223171</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.346272214638216</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.096729573449921</v>
+        <v>-4.980813752316872</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7863111460788561</v>
+        <v>0.8326774745320755</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.346272214638216</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.921255313657452</v>
+        <v>-4.805339492524404</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8610680819876313</v>
+        <v>0.9074344104408507</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.346272214638216</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.032191566298701</v>
+        <v>-4.916275745165652</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7924356096923386</v>
+        <v>0.8388019381455583</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.346272214638216</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.77321029711129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.04047364044376</v>
+        <v>-4.924557819310711</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7922541652542208</v>
+        <v>0.8386204937074404</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3545542887832744</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.980621021240037</v>
+        <v>-4.864705200106988</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8263675993678425</v>
+        <v>0.872733927821062</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3545542887832744</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.894377558213659</v>
+        <v>-4.77846173708061</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8558112551522539</v>
+        <v>0.9021775836054735</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3545542887832744</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.939684377612639</v>
+        <v>-4.82376855647959</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8294643028371875</v>
+        <v>0.8758306312904072</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3953644517925052</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.96871748231494</v>
+        <v>-4.852801661181891</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8184029339893686</v>
+        <v>0.8647692624425882</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3953644517925052</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.87590700086408</v>
+        <v>-4.759991179731031</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.784799818461078</v>
+        <v>0.8311661469142977</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3025539703416458</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.920296470193508</v>
+        <v>-4.804380649060459</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.768917506653908</v>
+        <v>0.8152838351071274</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3469434396710735</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.807625251957258</v>
+        <v>-4.691709430824209</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.809061702460131</v>
+        <v>0.8554280309133506</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2342722214348233</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.695248250774585</v>
+        <v>-4.579332429641536</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8595037987638674</v>
+        <v>0.905870127217087</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2342722214348233</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.893482819661315</v>
+        <v>-4.777566998528266</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7917071729777141</v>
+        <v>0.8380735014309337</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4325067903215539</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.976484100686594</v>
+        <v>-4.860568279553545</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5968623805682558</v>
+        <v>0.6432287090214754</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.4510776748487276</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729273</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.085098179129925</v>
+        <v>-4.969182357996877</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6735664099101291</v>
+        <v>0.7199327383633487</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.4510776748487276</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.171696762111028</v>
+        <v>-5.055780940977979</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6534400028200107</v>
+        <v>0.6998063312732303</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.4510776748487276</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.133313099552877</v>
+        <v>-5.017397278419828</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6662129091856399</v>
+        <v>0.7125792376388596</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.4126940122905765</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.956196769517711</v>
+        <v>-4.840280948384662</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7337884700450084</v>
+        <v>0.780154798498228</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.4126940122905765</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.001289014351257</v>
+        <v>-4.885373193218208</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7164349638735032</v>
+        <v>0.7628012923267227</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.4745900554599662</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.821913593112489</v>
+        <v>-4.70599777197944</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7819721076754247</v>
+        <v>0.8283384361286441</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3178132972892476</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.866927806633095</v>
+        <v>-4.751011985500046</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.744773877598772</v>
+        <v>0.7911402060519916</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.3481621926038522</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.13393231690553</v>
+        <v>-5.018016495772481</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.643663635828744</v>
+        <v>0.6900299642819632</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.5425252306468007</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.235130098342703</v>
+        <v>-5.119214277209654</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.602388445150376</v>
+        <v>0.6487547736035957</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.6109340441921198</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.202654512171931</v>
+        <v>-5.086738691038882</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6129786411730018</v>
+        <v>0.6593449696262215</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.6109340441921198</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.183616384464633</v>
+        <v>-5.067700563331584</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6171186114641656</v>
+        <v>0.6634849399173852</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.6691176555233144</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.214743015615252</v>
+        <v>-5.098827194482203</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7822498279425987</v>
+        <v>0.8286161563958183</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.6691176555233144</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.267063396216043</v>
+        <v>-5.151147575082994</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7621550046884158</v>
+        <v>0.808521333141635</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.6341707955144422</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.287320694745001</v>
+        <v>-5.171404873611952</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7600606156737584</v>
+        <v>0.806426944126978</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.6341707955144422</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.139577724509999</v>
+        <v>-5.02366190337695</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8983104515597815</v>
+        <v>0.9446767800130007</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.4663634382795591</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.24159240704122</v>
+        <v>-5.125676585908171</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8602982000787738</v>
+        <v>0.9066645285319934</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.4663634382795591</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394733</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.235439700988436</v>
+        <v>-5.119523879855387</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8634216308915459</v>
+        <v>0.9097879593447655</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.4602107322267748</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.252248999138938</v>
+        <v>-5.136333178005889</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8557783883714554</v>
+        <v>0.902144716824675</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.4770200303772764</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679843</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.189951000362815</v>
+        <v>-5.074035179229766</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.947033141678725</v>
+        <v>0.9933994701319446</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.4770200303772764</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.988160802697657</v>
+        <v>-4.872244981564609</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7363300931341863</v>
+        <v>0.7826964215874059</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.279001838208122</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.928270121055064</v>
+        <v>-4.812354299922015</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.830576598113399</v>
+        <v>0.8769429265666184</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.2191111565655285</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.026010665680039</v>
+        <v>-4.91009484454699</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8061081163794528</v>
+        <v>0.8524744448326724</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.2350004346985087</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.202348425802968</v>
+        <v>-5.086432604669919</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7341089931549529</v>
+        <v>0.7804753216081721</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.4113381948214381</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.130802103026091</v>
+        <v>-5.014886281893042</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7612191403056321</v>
+        <v>0.8075854687588517</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.4113381948214381</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.086428971387522</v>
+        <v>-4.970513150254473</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7788312603964958</v>
+        <v>0.8251975888497154</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.3669650631828695</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.07847500109275</v>
+        <v>-4.962559179959701</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7820128485144044</v>
+        <v>0.8283791769676241</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.3669650631828695</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.030819270531694</v>
+        <v>-4.914903449398645</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8074568977666314</v>
+        <v>0.8538232262198511</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.3193093326218139</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.903134960737398</v>
+        <v>-4.787219139604349</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.863422995059075</v>
+        <v>0.9097893235122945</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.1916250228275174</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.82883791131455</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.963801551139786</v>
+        <v>-4.847885730006738</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8259110313739917</v>
+        <v>0.8722773598272113</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.2733233395460511</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.898807691206141</v>
+        <v>-4.782891870073092</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8560062779580786</v>
+        <v>0.902372606411298</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.2464927249418957</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.999566326963139</v>
+        <v>-4.88365050583009</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8198637632863572</v>
+        <v>0.8662300917395769</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.3353182936689011</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.955363489877239</v>
+        <v>-4.83944766874419</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8434245006485546</v>
+        <v>0.8897908291017742</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.2911154565830007</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.992342517540681</v>
+        <v>-4.876426696407632</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8270428900524252</v>
+        <v>0.8734092185056446</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.2541415547916702</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.012400596405522</v>
+        <v>-4.896484775272473</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8702674236895285</v>
+        <v>0.9166337521427481</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.2541415547916702</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.972469923227631</v>
+        <v>-4.856554102094583</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8846803975549378</v>
+        <v>0.9310467260081574</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.2142108816137798</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232398</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.931999575664927</v>
+        <v>-4.816083754531878</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8958167648182898</v>
+        <v>0.9421830932715092</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.1737405340510749</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.866775394537721</v>
+        <v>-4.750859573404672</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9390938413618768</v>
+        <v>0.9854601698150964</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.1085163529238692</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.917269684894777</v>
+        <v>-4.801353863761729</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9148570975183348</v>
+        <v>0.9612234259715542</v>
       </c>
       <c r="F1989" t="n">
         <v>-0.1535370900499435</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.937381340929486</v>
+        <v>-4.821465519796437</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9080692274356916</v>
+        <v>0.9544355558889113</v>
       </c>
       <c r="F1990" t="n">
         <v>-0.1425097450525243</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.035061920202132</v>
+        <v>-4.919146099069083</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.029554766747844</v>
+        <v>1.075921095201063</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.2532129403927131</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.011270351595989</v>
+        <v>-4.89535453046294</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.159184303408118</v>
+        <v>1.205550631861338</v>
       </c>
       <c r="F1992" t="n">
         <v>-0.2294213717865708</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756014</v>
+        <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.048024770157712</v>
+        <v>-4.932108949024663</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.136190511997288</v>
+        <v>1.182556840450508</v>
       </c>
       <c r="F1993" t="n">
         <v>-0.2294213717865708</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654192</v>
+        <v>3.803426852654188</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-5.043690467100664</v>
+        <v>-4.927774645967615</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.136117428803887</v>
+        <v>1.182483757257107</v>
       </c>
       <c r="F1994" t="n">
         <v>-0.07777126846736687</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.809008178316424</v>
+        <v>3.809008178316421</v>
       </c>
       <c r="C1995" t="n">
         <v>3.206924726045854</v>
       </c>
       <c r="D1995" t="n">
-        <v>-5.043690467100664</v>
+        <v>-4.927774645967615</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.136117428803887</v>
+        <v>1.182483757257107</v>
       </c>
       <c r="F1995" t="n">
         <v>-0.07777126846736687</v>

--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>-1.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.3%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-686.1%</t>
+          <t>-702.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.1%</t>
+          <t>456.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.4%</t>
+          <t>-676.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.8%</t>
+          <t>-281.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3421.5%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-258.0%</t>
+          <t>-266.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-316.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-165.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.8%</t>
+          <t>-247.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.1%</t>
+          <t>-190.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-126.0%</t>
+          <t>-136.3%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.282369385115126</v>
+        <v>0.2177198195886446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.231081519223579</v>
+        <v>3.205221693012986</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.2341471182680425</v>
+        <v>0.0698802420482833</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.215872595106412</v>
+        <v>3.150165844618509</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.657162997990651</v>
+        <v>1.557545687297374</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.116867970907334</v>
+        <v>4.057097584491367</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.002984373581752631</v>
+        <v>-0.1672512498015118</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.155961082864036</v>
+        <v>3.090254332376132</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.657162997990651</v>
+        <v>1.557545687297374</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.151809055404875</v>
+        <v>4.092038668988909</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.002053217145833897</v>
+        <v>-0.1622136590739253</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.156553559340409</v>
+        <v>3.090846808852505</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.712807454256969</v>
+        <v>1.613190143563691</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.183773169350004</v>
+        <v>4.124002782934037</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2551408175622228</v>
+        <v>-0.419407693781982</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.032422327080923</v>
+        <v>2.966715576593019</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.455613419548912</v>
+        <v>1.355996108855634</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.008203130148907</v>
+        <v>3.948432743732941</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3209082076116349</v>
+        <v>-0.4851750838313941</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.007132980191628</v>
+        <v>2.941426229703725</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.455613419548912</v>
+        <v>1.355996108855634</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.009220739279377</v>
+        <v>3.94945035286341</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5261528846688794</v>
+        <v>-0.6904197608886387</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.915663141356486</v>
+        <v>2.849956390868583</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.455613419548912</v>
+        <v>1.355996108855634</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.999848771267133</v>
+        <v>3.940078384851166</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6079247850966312</v>
+        <v>-0.7721916613163904</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.873037107140624</v>
+        <v>2.80733035665272</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.482648992955049</v>
+        <v>1.383031682261771</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.006152841266053</v>
+        <v>3.946382454850086</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6751338929685089</v>
+        <v>-0.8394007691882681</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.850918780825575</v>
+        <v>2.785212030337672</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.482648992955049</v>
+        <v>1.383031682261771</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.010918158099756</v>
+        <v>3.951147771683789</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8826996773601208</v>
+        <v>-1.04696655357988</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.76571726318817</v>
+        <v>2.700010512700267</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.275083208563437</v>
+        <v>1.175465897870159</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.884203483584028</v>
+        <v>3.824433097168062</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.300453700906958</v>
+        <v>-1.464720577126717</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.596542545274499</v>
+        <v>2.530835794786595</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8573291850165997</v>
+        <v>0.7577118743233217</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.631477960960989</v>
+        <v>3.571707574545023</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.590585367512389</v>
+        <v>-1.754852243732149</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.480356095231248</v>
+        <v>2.414649344743344</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8814109797567796</v>
+        <v>0.7817936690635016</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.645793254404019</v>
+        <v>3.586022867988052</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.798589425865466</v>
+        <v>-1.962856302085226</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.402046616443942</v>
+        <v>2.336339865956039</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8814109797567796</v>
+        <v>0.7817936690635016</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.650685398957944</v>
+        <v>3.590915012541978</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.010001846753442</v>
+        <v>-2.174268722973201</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.312563104426741</v>
+        <v>2.246856353938837</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6699985588688046</v>
+        <v>0.5703812481755265</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.518919402763148</v>
+        <v>3.459149016347181</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.376070573898094</v>
+        <v>-2.540337450117854</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.159219912875328</v>
+        <v>2.093513162387425</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3039298317241519</v>
+        <v>0.2043125210308738</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.292362465782805</v>
+        <v>3.232592079366838</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.584561355349779</v>
+        <v>-2.748828231569538</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.096161890033423</v>
+        <v>2.030455139545519</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.09543905027246746</v>
+        <v>-0.004178260420810598</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.187606286650563</v>
+        <v>3.127835900234596</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.831762540115</v>
+        <v>-2.99602941633476</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.005380166535903</v>
+        <v>1.939673416048</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1155924037712799</v>
+        <v>0.01597509307800182</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.207797049158418</v>
+        <v>3.148026662742452</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.324147568139097</v>
+        <v>-3.488414444358857</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.809532547369997</v>
+        <v>1.743825796882093</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.4764099349460949</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.913472424387693</v>
+        <v>2.853702037971726</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.709327959069169</v>
+        <v>-3.873594835288929</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.654002929810831</v>
+        <v>1.588296179322927</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.4764099349460949</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.912014963200556</v>
+        <v>2.852244576784589</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.053010732295832</v>
+        <v>-4.217277608515592</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.518298943974782</v>
+        <v>1.452592193486878</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.484698676280035</v>
+        <v>-0.5843159869733131</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.849040455438841</v>
+        <v>2.789270069022875</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.259522509182854</v>
+        <v>-4.423789385402613</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.431800291876231</v>
+        <v>1.366093541388327</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.7908277638603346</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.721239447962886</v>
+        <v>2.661469061546919</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.578866584263356</v>
+        <v>-4.743133460483115</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.30583558854429</v>
+        <v>1.240128838056386</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.7908277638603346</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.723012374663146</v>
+        <v>2.663241988247179</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.010672377413143</v>
+        <v>-5.174939253632902</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.119446158751779</v>
+        <v>1.053739408263876</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8276279496083235</v>
+        <v>-0.9272452603016016</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.62749476426579</v>
+        <v>2.567724377849823</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.245366371545695</v>
+        <v>-5.409633247765455</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.013853336100849</v>
+        <v>0.9481465856129452</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.9209089930723464</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.619581299605434</v>
+        <v>2.559810913189467</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.581029018776148</v>
+        <v>-5.745295894995907</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8781688688646332</v>
+        <v>0.8124621183767293</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.9209089930723464</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.618161891261399</v>
+        <v>2.558391504845432</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.944655263676461</v>
+        <v>-6.108922139896221</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7392059311387493</v>
+        <v>0.6734991806508455</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9195133192461942</v>
+        <v>-1.019130629939472</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.565716469375365</v>
+        <v>2.505946082959398</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.309782646315208</v>
+        <v>-6.474049522534967</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.592409493089082</v>
+        <v>0.5267027426011786</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.315441414238485</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.327414127385822</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.718371423495887</v>
+        <v>-6.882638299715646</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4277355262315696</v>
+        <v>0.3620287757436658</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.724030191419163</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.081022405092174</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.994947523811719</v>
+        <v>-7.159214400031479</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3122905185766971</v>
+        <v>0.2465837680887937</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.724030191419163</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.076207837563635</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.411339398098717</v>
+        <v>-7.575606274318476</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1437278194707758</v>
+        <v>0.07802106898287198</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.724030191419163</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.074201888172512</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.682105487191362</v>
+        <v>-7.846372363411121</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.04568007450239664</v>
+        <v>-0.02002667598550723</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.724030191419163</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.084460578841191</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.02798030917617</v>
+        <v>-8.19224718539593</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.09657028914583154</v>
+        <v>-0.1622770396337354</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.724030191419163</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.080560143986887</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.191560187360555</v>
+        <v>-8.355827063580314</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1635973203645844</v>
+        <v>-0.2293040708524883</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.724030191419163</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.078965064041888</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.488221529170753</v>
+        <v>-8.652488405390512</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2784828811594555</v>
+        <v>-0.3441896316473594</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.792773327153042</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.041498158530768</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.674941237480056</v>
+        <v>-8.839208113699815</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3571970690175799</v>
+        <v>-0.4229038195054837</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.792773327153042</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.037471853996365</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.057942626222687</v>
+        <v>-9.222209502442446</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5104997258362163</v>
+        <v>-0.5762064763241201</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.792773327153042</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.037369752674781</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.239812417207721</v>
+        <v>-9.404079293427481</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5806761262587998</v>
+        <v>-0.6463828767467037</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.974643118138077</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>1.93081939405519</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.599342739711723</v>
+        <v>-9.763609615931482</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7191379519623506</v>
+        <v>-0.7848447024502541</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.974643118138077</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>1.936169697353241</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.649691803165945</v>
+        <v>-9.813958679385705</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7313615573868617</v>
+        <v>-0.7970683078747656</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-2.024992181592299</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>1.913876279237885</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.747311080587341</v>
+        <v>-9.911577956807101</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7673675177336512</v>
+        <v>-0.8330742682215551</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-2.122611459013695</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.858346463406816</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.894837168592984</v>
+        <v>-10.05910404481274</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8234843966143361</v>
+        <v>-0.8891911471022405</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.270137547019339</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.772724366925002</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.09909534392285</v>
+        <v>-10.26336222014261</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8996744696276391</v>
+        <v>-0.9653812201155434</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.397776491633328</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.701654197275251</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.17342832018301</v>
+        <v>-10.33769519640277</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9249251056472692</v>
+        <v>-0.9906318561351726</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.442858704874723</v>
+        <v>-2.542476015568</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.67908742381485</v>
+        <v>1.619317037398883</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.09995848851556</v>
+        <v>-10.26422536473532</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8801654714868681</v>
+        <v>-0.9458722219747724</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.369388873207274</v>
+        <v>-2.469006183900552</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.73854102430874</v>
+        <v>1.678770637892773</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.27508290590211</v>
+        <v>-10.43934978212187</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9356600176939693</v>
+        <v>-1.001366768181873</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.544513290593818</v>
+        <v>-2.644130601287096</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.64802159462433</v>
+        <v>1.588251208208364</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.5095349999166</v>
+        <v>-10.67380187613636</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.03666002020136</v>
+        <v>-1.102366770689265</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.544513290593818</v>
+        <v>-2.644130601287096</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.640802429722734</v>
+        <v>1.581032043306768</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.79733884445383</v>
+        <v>-10.96160572067359</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.158453748790233</v>
+        <v>-1.224160499278136</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.832317135131056</v>
+        <v>-2.931934445824334</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.461447932226415</v>
+        <v>1.401677545810449</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.85012500005416</v>
+        <v>-11.01439187627392</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.178452421191807</v>
+        <v>-1.24415917167971</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.927992621713453</v>
+        <v>-3.027609932406731</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.405158430115533</v>
+        <v>1.345388043699567</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.97616179342245</v>
+        <v>-11.14042866964221</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.226173409910008</v>
+        <v>-1.291880160397911</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.902740998903711</v>
+        <v>-3.002358309596989</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.423003132430493</v>
+        <v>1.363232746014527</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.92414627945364</v>
+        <v>-11.0884131556734</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.201376868636082</v>
+        <v>-1.267083619123985</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.902740998903711</v>
+        <v>-3.002358309596989</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.426993468116894</v>
+        <v>1.367223081700928</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.06581812117776</v>
+        <v>-11.23008499739752</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.259520832224472</v>
+        <v>-1.325227582712375</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.902740998903711</v>
+        <v>-3.002358309596989</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.425518241218153</v>
+        <v>1.365747854802186</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.01622727675292</v>
+        <v>-11.18049415297268</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.224631084289666</v>
+        <v>-1.290337834777569</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.853150154478877</v>
+        <v>-2.952767465172155</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.470326158037925</v>
+        <v>1.410555771621959</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.00341988374815</v>
+        <v>-11.16768675996791</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.232559260734439</v>
+        <v>-1.298266011222343</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.902005929487778</v>
+        <v>-3.001623240181055</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.427961559385902</v>
+        <v>1.368191172969935</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.77757473102874</v>
+        <v>-10.9418416072485</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.132642126610466</v>
+        <v>-1.19834887709837</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.860079253900614</v>
+        <v>-2.959696564593892</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.462696637774409</v>
+        <v>1.402926251358442</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.65299607469115</v>
+        <v>-10.81726295091091</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.08167151951937</v>
+        <v>-1.147378270007275</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.860079253900614</v>
+        <v>-2.959696564593892</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.463835782330468</v>
+        <v>1.404065395914501</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.70589136273543</v>
+        <v>-10.87015823895519</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.100195860574978</v>
+        <v>-1.165902611062881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.855123907812168</v>
+        <v>-2.954741218505446</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.469442764145643</v>
+        <v>1.409672377729676</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.63375818744755</v>
+        <v>-10.79802506366731</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.065608886221189</v>
+        <v>-1.131315636709092</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.855123907812168</v>
+        <v>-2.954741218505446</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.475176468384279</v>
+        <v>1.415406081968313</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.56239179483791</v>
+        <v>-10.72665867105767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.046799591571195</v>
+        <v>-1.112506342059099</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.78375751520252</v>
+        <v>-2.883374825895797</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.508259041556203</v>
+        <v>1.448488655140237</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.29855492763384</v>
+        <v>-10.4628218038536</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9511483260024742</v>
+        <v>-1.016855076490379</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.78375751520252</v>
+        <v>-2.883374825895797</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.498375560243296</v>
+        <v>1.438605173827329</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.03131312676544</v>
+        <v>-10.1955800029852</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8460861661544894</v>
+        <v>-0.9117929166423928</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.78375751520252</v>
+        <v>-2.883374825895797</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.496540999743922</v>
+        <v>1.436770613327955</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.933406088088947</v>
+        <v>-10.09767296430871</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8072236656573537</v>
+        <v>-0.8729304161452576</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.715771765341963</v>
+        <v>-2.815389076035241</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.537032134686795</v>
+        <v>1.477261748270828</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.90945254711299</v>
+        <v>-10.07371942333275</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7969737431214772</v>
+        <v>-0.8626804936093806</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.691818224366006</v>
+        <v>-2.791435535059283</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.552072765417863</v>
+        <v>1.492302379001896</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.645392608790193</v>
+        <v>-9.809659485009952</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7046100839541105</v>
+        <v>-0.7703168344420144</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.42775828604321</v>
+        <v>-2.527375596736487</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.697248412249788</v>
+        <v>1.637478025833822</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.938312985285355</v>
+        <v>-9.102579861505115</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4245652682124765</v>
+        <v>-0.49027201870038</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.42775828604321</v>
+        <v>-2.527375596736487</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.694461378589488</v>
+        <v>1.634690992173521</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.898128686919165</v>
+        <v>-9.062395563138924</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.408147924978159</v>
+        <v>-0.4738546754660624</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.387573987677019</v>
+        <v>-2.487191298370297</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.718915581497043</v>
+        <v>1.659145195081077</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.734728815979803</v>
+        <v>-8.898995692199563</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3434211553816571</v>
+        <v>-0.4091279058695609</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.224174116737657</v>
+        <v>-2.323791427430934</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.816322325281418</v>
+        <v>1.756551938865451</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.501247593750204</v>
+        <v>-8.665514469969963</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2421042376519651</v>
+        <v>-0.307810988139869</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.990692894508058</v>
+        <v>-2.090310205201336</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.96433548745703</v>
+        <v>1.904565101041063</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.35158120274269</v>
+        <v>-8.515848078962449</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1851298915619184</v>
+        <v>-0.2508366420498223</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.897789403265522</v>
+        <v>-1.9974067139588</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.017185371889592</v>
+        <v>1.957414985473625</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.219305729111802</v>
+        <v>-8.383572605331562</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1368522153625364</v>
+        <v>-0.2025589658504403</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.765513929634635</v>
+        <v>-1.865131240327913</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.091918142815151</v>
+        <v>2.032147756399184</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.028706054438649</v>
+        <v>-8.192972930658408</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0577972848056385</v>
+        <v>-0.1235040352935424</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.574914254961483</v>
+        <v>-1.67453156565476</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.209093008306679</v>
+        <v>2.149322621890713</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.779706255755068</v>
+        <v>-7.943973131974827</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.05470897589145274</v>
+        <v>-0.01099777459645113</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.574914254961483</v>
+        <v>-1.67453156565476</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.221999349530338</v>
+        <v>2.162228963114371</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.885296245528172</v>
+        <v>-8.049563121747932</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1155029496170079</v>
+        <v>-0.1812097001049118</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.680504244734587</v>
+        <v>-1.780121555427864</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.030669426067257</v>
+        <v>1.97089903965129</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.904031147646769</v>
+        <v>-8.068298023866529</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07445256858736027</v>
+        <v>-0.1401593190752641</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.686100254394718</v>
+        <v>-1.785717565087996</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.075856162148265</v>
+        <v>2.016085775732297</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.75609110623917</v>
+        <v>-7.920357982458929</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1351554747124881</v>
+        <v>-0.200862225200392</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.665779338486161</v>
+        <v>-1.765396649179438</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.968169789005231</v>
+        <v>1.908399402589265</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.703121583985181</v>
+        <v>-7.867388460204941</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.122681652064371</v>
+        <v>-0.1883884025522748</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.612809816232172</v>
+        <v>-1.712427126925449</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.991237516104146</v>
+        <v>1.93146712968818</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.659573177214491</v>
+        <v>-7.82384005343425</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.112222901451188</v>
+        <v>-0.1779296519390918</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.612809816232172</v>
+        <v>-1.712427126925449</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.984276904009053</v>
+        <v>1.924506517593087</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.417424783760633</v>
+        <v>-7.581691659980392</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.0009011896885016135</v>
+        <v>-0.06660794017640548</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.612809816232172</v>
+        <v>-1.712427126925449</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.998739258390196</v>
+        <v>1.93896887197423</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.309165646638111</v>
+        <v>-7.473432522857871</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.03693458561970209</v>
+        <v>-0.02877216486820178</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.612809816232172</v>
+        <v>-1.712427126925449</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.993271378849391</v>
+        <v>1.933500992433425</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.18587451182098</v>
+        <v>-7.35014138804074</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.08374913355713121</v>
+        <v>0.01804238306922779</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.489518681415041</v>
+        <v>-1.589135992108319</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.064744153750246</v>
+        <v>2.00497376733428</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.164725312917537</v>
+        <v>-7.328992189137296</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.099909791355834</v>
+        <v>0.03420304086793013</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.468369482511598</v>
+        <v>-1.567986793204875</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.085134651329638</v>
+        <v>2.025364264913671</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.920959870934093</v>
+        <v>-7.085226747153852</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1931966764962625</v>
+        <v>0.1274899260083586</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.468369482511598</v>
+        <v>-1.567986793204875</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.080915359676689</v>
+        <v>2.021144973260722</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.819197050656798</v>
+        <v>-6.983463926876557</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2360261185271963</v>
+        <v>0.1703193680392925</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.455150414119169</v>
+        <v>-1.554767724812447</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.090971114632162</v>
+        <v>2.031200728216195</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.569346656707723</v>
+        <v>-6.733613532927483</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3287083510905284</v>
+        <v>0.2630016006026246</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.455150414119169</v>
+        <v>-1.554767724812447</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.083713189615864</v>
+        <v>2.023942803199897</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.39345456424029</v>
+        <v>-6.55772144046005</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4026643115981501</v>
+        <v>0.3369575611102462</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.455150414119169</v>
+        <v>-1.554767724812447</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.087312313136513</v>
+        <v>2.027541926720546</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.222008101217827</v>
+        <v>-6.386274977437586</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4845704028616891</v>
+        <v>0.4188636523737856</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.283703951096706</v>
+        <v>-1.383321261789983</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.203507697004544</v>
+        <v>2.143737310588578</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.996975101549004</v>
+        <v>-6.161241977768763</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5736040803455156</v>
+        <v>0.5078973298576117</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.058670951427883</v>
+        <v>-1.158288262121161</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.337547974422135</v>
+        <v>2.277777588006168</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.933339359315069</v>
+        <v>-6.097606235534829</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6037531782934065</v>
+        <v>0.5380464278055026</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9950352091939484</v>
+        <v>-1.094652519887226</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.380424220816813</v>
+        <v>2.320653834400846</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.889577178009228</v>
+        <v>-6.053844054228987</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6024523095995389</v>
+        <v>0.536745559111635</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9950352091939484</v>
+        <v>-1.094652519887226</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.361618479600609</v>
+        <v>2.301848093184642</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.649146681204368</v>
+        <v>-5.813413557424127</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7003675849463602</v>
+        <v>0.6346608344584563</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7546047123890881</v>
+        <v>-0.8542220230823658</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.507619854308402</v>
+        <v>2.447849467892436</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.576904113033173</v>
+        <v>-5.741170989252932</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7331939260496583</v>
+        <v>0.6674871755617544</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7546047123890881</v>
+        <v>-0.8542220230823658</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.511549168143222</v>
+        <v>2.451778781727255</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.523905790751785</v>
+        <v>-5.688172666971544</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7550718388795534</v>
+        <v>0.6893650883916496</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6992684533871493</v>
+        <v>-0.798885764080427</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.545429507461725</v>
+        <v>2.485659121045759</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.415100905272058</v>
+        <v>-5.579367781491817</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7955918642914379</v>
+        <v>0.729885113803534</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6992684533871493</v>
+        <v>-0.798885764080427</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.542427578681719</v>
+        <v>2.482657192265752</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.195080107235047</v>
+        <v>-5.359346983454807</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8851792205168563</v>
+        <v>0.8194724700289524</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.558048608319169</v>
+        <v>-0.6576659190124468</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.628738522733121</v>
+        <v>2.568968136317155</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.06221241817177</v>
+        <v>-5.226479294391529</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9542204789439905</v>
+        <v>0.8885137284560867</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.558048608319169</v>
+        <v>-0.6576659190124468</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.644632705534945</v>
+        <v>2.584862319118978</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.942039334807271</v>
+        <v>-5.106306211027031</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.003435556730092</v>
+        <v>0.937728806242188</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4378755249546701</v>
+        <v>-0.5374928356479478</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.717882399993946</v>
+        <v>2.658112013577979</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.797367189707534</v>
+        <v>-4.961634065927293</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.071392517331427</v>
+        <v>1.005685766843523</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2932033798549327</v>
+        <v>-0.3928206905482104</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.814773789615228</v>
+        <v>2.755003403199261</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942099</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.857242017065226</v>
+        <v>-5.021508893284985</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.033480077789776</v>
+        <v>0.967773327301872</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3530782072126248</v>
+        <v>-0.4526955179059025</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.764886384602039</v>
+        <v>2.705115998186072</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.770442519286217</v>
+        <v>-4.934709395505976</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.090600370223946</v>
+        <v>1.024893619736042</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3530782072126248</v>
+        <v>-0.4526955179059025</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.787286877924605</v>
+        <v>2.727516491508638</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.772912225748023</v>
+        <v>-4.937179101967782</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.089684889012635</v>
+        <v>1.023978138524731</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3555479136744309</v>
+        <v>-0.4551652243677087</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.785877455420933</v>
+        <v>2.726107069004966</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.841282412072033</v>
+        <v>-5.005549288291792</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.073343736957733</v>
+        <v>1.007636986469829</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.4458895253314937</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.802449797317364</v>
+        <v>2.742679410901398</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.949820592988167</v>
+        <v>-5.114087469207926</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.020365173223171</v>
+        <v>0.954658422735267</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.4458895253314937</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.792886505949256</v>
+        <v>2.733116119533289</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.980813752316872</v>
+        <v>-5.145080628536632</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8326774745320755</v>
+        <v>0.7669707240441719</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.4458895253314937</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.617596070989642</v>
+        <v>2.557825684573676</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.805339492524404</v>
+        <v>-4.969606368744163</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9074344104408507</v>
+        <v>0.8417276599529471</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.4458895253314937</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.62216330298143</v>
+        <v>2.562392916565464</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.916275745165652</v>
+        <v>-5.080542621385412</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8388019381455583</v>
+        <v>0.7730951876576544</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.346272214638216</v>
+        <v>-0.4458895253314937</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.597905331742637</v>
+        <v>2.538134945326671</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77321029711129</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.924557819310711</v>
+        <v>-5.08882469553047</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8386204937074404</v>
+        <v>0.7729137432195365</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3545542887832744</v>
+        <v>-0.4541715994765521</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.596067472475508</v>
+        <v>2.536297086059541</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264159</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.864705200106988</v>
+        <v>-5.028972076326747</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.872733927821062</v>
+        <v>0.8070271773331581</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3545542887832744</v>
+        <v>-0.4541715994765521</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.60623985890764</v>
+        <v>2.546469472491673</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742295</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.77846173708061</v>
+        <v>-4.942728613300369</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9021775836054735</v>
+        <v>0.8364708331175696</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3545542887832744</v>
+        <v>-0.4541715994765521</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.6011861294815</v>
+        <v>2.541415743065534</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.82376855647959</v>
+        <v>-4.988035432699349</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8758306312904072</v>
+        <v>0.8101238808025033</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3953644517925052</v>
+        <v>-0.4949817624857829</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.568475807120488</v>
+        <v>2.508705420704521</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.852801661181891</v>
+        <v>-5.01706853740165</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8647692624425882</v>
+        <v>0.7990625119546846</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3953644517925052</v>
+        <v>-0.4949817624857829</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.569027680153589</v>
+        <v>2.509257293737623</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.759991179731031</v>
+        <v>-4.984070864682044</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8311661469142977</v>
+        <v>0.7415342729338925</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3025539703416458</v>
+        <v>-0.4619840897661766</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.55398666091547</v>
+        <v>2.458328589260752</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.804380649060459</v>
+        <v>-5.028460334011472</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8152838351071274</v>
+        <v>0.7256519611267223</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3469434396710735</v>
+        <v>-0.5063735590956042</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.529226455242414</v>
+        <v>2.433568383587696</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.691709430824209</v>
+        <v>-4.915789115775222</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8554280309133506</v>
+        <v>0.7657961569329454</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2342722214348233</v>
+        <v>-0.393702340859354</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.591904894695888</v>
+        <v>2.496246823041169</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.579332429641536</v>
+        <v>-4.803412114592549</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.905870127217087</v>
+        <v>0.8162382532366819</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2342722214348233</v>
+        <v>-0.393702340859354</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.597396190526555</v>
+        <v>2.501738118871836</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.777566998528266</v>
+        <v>-5.001646683479279</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8380735014309337</v>
+        <v>0.7484416274505286</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4325067903215539</v>
+        <v>-0.5919369097460846</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.489952650963056</v>
+        <v>2.394294579308337</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.860568279553545</v>
+        <v>-5.084647964504558</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6432287090214754</v>
+        <v>0.5535968350410703</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4510776748487276</v>
+        <v>-0.6105077942732584</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.317165840247405</v>
+        <v>2.221507768592686</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.969182357996877</v>
+        <v>-5.19326204294789</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7199327383633487</v>
+        <v>0.6303008643829435</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4510776748487276</v>
+        <v>-0.6105077942732584</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.43731550096661</v>
+        <v>2.341657429311892</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.055780940977979</v>
+        <v>-5.279860625928992</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6998063312732303</v>
+        <v>0.6101744572928252</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4510776748487276</v>
+        <v>-0.6105077942732584</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.451828527068933</v>
+        <v>2.356170455414215</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.017397278419828</v>
+        <v>-5.241476963370841</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7125792376388596</v>
+        <v>0.6229473636584544</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4126940122905765</v>
+        <v>-0.5721241317151072</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.472278165946193</v>
+        <v>2.376620094291474</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.840280948384662</v>
+        <v>-5.064360633335675</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.780154798498228</v>
+        <v>0.6905229245178228</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4126940122905765</v>
+        <v>-0.5721241317151072</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.469007194791494</v>
+        <v>2.373349123136776</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.885373193218208</v>
+        <v>-5.109452878169221</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7628012923267227</v>
+        <v>0.6731694183463177</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4745900554599662</v>
+        <v>-0.634020174884497</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.432552960651774</v>
+        <v>2.336894888997055</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.70599777197944</v>
+        <v>-4.930077456930453</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8283384361286441</v>
+        <v>0.7387065621482389</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3178132972892476</v>
+        <v>-0.4772434167137783</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.520405990860619</v>
+        <v>2.424747919205901</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.751011985500046</v>
+        <v>-4.975091670451059</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7911402060519916</v>
+        <v>0.7015083320715865</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3481621926038522</v>
+        <v>-0.507592312028383</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.483004109003446</v>
+        <v>2.387346037348728</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.018016495772481</v>
+        <v>-5.242096180723494</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6900299642819632</v>
+        <v>0.600398090301558</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5425252306468007</v>
+        <v>-0.7019553500713316</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.372077848516623</v>
+        <v>2.276419776861904</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.119214277209654</v>
+        <v>-5.343293962160667</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6487547736035957</v>
+        <v>0.5591228996231905</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6109340441921198</v>
+        <v>-0.7703641636166507</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.330236482285933</v>
+        <v>2.234578410631214</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.086738691038882</v>
+        <v>-5.310818375989895</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6593449696262215</v>
+        <v>0.5697130956458163</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6109340441921198</v>
+        <v>-0.7703641636166507</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.327836443840249</v>
+        <v>2.232178372185531</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.067700563331584</v>
+        <v>-5.291780248282597</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6634849399173852</v>
+        <v>0.57385306593698</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6691176555233144</v>
+        <v>-0.8285477749478453</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.289450996249778</v>
+        <v>2.193792924595059</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.098827194482203</v>
+        <v>-5.322906879433216</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8286161563958183</v>
+        <v>0.7389842824154131</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6691176555233144</v>
+        <v>-0.8285477749478453</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.467032865188458</v>
+        <v>2.37137479353374</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.151147575082994</v>
+        <v>-5.375227260034007</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.808521333141635</v>
+        <v>0.7188894591612298</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6341707955144422</v>
+        <v>-0.7936009149389731</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.488834310179915</v>
+        <v>2.393176238525196</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.171404873611952</v>
+        <v>-5.395484558562965</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.806426944126978</v>
+        <v>0.7167950701465728</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6341707955144422</v>
+        <v>-0.7936009149389731</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.494842840576841</v>
+        <v>2.399184768922122</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.02366190337695</v>
+        <v>-5.247741588327963</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9446767800130007</v>
+        <v>0.8550449060325955</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4663634382795591</v>
+        <v>-0.62579355770409</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.674679902709793</v>
+        <v>2.579021831055075</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.125676585908171</v>
+        <v>-5.349756270859184</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9066645285319934</v>
+        <v>0.8170326545515882</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4663634382795591</v>
+        <v>-0.62579355770409</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.677473524241274</v>
+        <v>2.581815452586556</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394733</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.119523879855387</v>
+        <v>-5.3436035648064</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9097879593447655</v>
+        <v>0.8201560853643604</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4602107322267748</v>
+        <v>-0.6196408516513057</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.681827496264603</v>
+        <v>2.586169424609884</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.136333178005889</v>
+        <v>-5.360412862956902</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.902144716824675</v>
+        <v>0.8125128428442698</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4770200303772764</v>
+        <v>-0.6364501498018074</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.670822394114412</v>
+        <v>2.575164322459694</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.86736263679843</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.074035179229766</v>
+        <v>-5.298114864180779</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9933994701319446</v>
+        <v>0.9037675961515395</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4770200303772764</v>
+        <v>-0.6364501498018074</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.737157947911233</v>
+        <v>2.641499876256515</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.872244981564609</v>
+        <v>-5.096324666515621</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7826964215874059</v>
+        <v>0.6930645476070008</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.279001838208122</v>
+        <v>-0.438431957632653</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.564549735602124</v>
+        <v>2.468891663947405</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.812354299922015</v>
+        <v>-5.036433984873028</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8769429265666184</v>
+        <v>0.7873110525862135</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2191111565655285</v>
+        <v>-0.3785412759900595</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.670774376909855</v>
+        <v>2.575116305255136</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.91009484454699</v>
+        <v>-5.134174529498003</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8524744448326724</v>
+        <v>0.7628425708522673</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2350004346985087</v>
+        <v>-0.3944305541230397</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.67586854614611</v>
+        <v>2.580210474491392</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.086432604669919</v>
+        <v>-5.310512289620932</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7804753216081721</v>
+        <v>0.6908434476277669</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4113381948214381</v>
+        <v>-0.5707683142459691</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.568601870897024</v>
+        <v>2.472943799242306</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.014886281893042</v>
+        <v>-5.238965966844055</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8075854687588517</v>
+        <v>0.7179535947784466</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4113381948214381</v>
+        <v>-0.5707683142459691</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.567093488936953</v>
+        <v>2.471435417282235</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.970513150254473</v>
+        <v>-5.194592835205486</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8251975888497154</v>
+        <v>0.7355657148693102</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3669650631828695</v>
+        <v>-0.5263951826074005</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.59358023535553</v>
+        <v>2.497922163700812</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.962559179959701</v>
+        <v>-5.186638864910714</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8283791769676241</v>
+        <v>0.7387473029872189</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3669650631828695</v>
+        <v>-0.5263951826074005</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.59358023535553</v>
+        <v>2.497922163700812</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.914903449398645</v>
+        <v>-5.138983134349658</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8538232262198511</v>
+        <v>0.7641913522394459</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3193093326218139</v>
+        <v>-0.4787394520463448</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.628555430719969</v>
+        <v>2.53289735906525</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.787219139604349</v>
+        <v>-5.011298824555362</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9097893235122945</v>
+        <v>0.8201574495318895</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1916250228275174</v>
+        <v>-0.3510551422520484</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.710058389971271</v>
+        <v>2.614400318316553</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82883791131455</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.847885730006738</v>
+        <v>-5.07196541495775</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8722773598272113</v>
+        <v>0.7826454858468059</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2733233395460511</v>
+        <v>-0.432753458970582</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.647794072416023</v>
+        <v>2.552136000761305</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.782891870073092</v>
+        <v>-5.006971555024105</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.902372606411298</v>
+        <v>0.8127407324308928</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2464927249418957</v>
+        <v>-0.4059228443664267</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.667990143789145</v>
+        <v>2.572332072134426</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.88365050583009</v>
+        <v>-5.107730190781103</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8662300917395769</v>
+        <v>0.7765982177591715</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3353182936689011</v>
+        <v>-0.4947484130934321</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.61885574218402</v>
+        <v>2.523197670529301</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.83944766874419</v>
+        <v>-5.063527353695203</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8897908291017742</v>
+        <v>0.8001589551213688</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2911154565830007</v>
+        <v>-0.4505455760075316</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.651257046963397</v>
+        <v>2.555598975308679</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.876426696407632</v>
+        <v>-5.100506381358645</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8734092185056446</v>
+        <v>0.7837773445252396</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.2541415547916702</v>
+        <v>-0.4135716742162011</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.671851388507443</v>
+        <v>2.576193316852724</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.896484775272473</v>
+        <v>-5.120564460223486</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9166337521427481</v>
+        <v>0.8270018781623429</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.2541415547916702</v>
+        <v>-0.4135716742162011</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.723099153690482</v>
+        <v>2.627441082035764</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.856554102094583</v>
+        <v>-5.080633787045596</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9310467260081574</v>
+        <v>0.8414148520277522</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.2142108816137798</v>
+        <v>-0.3736410010383108</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.74549826219147</v>
+        <v>2.649840190536751</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232398</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.816083754531878</v>
+        <v>-5.040163439482891</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9421830932715092</v>
+        <v>0.852551219291104</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.1737405340510749</v>
+        <v>-0.3331706534756058</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.764728698967363</v>
+        <v>2.669070627312645</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.750859573404672</v>
+        <v>-4.974939258355685</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9854601698150964</v>
+        <v>0.8958282958346913</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1085163529238692</v>
+        <v>-0.2679464723484002</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.821050611736391</v>
+        <v>2.725392540081673</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.801353863761729</v>
+        <v>-5.025433548712742</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9612234259715542</v>
+        <v>0.8715915519911492</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.1535370900499435</v>
+        <v>-0.3129672094744744</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.789999141760027</v>
+        <v>2.694341070105309</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.821465519796437</v>
+        <v>-5.04554520474745</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9544355558889113</v>
+        <v>0.8648036819085059</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.1425097450525243</v>
+        <v>-0.3019398644770552</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.797872341089719</v>
+        <v>2.702214269435</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.919146099069083</v>
+        <v>-5.143225784020096</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.075921095201063</v>
+        <v>0.9862892212206584</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.2532129403927131</v>
+        <v>-0.412643059817244</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.892008194906817</v>
+        <v>2.796350123252098</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.89535453046294</v>
+        <v>-5.119434215413953</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.205550631861338</v>
+        <v>1.115918757880932</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.2294213717865708</v>
+        <v>-0.3888514912111017</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.026396045288319</v>
+        <v>2.930737973633601</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175601</v>
+        <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.932108949024663</v>
+        <v>-5.156188633975676</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.182556840450508</v>
+        <v>1.092924966470103</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.2294213717865708</v>
+        <v>-0.3888514912111017</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.018104021302178</v>
+        <v>2.92244594964746</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654188</v>
+        <v>3.803426852654191</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.927774645967615</v>
+        <v>-5.151854330918628</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.182483757257107</v>
+        <v>1.092851883276701</v>
       </c>
       <c r="F1994" t="n">
-        <v>-0.07777126846736687</v>
+        <v>-0.2372013878918978</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.10728727887748</v>
+        <v>3.011629207222761</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.809008178316421</v>
+        <v>3.58026641875751</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.206924726045854</v>
+        <v>3.103969179931511</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.927774645967615</v>
+        <v>-5.151854330918628</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.182483757257107</v>
+        <v>1.092851883276701</v>
       </c>
       <c r="F1995" t="n">
-        <v>-0.07777126846736687</v>
+        <v>-0.2372013878918978</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.199988523032221</v>
+        <v>3.097032976917879</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-702.5%</t>
+          <t>-692.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-51.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.6%</t>
+          <t>449.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-676.8%</t>
+          <t>-645.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.4%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-41.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-43.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-266.9%</t>
+          <t>-252.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-316.1%</t>
+          <t>-306.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-165.5%</t>
+          <t>-163.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.7%</t>
+          <t>-203.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-190.0%</t>
+          <t>-184.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-136.3%</t>
+          <t>-116.4%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.0698802420482833</v>
+        <v>0.1694975527415611</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.150165844618509</v>
+        <v>3.19001276889582</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.557545687297374</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.057097584491367</v>
+        <v>4.116867970907334</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1672512498015118</v>
+        <v>-0.06763393910823401</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.090254332376132</v>
+        <v>3.130101256653444</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.557545687297374</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.092038668988909</v>
+        <v>4.151809055404875</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1622136590739253</v>
+        <v>-0.06259634838064748</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.090846808852505</v>
+        <v>3.130693733129816</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.613190143563691</v>
+        <v>1.712807454256969</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.124002782934037</v>
+        <v>4.183773169350004</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.419407693781982</v>
+        <v>-0.3197903830887042</v>
       </c>
       <c r="E1841" t="n">
-        <v>2.966715576593019</v>
+        <v>3.006562500870331</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.355996108855634</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.948432743732941</v>
+        <v>4.008203130148907</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.4851750838313941</v>
+        <v>-0.3855577731381163</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.941426229703725</v>
+        <v>2.981273153981036</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.355996108855634</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.94945035286341</v>
+        <v>4.009220739279377</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.6904197608886387</v>
+        <v>-0.5908024501953608</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.849956390868583</v>
+        <v>2.889803315145894</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.355996108855634</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.940078384851166</v>
+        <v>3.999848771267133</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.7721916613163904</v>
+        <v>-0.6725743506231125</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.80733035665272</v>
+        <v>2.847177280930031</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.383031682261771</v>
+        <v>1.482648992955049</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.946382454850086</v>
+        <v>4.006152841266053</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8394007691882681</v>
+        <v>-0.7397834584949903</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.785212030337672</v>
+        <v>2.825058954614982</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.383031682261771</v>
+        <v>1.482648992955049</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.951147771683789</v>
+        <v>4.010918158099756</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.04696655357988</v>
+        <v>-0.9473492428866022</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.700010512700267</v>
+        <v>2.739857436977578</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.175465897870159</v>
+        <v>1.275083208563437</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.824433097168062</v>
+        <v>3.884203483584028</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.464720577126717</v>
+        <v>-1.365103266433439</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.530835794786595</v>
+        <v>2.570682719063906</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.7577118743233217</v>
+        <v>0.8573291850165997</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.571707574545023</v>
+        <v>3.631477960960989</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.754852243732149</v>
+        <v>-1.65523493303887</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.414649344743344</v>
+        <v>2.454496269020656</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.7817936690635016</v>
+        <v>0.8814109797567796</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.586022867988052</v>
+        <v>3.645793254404019</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.962856302085226</v>
+        <v>-1.863238991391948</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.336339865956039</v>
+        <v>2.37618679023335</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.7817936690635016</v>
+        <v>0.8814109797567796</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.590915012541978</v>
+        <v>3.650685398957944</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.174268722973201</v>
+        <v>-2.074651412279923</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.246856353938837</v>
+        <v>2.286703278216148</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.5703812481755265</v>
+        <v>0.6699985588688046</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.459149016347181</v>
+        <v>3.518919402763148</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.540337450117854</v>
+        <v>-2.440720139424576</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.093513162387425</v>
+        <v>2.133360086664736</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2043125210308738</v>
+        <v>0.3039298317241519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.232592079366838</v>
+        <v>3.292362465782805</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.748828231569538</v>
+        <v>-2.649210920876261</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.030455139545519</v>
+        <v>2.07030206382283</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.004178260420810598</v>
+        <v>0.09543905027246746</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.127835900234596</v>
+        <v>3.187606286650563</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.99602941633476</v>
+        <v>-2.896412105641482</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.939673416048</v>
+        <v>1.97952034032531</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.01597509307800182</v>
+        <v>0.1155924037712799</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.148026662742452</v>
+        <v>3.207797049158418</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.488414444358857</v>
+        <v>-3.388797133665579</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.743825796882093</v>
+        <v>1.783672721159404</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4764099349460949</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.853702037971726</v>
+        <v>2.913472424387693</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.873594835288929</v>
+        <v>-3.773977524595651</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.588296179322927</v>
+        <v>1.628143103600238</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4764099349460949</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.852244576784589</v>
+        <v>2.912014963200556</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.217277608515592</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.452592193486878</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5843159869733131</v>
+        <v>-0.484698676280035</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.789270069022875</v>
+        <v>2.849040455438841</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.423789385402613</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.366093541388327</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7908277638603346</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.661469061546919</v>
+        <v>2.721239447962886</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.743133460483115</v>
+        <v>-4.643516149789837</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.240128838056386</v>
+        <v>1.279975762333697</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7908277638603346</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.663241988247179</v>
+        <v>2.723012374663146</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.174939253632902</v>
+        <v>-5.075321942939625</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.053739408263876</v>
+        <v>1.093586332541187</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9272452603016016</v>
+        <v>-0.8276279496083235</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.567724377849823</v>
+        <v>2.62749476426579</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.409633247765455</v>
+        <v>-5.310015937072177</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9481465856129452</v>
+        <v>0.9879935098902566</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9209089930723464</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.559810913189467</v>
+        <v>2.619581299605434</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.745295894995907</v>
+        <v>-5.64567858430263</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8124621183767293</v>
+        <v>0.8523090426540407</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9209089930723464</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.558391504845432</v>
+        <v>2.618161891261399</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.108922139896221</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6734991806508455</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.019130629939472</v>
+        <v>-0.9195133192461942</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.505946082959398</v>
+        <v>2.565716469375365</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.474049522534967</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5267027426011786</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.315441414238485</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.327414127385822</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.882638299715646</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3620287757436658</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.724030191419163</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.081022405092174</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.159214400031479</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2465837680887937</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.724030191419163</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.076207837563635</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.575606274318476</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.07802106898287198</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.724030191419163</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.074201888172512</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.846372363411121</v>
+        <v>-7.746755052717844</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.02002667598550723</v>
+        <v>0.01982024829180373</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.724030191419163</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.084460578841191</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.19224718539593</v>
+        <v>-8.092629874702652</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1622770396337354</v>
+        <v>-0.1224301153564245</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.724030191419163</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.080560143986887</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.355827063580314</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2293040708524883</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.724030191419163</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.078965064041888</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.652488405390512</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3441896316473594</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.792773327153042</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.041498158530768</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.839208113699815</v>
+        <v>-8.739590803006537</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4229038195054837</v>
+        <v>-0.3830568952281723</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.792773327153042</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.037471853996365</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.222209502442446</v>
+        <v>-9.122592191749169</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5762064763241201</v>
+        <v>-0.5363595520468092</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.792773327153042</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.037369752674781</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.404079293427481</v>
+        <v>-9.304461982734203</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6463828767467037</v>
+        <v>-0.6065359524693927</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.974643118138077</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.93081939405519</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.763609615931482</v>
+        <v>-9.663992305238205</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7848447024502541</v>
+        <v>-0.7449977781729431</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.974643118138077</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.936169697353241</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.813958679385705</v>
+        <v>-9.714341368692427</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7970683078747656</v>
+        <v>-0.7572213835974546</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.024992181592299</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.913876279237885</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.911577956807101</v>
+        <v>-9.811960646113823</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8330742682215551</v>
+        <v>-0.7932273439442441</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.122611459013695</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.858346463406816</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.05910404481274</v>
+        <v>-9.959486734119466</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8891911471022405</v>
+        <v>-0.8493442228249291</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.270137547019339</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.772724366925002</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.26336222014261</v>
+        <v>-10.16374490944933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9653812201155434</v>
+        <v>-0.925534295838232</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.397776491633328</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.701654197275251</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.33769519640277</v>
+        <v>-10.23807788570949</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9906318561351726</v>
+        <v>-0.9507849318578621</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.542476015568</v>
+        <v>-2.442858704874723</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.619317037398883</v>
+        <v>1.67908742381485</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.26422536473532</v>
+        <v>-10.16460805404204</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9458722219747724</v>
+        <v>-0.906025297697461</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.469006183900552</v>
+        <v>-2.369388873207274</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.678770637892773</v>
+        <v>1.73854102430874</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.43934978212187</v>
+        <v>-10.33973247142859</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.001366768181873</v>
+        <v>-0.9615198439045614</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.644130601287096</v>
+        <v>-2.544513290593818</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.588251208208364</v>
+        <v>1.64802159462433</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.67380187613636</v>
+        <v>-10.57418456544308</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.102366770689265</v>
+        <v>-1.062519846411953</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.644130601287096</v>
+        <v>-2.544513290593818</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.581032043306768</v>
+        <v>1.640802429722734</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.96160572067359</v>
+        <v>-10.86198840998032</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.224160499278136</v>
+        <v>-1.184313575000826</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.931934445824334</v>
+        <v>-2.832317135131056</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.401677545810449</v>
+        <v>1.461447932226415</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.01439187627392</v>
+        <v>-10.91477456558064</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.24415917167971</v>
+        <v>-1.2043122474024</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.027609932406731</v>
+        <v>-2.927992621713453</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.345388043699567</v>
+        <v>1.405158430115533</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.14042866964221</v>
+        <v>-11.04081135894893</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.291880160397911</v>
+        <v>-1.252033236120601</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.002358309596989</v>
+        <v>-2.902740998903711</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.363232746014527</v>
+        <v>1.423003132430493</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.0884131556734</v>
+        <v>-10.98879584498012</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.267083619123985</v>
+        <v>-1.227236694846675</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.002358309596989</v>
+        <v>-2.902740998903711</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.367223081700928</v>
+        <v>1.426993468116894</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.23008499739752</v>
+        <v>-11.13046768670424</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.325227582712375</v>
+        <v>-1.285380658435065</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.002358309596989</v>
+        <v>-2.902740998903711</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.365747854802186</v>
+        <v>1.425518241218153</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.18049415297268</v>
+        <v>-11.08087684227941</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.290337834777569</v>
+        <v>-1.250490910500258</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.952767465172155</v>
+        <v>-2.853150154478877</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.410555771621959</v>
+        <v>1.470326158037925</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.16768675996791</v>
+        <v>-11.06806944927463</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.298266011222343</v>
+        <v>-1.258419086945032</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.001623240181055</v>
+        <v>-2.902005929487778</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.368191172969935</v>
+        <v>1.427961559385902</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.9418416072485</v>
+        <v>-10.84222429655522</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.19834887709837</v>
+        <v>-1.158501952821058</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.959696564593892</v>
+        <v>-2.860079253900614</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.402926251358442</v>
+        <v>1.462696637774409</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.81726295091091</v>
+        <v>-10.71764564021763</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.147378270007275</v>
+        <v>-1.107531345729962</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.959696564593892</v>
+        <v>-2.860079253900614</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.404065395914501</v>
+        <v>1.463835782330468</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.87015823895519</v>
+        <v>-10.77054092826191</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.165902611062881</v>
+        <v>-1.12605568678557</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.954741218505446</v>
+        <v>-2.855123907812168</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.409672377729676</v>
+        <v>1.469442764145643</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.79802506366731</v>
+        <v>-10.69840775297403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.131315636709092</v>
+        <v>-1.091468712431781</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.954741218505446</v>
+        <v>-2.855123907812168</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.415406081968313</v>
+        <v>1.475176468384279</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.72665867105767</v>
+        <v>-10.62704136036439</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.112506342059099</v>
+        <v>-1.072659417781787</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.883374825895797</v>
+        <v>-2.78375751520252</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.448488655140237</v>
+        <v>1.508259041556203</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.4628218038536</v>
+        <v>-10.36320449316032</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.016855076490379</v>
+        <v>-0.9770081522130662</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.883374825895797</v>
+        <v>-2.78375751520252</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.438605173827329</v>
+        <v>1.498375560243296</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.1955800029852</v>
+        <v>-10.09596269229192</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9117929166423928</v>
+        <v>-0.8719459923650814</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.883374825895797</v>
+        <v>-2.78375751520252</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.436770613327955</v>
+        <v>1.496540999743922</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.09767296430871</v>
+        <v>-9.998055653615427</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8729304161452576</v>
+        <v>-0.8330834918679457</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.815389076035241</v>
+        <v>-2.715771765341963</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.477261748270828</v>
+        <v>1.537032134686795</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.07371942333275</v>
+        <v>-9.97410211263947</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8626804936093806</v>
+        <v>-0.8228335693320692</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.791435535059283</v>
+        <v>-2.691818224366006</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.492302379001896</v>
+        <v>1.552072765417863</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.809659485009952</v>
+        <v>-9.710042174316673</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7703168344420144</v>
+        <v>-0.7304699101647025</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.527375596736487</v>
+        <v>-2.42775828604321</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.637478025833822</v>
+        <v>1.697248412249788</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.102579861505115</v>
+        <v>-9.002962550811835</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.49027201870038</v>
+        <v>-0.4504250944230686</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.527375596736487</v>
+        <v>-2.42775828604321</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.634690992173521</v>
+        <v>1.694461378589488</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.062395563138924</v>
+        <v>-8.962778252445645</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4738546754660624</v>
+        <v>-0.434007751188751</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.487191298370297</v>
+        <v>-2.387573987677019</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.659145195081077</v>
+        <v>1.718915581497043</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.898995692199563</v>
+        <v>-8.799378381506283</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4091279058695609</v>
+        <v>-0.3692809815922491</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.323791427430934</v>
+        <v>-2.224174116737657</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.756551938865451</v>
+        <v>1.816322325281418</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.665514469969963</v>
+        <v>-8.565897159276684</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.307810988139869</v>
+        <v>-0.2679640638625571</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.090310205201336</v>
+        <v>-1.990692894508058</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.904565101041063</v>
+        <v>1.96433548745703</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.515848078962449</v>
+        <v>-8.41623076826917</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2508366420498223</v>
+        <v>-0.2109897177725104</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.9974067139588</v>
+        <v>-1.897789403265522</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.957414985473625</v>
+        <v>2.017185371889592</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.383572605331562</v>
+        <v>-8.283955294638282</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2025589658504403</v>
+        <v>-0.1627120415731285</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.865131240327913</v>
+        <v>-1.765513929634635</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.032147756399184</v>
+        <v>2.091918142815151</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.192972930658408</v>
+        <v>-8.142928444636439</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1235040352935424</v>
+        <v>-0.1034862408847546</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.67453156565476</v>
+        <v>-1.643852229924918</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.149322621890713</v>
+        <v>2.167730223328618</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.943973131974827</v>
+        <v>-7.893928645952858</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.01099777459645113</v>
+        <v>0.009020019812336688</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.67453156565476</v>
+        <v>-1.643852229924918</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.162228963114371</v>
+        <v>2.180636564552277</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.049563121747932</v>
+        <v>-7.999518635725963</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1812097001049118</v>
+        <v>-0.161191905696124</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.780121555427864</v>
+        <v>-1.749442219698022</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.97089903965129</v>
+        <v>1.989306641089196</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.068298023866529</v>
+        <v>-8.01825353784456</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1401593190752641</v>
+        <v>-0.1201415246664763</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.785717565087996</v>
+        <v>-1.755038229358153</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.016085775732297</v>
+        <v>2.034493377170203</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.920357982458929</v>
+        <v>-7.87031349643696</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.200862225200392</v>
+        <v>-0.1808444307916042</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.765396649179438</v>
+        <v>-1.734717313449596</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.908399402589265</v>
+        <v>1.92680700402717</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.867388460204941</v>
+        <v>-7.817343974182972</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1883884025522748</v>
+        <v>-0.168370608143487</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.712427126925449</v>
+        <v>-1.681747791195607</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.93146712968818</v>
+        <v>1.949874731126085</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.82384005343425</v>
+        <v>-7.773795567412281</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1779296519390918</v>
+        <v>-0.157911857530304</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.712427126925449</v>
+        <v>-1.681747791195607</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.924506517593087</v>
+        <v>1.942914119030992</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.581691659980392</v>
+        <v>-7.531647173958423</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.06660794017640548</v>
+        <v>-0.04659014576761766</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.712427126925449</v>
+        <v>-1.681747791195607</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.93896887197423</v>
+        <v>1.957376473412135</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.473432522857871</v>
+        <v>-7.423388036835902</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.02877216486820178</v>
+        <v>-0.008754370459413963</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.712427126925449</v>
+        <v>-1.681747791195607</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.933500992433425</v>
+        <v>1.95190859387133</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.35014138804074</v>
+        <v>-7.300096902018771</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.01804238306922779</v>
+        <v>0.03806017747801516</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.589135992108319</v>
+        <v>-1.558456656378477</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.00497376733428</v>
+        <v>2.023381368772185</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.328992189137296</v>
+        <v>-7.278947703115327</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.03420304086793013</v>
+        <v>0.05422083527671795</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.567986793204875</v>
+        <v>-1.537307457475033</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.025364264913671</v>
+        <v>2.043771866351577</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.085226747153852</v>
+        <v>-7.035182261131883</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1274899260083586</v>
+        <v>0.147507720417146</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.567986793204875</v>
+        <v>-1.537307457475033</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.021144973260722</v>
+        <v>2.039552574698627</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.983463926876557</v>
+        <v>-6.933419440854588</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1703193680392925</v>
+        <v>0.1903371624480803</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.554767724812447</v>
+        <v>-1.524088389082604</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.031200728216195</v>
+        <v>2.049608329654101</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.733613532927483</v>
+        <v>-6.683569046905514</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2630016006026246</v>
+        <v>0.2830193950114119</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.554767724812447</v>
+        <v>-1.524088389082604</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.023942803199897</v>
+        <v>2.042350404637802</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.55772144046005</v>
+        <v>-6.507676954438081</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3369575611102462</v>
+        <v>0.356975355519034</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.554767724812447</v>
+        <v>-1.524088389082604</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.027541926720546</v>
+        <v>2.045949528158451</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.386274977437586</v>
+        <v>-6.336230491415617</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4188636523737856</v>
+        <v>0.438881446782573</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.383321261789983</v>
+        <v>-1.352641926060141</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.143737310588578</v>
+        <v>2.162144912026483</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.161241977768763</v>
+        <v>-6.111197491746794</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5078973298576117</v>
+        <v>0.5279151242663991</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.158288262121161</v>
+        <v>-1.127608926391318</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.277777588006168</v>
+        <v>2.296185189444074</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.097606235534829</v>
+        <v>-6.04756174951286</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5380464278055026</v>
+        <v>0.5580642222142904</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.094652519887226</v>
+        <v>-1.063973184157384</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.320653834400846</v>
+        <v>2.339061435838752</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.053844054228987</v>
+        <v>-6.003799568207018</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.536745559111635</v>
+        <v>0.5567633535204228</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.094652519887226</v>
+        <v>-1.063973184157384</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.301848093184642</v>
+        <v>2.320255694622547</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.813413557424127</v>
+        <v>-5.763369071402158</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6346608344584563</v>
+        <v>0.6546786288672442</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8542220230823658</v>
+        <v>-0.8235426873525236</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.447849467892436</v>
+        <v>2.466257069330341</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.741170989252932</v>
+        <v>-5.691126503230963</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6674871755617544</v>
+        <v>0.6875049699705422</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8542220230823658</v>
+        <v>-0.8235426873525236</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.451778781727255</v>
+        <v>2.470186383165161</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.688172666971544</v>
+        <v>-5.638128180949575</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6893650883916496</v>
+        <v>0.7093828828004374</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.798885764080427</v>
+        <v>-0.7682064283505847</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.485659121045759</v>
+        <v>2.504066722483664</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.579367781491817</v>
+        <v>-5.529323295469848</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.729885113803534</v>
+        <v>0.7499029082123219</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.798885764080427</v>
+        <v>-0.7682064283505847</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.482657192265752</v>
+        <v>2.501064793703658</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.359346983454807</v>
+        <v>-5.309302497432838</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8194724700289524</v>
+        <v>0.8394902644377402</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6576659190124468</v>
+        <v>-0.6269865832826045</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.568968136317155</v>
+        <v>2.58737573775506</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.226479294391529</v>
+        <v>-5.17643480836956</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8885137284560867</v>
+        <v>0.9085315228648745</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6576659190124468</v>
+        <v>-0.6269865832826045</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.584862319118978</v>
+        <v>2.603269920556883</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.106306211027031</v>
+        <v>-5.056261725005061</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.937728806242188</v>
+        <v>0.9577466006509758</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5374928356479478</v>
+        <v>-0.5068134999181055</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.658112013577979</v>
+        <v>2.676519615015884</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.961634065927293</v>
+        <v>-4.911589579905324</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.005685766843523</v>
+        <v>1.025703561252311</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3928206905482104</v>
+        <v>-0.3621413548183681</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.755003403199261</v>
+        <v>2.773411004637167</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.021508893284985</v>
+        <v>-4.971464407263016</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.967773327301872</v>
+        <v>0.9877911217106594</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4526955179059025</v>
+        <v>-0.4220161821760602</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.705115998186072</v>
+        <v>2.723523599623977</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.934709395505976</v>
+        <v>-4.884664909484007</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.024893619736042</v>
+        <v>1.044911414144829</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4526955179059025</v>
+        <v>-0.4220161821760602</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.727516491508638</v>
+        <v>2.745924092946543</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.937179101967782</v>
+        <v>-4.887134615945813</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.023978138524731</v>
+        <v>1.043995932933519</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4551652243677087</v>
+        <v>-0.4244858886378664</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.726107069004966</v>
+        <v>2.744514670442872</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.005549288291792</v>
+        <v>-4.955504802269823</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.007636986469829</v>
+        <v>1.027654780878617</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4458895253314937</v>
+        <v>-0.4152101896016515</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.742679410901398</v>
+        <v>2.761087012339303</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.114087469207926</v>
+        <v>-5.064042983185957</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.954658422735267</v>
+        <v>0.9746762171440548</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4458895253314937</v>
+        <v>-0.4152101896016515</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.733116119533289</v>
+        <v>2.751523720971194</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.145080628536632</v>
+        <v>-5.095036142514663</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7669707240441719</v>
+        <v>0.7869885184529593</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4458895253314937</v>
+        <v>-0.4152101896016515</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.557825684573676</v>
+        <v>2.576233286011581</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.969606368744163</v>
+        <v>-4.919561882722194</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8417276599529471</v>
+        <v>0.8617454543617347</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4458895253314937</v>
+        <v>-0.4152101896016515</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.562392916565464</v>
+        <v>2.580800518003369</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.080542621385412</v>
+        <v>-5.030498135363443</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7730951876576544</v>
+        <v>0.7931129820664422</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4458895253314937</v>
+        <v>-0.4152101896016515</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.538134945326671</v>
+        <v>2.556542546764576</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.08882469553047</v>
+        <v>-5.038780209508501</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7729137432195365</v>
+        <v>0.7929315376283244</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4541715994765521</v>
+        <v>-0.4234922637467098</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.536297086059541</v>
+        <v>2.554704687497447</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.028972076326747</v>
+        <v>-4.978927590304778</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8070271773331581</v>
+        <v>0.8270449717419459</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4541715994765521</v>
+        <v>-0.4234922637467098</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.546469472491673</v>
+        <v>2.564877073929579</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.942728613300369</v>
+        <v>-4.8926841272784</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8364708331175696</v>
+        <v>0.8564886275263572</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4541715994765521</v>
+        <v>-0.4234922637467098</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.541415743065534</v>
+        <v>2.559823344503439</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.988035432699349</v>
+        <v>-4.93799094667738</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8101238808025033</v>
+        <v>0.8301416752112909</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4949817624857829</v>
+        <v>-0.4643024267559406</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.508705420704521</v>
+        <v>2.527113022142426</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.01706853740165</v>
+        <v>-4.967024051379681</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7990625119546846</v>
+        <v>0.819080306363472</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4949817624857829</v>
+        <v>-0.4643024267559406</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.509257293737623</v>
+        <v>2.527664895175528</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.984070864682044</v>
+        <v>-4.874213569928822</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7415342729338925</v>
+        <v>0.7854771908351816</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4619840897661766</v>
+        <v>-0.3714919453050813</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.458328589260752</v>
+        <v>2.512623875937409</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.028460334011472</v>
+        <v>-4.918603039258249</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7256519611267223</v>
+        <v>0.7695948790280114</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5063735590956042</v>
+        <v>-0.415881414634509</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.433568383587696</v>
+        <v>2.487863670264353</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.915789115775222</v>
+        <v>-4.805931821021999</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7657961569329454</v>
+        <v>0.8097390748342344</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.393702340859354</v>
+        <v>-0.3032101963982587</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.496246823041169</v>
+        <v>2.550542109717826</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.803412114592549</v>
+        <v>-4.693554819839326</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8162382532366819</v>
+        <v>0.8601811711379708</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.393702340859354</v>
+        <v>-0.3032101963982587</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.501738118871836</v>
+        <v>2.556033405548494</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.001646683479279</v>
+        <v>-4.891789388726057</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7484416274505286</v>
+        <v>0.7923845453518177</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5919369097460846</v>
+        <v>-0.5014447652849894</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.394294579308337</v>
+        <v>2.448589865984994</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.084647964504558</v>
+        <v>-4.974790669751336</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5535968350410703</v>
+        <v>0.5975397529423594</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6105077942732584</v>
+        <v>-0.5200156498121631</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.221507768592686</v>
+        <v>2.275803055269343</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.19326204294789</v>
+        <v>-5.083404748194667</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6303008643829435</v>
+        <v>0.6742437822842327</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6105077942732584</v>
+        <v>-0.5200156498121631</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.341657429311892</v>
+        <v>2.395952715988549</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.279860625928992</v>
+        <v>-5.17000333117577</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6101744572928252</v>
+        <v>0.6541173751941143</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6105077942732584</v>
+        <v>-0.5200156498121631</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.356170455414215</v>
+        <v>2.410465742090872</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.241476963370841</v>
+        <v>-5.131619668617619</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6229473636584544</v>
+        <v>0.6668902815597435</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5721241317151072</v>
+        <v>-0.4816319872540119</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.376620094291474</v>
+        <v>2.430915380968131</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.064360633335675</v>
+        <v>-4.954503338582453</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6905229245178228</v>
+        <v>0.7344658424191117</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5721241317151072</v>
+        <v>-0.4816319872540119</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.373349123136776</v>
+        <v>2.427644409813433</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.109452878169221</v>
+        <v>-4.999595583415998</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6731694183463177</v>
+        <v>0.7171123362476066</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.634020174884497</v>
+        <v>-0.5435280304234017</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.336894888997055</v>
+        <v>2.391190175673712</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.930077456930453</v>
+        <v>-4.820220162177231</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7387065621482389</v>
+        <v>0.7826494800495281</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4772434167137783</v>
+        <v>-0.386751272252683</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.424747919205901</v>
+        <v>2.479043205882558</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.975091670451059</v>
+        <v>-4.865234375697836</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7015083320715865</v>
+        <v>0.7454512499728754</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.507592312028383</v>
+        <v>-0.4171001675672876</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.387346037348728</v>
+        <v>2.441641324025385</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.242096180723494</v>
+        <v>-5.132238885970271</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.600398090301558</v>
+        <v>0.6443410082028471</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7019553500713316</v>
+        <v>-0.6114632056102363</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.276419776861904</v>
+        <v>2.330715063538562</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.343293962160667</v>
+        <v>-5.233436667407444</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5591228996231905</v>
+        <v>0.6030658175244796</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7703641636166507</v>
+        <v>-0.6798720191555554</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.234578410631214</v>
+        <v>2.288873697307872</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.310818375989895</v>
+        <v>-5.200961081236672</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5697130956458163</v>
+        <v>0.613656013547105</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7703641636166507</v>
+        <v>-0.6798720191555554</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.232178372185531</v>
+        <v>2.286473658862188</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.291780248282597</v>
+        <v>-5.181922953529375</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.57385306593698</v>
+        <v>0.6177959838382692</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.8285477749478453</v>
+        <v>-0.7380556304867499</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.193792924595059</v>
+        <v>2.248088211271717</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.322906879433216</v>
+        <v>-5.213049584679993</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7389842824154131</v>
+        <v>0.7829272003167023</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.8285477749478453</v>
+        <v>-0.7380556304867499</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.37137479353374</v>
+        <v>2.425670080210397</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.375227260034007</v>
+        <v>-5.265369965280785</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7188894591612298</v>
+        <v>0.7628323770625189</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7936009149389731</v>
+        <v>-0.7031087704778778</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.393176238525196</v>
+        <v>2.447471525201854</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.395484558562965</v>
+        <v>-5.285627263809743</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7167950701465728</v>
+        <v>0.760737988047862</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7936009149389731</v>
+        <v>-0.7031087704778778</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.399184768922122</v>
+        <v>2.45348005559878</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.247741588327963</v>
+        <v>-5.13788429357474</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8550449060325955</v>
+        <v>0.8989878239338847</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.62579355770409</v>
+        <v>-0.5353014132429946</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.579021831055075</v>
+        <v>2.633317117731732</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.349756270859184</v>
+        <v>-5.239898976105962</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8170326545515882</v>
+        <v>0.8609755724528774</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.62579355770409</v>
+        <v>-0.5353014132429946</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.581815452586556</v>
+        <v>2.636110739263213</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394733</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.3436035648064</v>
+        <v>-5.233746270053177</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8201560853643604</v>
+        <v>0.8640990032656495</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6196408516513057</v>
+        <v>-0.5291487071902103</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.586169424609884</v>
+        <v>2.640464711286541</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.360412862956902</v>
+        <v>-5.250555568203679</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8125128428442698</v>
+        <v>0.856455760745559</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6364501498018074</v>
+        <v>-0.545958005340712</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.575164322459694</v>
+        <v>2.629459609136351</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679843</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.298114864180779</v>
+        <v>-5.188257569427557</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9037675961515395</v>
+        <v>0.9477105140528286</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6364501498018074</v>
+        <v>-0.545958005340712</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.641499876256515</v>
+        <v>2.695795162933172</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.096324666515621</v>
+        <v>-4.986467371762399</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6930645476070008</v>
+        <v>0.7370074655082899</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.438431957632653</v>
+        <v>-0.3479398131715576</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.468891663947405</v>
+        <v>2.523186950624062</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.036433984873028</v>
+        <v>-4.926576690119806</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7873110525862135</v>
+        <v>0.8312539704875024</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3785412759900595</v>
+        <v>-0.2880491315289642</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.575116305255136</v>
+        <v>2.629411591931794</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031955</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.134174529498003</v>
+        <v>-5.02431723474478</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7628425708522673</v>
+        <v>0.8067854887535564</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3944305541230397</v>
+        <v>-0.3039384096619444</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.580210474491392</v>
+        <v>2.634505761168049</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.310512289620932</v>
+        <v>-5.200654994867709</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6908434476277669</v>
+        <v>0.7347863655290561</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5707683142459691</v>
+        <v>-0.4802761697848738</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.472943799242306</v>
+        <v>2.527239085918963</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.238965966844055</v>
+        <v>-5.129108672090832</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7179535947784466</v>
+        <v>0.7618965126797357</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5707683142459691</v>
+        <v>-0.4802761697848738</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.471435417282235</v>
+        <v>2.525730703958892</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.194592835205486</v>
+        <v>-5.084735540452264</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7355657148693102</v>
+        <v>0.7795086327705993</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5263951826074005</v>
+        <v>-0.4359030381463052</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.497922163700812</v>
+        <v>2.552217450377469</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.186638864910714</v>
+        <v>-5.076781570157491</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7387473029872189</v>
+        <v>0.782690220888508</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5263951826074005</v>
+        <v>-0.4359030381463052</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.497922163700812</v>
+        <v>2.552217450377469</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.138983134349658</v>
+        <v>-5.029125839596436</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7641913522394459</v>
+        <v>0.808134270140735</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4787394520463448</v>
+        <v>-0.3882473075852495</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.53289735906525</v>
+        <v>2.587192645741907</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.011298824555362</v>
+        <v>-4.901441529802139</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8201574495318895</v>
+        <v>0.8641003674331784</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3510551422520484</v>
+        <v>-0.260562997790953</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.614400318316553</v>
+        <v>2.66869560499321</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.07196541495775</v>
+        <v>-4.851967351501232</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7826454858468059</v>
+        <v>0.8706447112294136</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.432753458970582</v>
+        <v>-0.2214058373343013</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.552136000761305</v>
+        <v>2.678944573743073</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.006971555024105</v>
+        <v>-4.786973491567586</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8127407324308928</v>
+        <v>0.9007399578135002</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4059228443664267</v>
+        <v>-0.1945752227301459</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.572332072134426</v>
+        <v>2.699140645116195</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.107730190781103</v>
+        <v>-4.887732127324584</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7765982177591715</v>
+        <v>0.8645974431417791</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4947484130934321</v>
+        <v>-0.2834007914571514</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.523197670529301</v>
+        <v>2.650006243511069</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.063527353695203</v>
+        <v>-4.843529290238684</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8001589551213688</v>
+        <v>0.8881581805039764</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4505455760075316</v>
+        <v>-0.2391979543712509</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.555598975308679</v>
+        <v>2.682407548290447</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.100506381358645</v>
+        <v>-4.880508317902127</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7837773445252396</v>
+        <v>0.8717765699078468</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4135716742162011</v>
+        <v>-0.2022240525799204</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.576193316852724</v>
+        <v>2.703001889834493</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.120564460223486</v>
+        <v>-4.900566396766967</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8270018781623429</v>
+        <v>0.9150011035449503</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4135716742162011</v>
+        <v>-0.2022240525799204</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.627441082035764</v>
+        <v>2.754249655017532</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.080633787045596</v>
+        <v>-4.860635723589077</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8414148520277522</v>
+        <v>0.9294140774103596</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.3736410010383108</v>
+        <v>-0.16229337940203</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.649840190536751</v>
+        <v>2.77664876351852</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.040163439482891</v>
+        <v>-4.820165376026372</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.852551219291104</v>
+        <v>0.9405504446737116</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.3331706534756058</v>
+        <v>-0.1218230318393251</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.669070627312645</v>
+        <v>2.795879200294413</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.974939258355685</v>
+        <v>-4.754941194899167</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8958282958346913</v>
+        <v>0.9838275212172987</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.2679464723484002</v>
+        <v>-0.05659885071211945</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.725392540081673</v>
+        <v>2.852201113063441</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.025433548712742</v>
+        <v>-4.805435485256223</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8715915519911492</v>
+        <v>0.9595907773737564</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.3129672094744744</v>
+        <v>-0.1016195878381937</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.694341070105309</v>
+        <v>2.821149643087077</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-5.04554520474745</v>
+        <v>-4.825547141290931</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8648036819085059</v>
+        <v>0.9528029072911135</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.3019398644770552</v>
+        <v>-0.0905922428407745</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.702214269435</v>
+        <v>2.829022842416769</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-5.143225784020096</v>
+        <v>-4.923227720563577</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9862892212206584</v>
+        <v>1.074288446603266</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.412643059817244</v>
+        <v>-0.2012954381809633</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.796350123252098</v>
+        <v>2.923158696233866</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-5.119434215413953</v>
+        <v>-4.899436151957435</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.115918757880932</v>
+        <v>1.20391798326354</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.3888514912111017</v>
+        <v>-0.177503869574821</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.930737973633601</v>
+        <v>3.057546546615369</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-5.156188633975676</v>
+        <v>-4.936190570519157</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.092924966470103</v>
+        <v>1.18092419185271</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.3888514912111017</v>
+        <v>-0.177503869574821</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.92244594964746</v>
+        <v>3.049254522629228</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654191</v>
+        <v>3.803426852654188</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-5.151854330918628</v>
+        <v>-4.851694520338306</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.092851883276701</v>
+        <v>1.21291580750883</v>
       </c>
       <c r="F1994" t="n">
-        <v>-0.2372013878918978</v>
+        <v>0.1953250127597008</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.011629207222761</v>
+        <v>3.27114504761372</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.58026641875751</v>
+        <v>3.502426013627459</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.103969179931511</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-5.151854330918628</v>
+        <v>-4.839477010767837</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.092851883276701</v>
+        <v>1.235357217063809</v>
       </c>
       <c r="F1995" t="n">
-        <v>-0.2372013878918978</v>
+        <v>0.2075425223301701</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.097032976917879</v>
+        <v>3.296029959082794</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240614.xlsx
+++ b/tame_output/ON/bt/strategyON_20240614.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.6%</t>
+          <t>449.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-645.5%</t>
+          <t>-664.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-43.8%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-252.7%</t>
+          <t>-260.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-163.0%</t>
+          <t>-161.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-203.2%</t>
+          <t>-235.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-116.4%</t>
+          <t>-135.7%</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.142928444636439</v>
+        <v>-8.141695777246049</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1034862408847546</v>
+        <v>-0.1029931739285987</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.643852229924918</v>
+        <v>-1.623254412242403</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.167730223328618</v>
+        <v>2.180088913938127</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.893928645952858</v>
+        <v>-7.892695978562468</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.009020019812336688</v>
+        <v>0.009513086768492496</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.643852229924918</v>
+        <v>-1.623254412242403</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.180636564552277</v>
+        <v>2.192995255161786</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.999518635725963</v>
+        <v>-7.998285968335573</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.161191905696124</v>
+        <v>-0.1606988387399682</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.749442219698022</v>
+        <v>-1.728844402015507</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.989306641089196</v>
+        <v>2.001665331698705</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.01825353784456</v>
+        <v>-8.01702087045417</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1201415246664763</v>
+        <v>-0.1196484577103205</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.755038229358153</v>
+        <v>-1.734440411675638</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.034493377170203</v>
+        <v>2.046852067779712</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.87031349643696</v>
+        <v>-7.86908082904657</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1808444307916042</v>
+        <v>-0.1803513638354484</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.734717313449596</v>
+        <v>-1.714119495767081</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.92680700402717</v>
+        <v>1.939165694636679</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.817343974182972</v>
+        <v>-7.816111306792582</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.168370608143487</v>
+        <v>-0.1678775411873312</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.681747791195607</v>
+        <v>-1.661149973513092</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.949874731126085</v>
+        <v>1.962233421735594</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.773795567412281</v>
+        <v>-7.772562900021891</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.157911857530304</v>
+        <v>-0.1574187905741482</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.681747791195607</v>
+        <v>-1.661149973513092</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.942914119030992</v>
+        <v>1.955272809640501</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.531647173958423</v>
+        <v>-7.530414506568033</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04659014576761766</v>
+        <v>-0.04609707881146186</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.681747791195607</v>
+        <v>-1.661149973513092</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.957376473412135</v>
+        <v>1.969735164021644</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.423388036835902</v>
+        <v>-7.422155369445512</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.008754370459413963</v>
+        <v>-0.008261303503258155</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.681747791195607</v>
+        <v>-1.661149973513092</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.95190859387133</v>
+        <v>1.964267284480839</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.300096902018771</v>
+        <v>-7.298864234628381</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.03806017747801516</v>
+        <v>0.03855324443417141</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.558456656378477</v>
+        <v>-1.537858838695962</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.023381368772185</v>
+        <v>2.035740059381694</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.278947703115327</v>
+        <v>-7.277715035724937</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.05422083527671795</v>
+        <v>0.05471390223287376</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.537307457475033</v>
+        <v>-1.516709639792518</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.043771866351577</v>
+        <v>2.056130556961086</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.035182261131883</v>
+        <v>-7.033949593741493</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.147507720417146</v>
+        <v>0.1480007873733022</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.537307457475033</v>
+        <v>-1.516709639792518</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.039552574698627</v>
+        <v>2.051911265308136</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.933419440854588</v>
+        <v>-6.932186773464198</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1903371624480803</v>
+        <v>0.1908302294042361</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.524088389082604</v>
+        <v>-1.503490571400089</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.049608329654101</v>
+        <v>2.06196702026361</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.683569046905514</v>
+        <v>-6.682336379515124</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2830193950114119</v>
+        <v>0.2835124619675682</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.524088389082604</v>
+        <v>-1.503490571400089</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.042350404637802</v>
+        <v>2.054709095247311</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.507676954438081</v>
+        <v>-6.506444287047691</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.356975355519034</v>
+        <v>0.3574684224751898</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.524088389082604</v>
+        <v>-1.503490571400089</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.045949528158451</v>
+        <v>2.05830821876796</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.336230491415617</v>
+        <v>-6.334997824025227</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.438881446782573</v>
+        <v>0.4393745137387293</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.352641926060141</v>
+        <v>-1.332044108377626</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.162144912026483</v>
+        <v>2.174503602635992</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.111197491746794</v>
+        <v>-6.109964824356404</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5279151242663991</v>
+        <v>0.5284081912225553</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.127608926391318</v>
+        <v>-1.107011108708803</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.296185189444074</v>
+        <v>2.308543880053583</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.04756174951286</v>
+        <v>-6.04632908212247</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5580642222142904</v>
+        <v>0.5585572891704462</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.063973184157384</v>
+        <v>-1.043375366474869</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.339061435838752</v>
+        <v>2.351420126448261</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.003799568207018</v>
+        <v>-6.002566900816628</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5567633535204228</v>
+        <v>0.5572564204765786</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.063973184157384</v>
+        <v>-1.043375366474869</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.320255694622547</v>
+        <v>2.332614385232056</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.763369071402158</v>
+        <v>-5.762136404011768</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6546786288672442</v>
+        <v>0.6551716958234</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8235426873525236</v>
+        <v>-0.8029448696700086</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.466257069330341</v>
+        <v>2.47861575993985</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.691126503230963</v>
+        <v>-5.689893835840573</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6875049699705422</v>
+        <v>0.687998036926698</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8235426873525236</v>
+        <v>-0.8029448696700086</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.470186383165161</v>
+        <v>2.48254507377467</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.638128180949575</v>
+        <v>-5.636895513559185</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7093828828004374</v>
+        <v>0.7098759497565932</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7682064283505847</v>
+        <v>-0.7476086106680697</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.504066722483664</v>
+        <v>2.516425413093173</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.529323295469848</v>
+        <v>-5.528090628079458</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7499029082123219</v>
+        <v>0.7503959751684777</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7682064283505847</v>
+        <v>-0.7476086106680697</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.501064793703658</v>
+        <v>2.513423484313167</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.309302497432838</v>
+        <v>-5.308069830042448</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8394902644377402</v>
+        <v>0.839983331393896</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6269865832826045</v>
+        <v>-0.6063887656000895</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.58737573775506</v>
+        <v>2.599734428364569</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.17643480836956</v>
+        <v>-5.17520214097917</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9085315228648745</v>
+        <v>0.9090245898210303</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6269865832826045</v>
+        <v>-0.6063887656000895</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.603269920556883</v>
+        <v>2.615628611166392</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.056261725005061</v>
+        <v>-5.055029057614671</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9577466006509758</v>
+        <v>0.9582396676071316</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5068134999181055</v>
+        <v>-0.4862156822355905</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.676519615015884</v>
+        <v>2.688878305625393</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.911589579905324</v>
+        <v>-4.910356912514934</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.025703561252311</v>
+        <v>1.026196628208467</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3621413548183681</v>
+        <v>-0.3415435371358531</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.773411004637167</v>
+        <v>2.785769695246676</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.971464407263016</v>
+        <v>-4.970231739872626</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9877911217106594</v>
+        <v>0.9882841886668154</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4220161821760602</v>
+        <v>-0.4014183644935452</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.723523599623977</v>
+        <v>2.735882290233486</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.884664909484007</v>
+        <v>-4.883432242093617</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.044911414144829</v>
+        <v>1.045404481100985</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4220161821760602</v>
+        <v>-0.4014183644935452</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.745924092946543</v>
+        <v>2.758282783556052</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.887134615945813</v>
+        <v>-4.885901948555423</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.043995932933519</v>
+        <v>1.044488999889675</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4244858886378664</v>
+        <v>-0.4038880709553514</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.744514670442872</v>
+        <v>2.756873361052381</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.955504802269823</v>
+        <v>-4.954272134879433</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.027654780878617</v>
+        <v>1.028147847834773</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4152101896016515</v>
+        <v>-0.3946123719191365</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.761087012339303</v>
+        <v>2.773445702948812</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.064042983185957</v>
+        <v>-5.062810315795567</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9746762171440548</v>
+        <v>0.9751692841002106</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4152101896016515</v>
+        <v>-0.3946123719191365</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.751523720971194</v>
+        <v>2.763882411580703</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.095036142514663</v>
+        <v>-5.093803475124273</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7869885184529593</v>
+        <v>0.7874815854091155</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4152101896016515</v>
+        <v>-0.3946123719191365</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.576233286011581</v>
+        <v>2.58859197662109</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.919561882722194</v>
+        <v>-4.918329215331804</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8617454543617347</v>
+        <v>0.8622385213178907</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4152101896016515</v>
+        <v>-0.3946123719191365</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.580800518003369</v>
+        <v>2.593159208612878</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.030498135363443</v>
+        <v>-5.029265467973053</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7931129820664422</v>
+        <v>0.793606049022598</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4152101896016515</v>
+        <v>-0.3946123719191365</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.556542546764576</v>
+        <v>2.568901237374085</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.038780209508501</v>
+        <v>-5.037547542118111</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7929315376283244</v>
+        <v>0.7934246045844802</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4234922637467098</v>
+        <v>-0.4028944460641948</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.554704687497447</v>
+        <v>2.567063378106956</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.978927590304778</v>
+        <v>-4.977694922914388</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8270449717419459</v>
+        <v>0.8275380386981019</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4234922637467098</v>
+        <v>-0.4028944460641948</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.564877073929579</v>
+        <v>2.577235764539088</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.8926841272784</v>
+        <v>-4.89145145988801</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8564886275263572</v>
+        <v>0.8569816944825133</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4234922637467098</v>
+        <v>-0.4028944460641948</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.559823344503439</v>
+        <v>2.572182035112948</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.93799094667738</v>
+        <v>-4.93675827928699</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8301416752112909</v>
+        <v>0.8306347421674469</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4643024267559406</v>
+        <v>-0.4437046090734256</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.527113022142426</v>
+        <v>2.539471712751935</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.967024051379681</v>
+        <v>-4.965791383989291</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.819080306363472</v>
+        <v>0.819573373319628</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4643024267559406</v>
+        <v>-0.4437046090734256</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.527664895175528</v>
+        <v>2.540023585785037</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.874213569928822</v>
+        <v>-4.872980902538432</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7854771908351816</v>
+        <v>0.7859702577913374</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3714919453050813</v>
+        <v>-0.3508941276225663</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.512623875937409</v>
+        <v>2.524982566546918</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.918603039258249</v>
+        <v>-4.917370371867859</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7695948790280114</v>
+        <v>0.7700879459841674</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.415881414634509</v>
+        <v>-0.3952835969519939</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.487863670264353</v>
+        <v>2.500222360873862</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.805931821021999</v>
+        <v>-4.804699153631609</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8097390748342344</v>
+        <v>0.8102321417903904</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3032101963982587</v>
+        <v>-0.2826123787157437</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.550542109717826</v>
+        <v>2.562900800327335</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.693554819839326</v>
+        <v>-4.692322152448936</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8601811711379708</v>
+        <v>0.8606742380941268</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3032101963982587</v>
+        <v>-0.2826123787157437</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.556033405548494</v>
+        <v>2.568392096158003</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.891789388726057</v>
+        <v>-4.890556721335667</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7923845453518177</v>
+        <v>0.7928776123079735</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5014447652849894</v>
+        <v>-0.4808469476024743</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.448589865984994</v>
+        <v>2.460948556594503</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.974790669751336</v>
+        <v>-4.973558002360946</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5975397529423594</v>
+        <v>0.5980328198985152</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5200156498121631</v>
+        <v>-0.4994178321296481</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.275803055269343</v>
+        <v>2.288161745878852</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.083404748194667</v>
+        <v>-5.082172080804277</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6742437822842327</v>
+        <v>0.6747368492403885</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5200156498121631</v>
+        <v>-0.4994178321296481</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.395952715988549</v>
+        <v>2.408311406598058</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.17000333117577</v>
+        <v>-5.16877066378538</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6541173751941143</v>
+        <v>0.6546104421502701</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5200156498121631</v>
+        <v>-0.4994178321296481</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.410465742090872</v>
+        <v>2.422824432700381</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.131619668617619</v>
+        <v>-5.130387001227229</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6668902815597435</v>
+        <v>0.6673833485158993</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4816319872540119</v>
+        <v>-0.4610341695714969</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.430915380968131</v>
+        <v>2.44327407157764</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.954503338582453</v>
+        <v>-4.953270671192063</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7344658424191117</v>
+        <v>0.7349589093752678</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4816319872540119</v>
+        <v>-0.4610341695714969</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.427644409813433</v>
+        <v>2.440003100422942</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.999595583415998</v>
+        <v>-4.998362916025608</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7171123362476066</v>
+        <v>0.7176054032037626</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5435280304234017</v>
+        <v>-0.5229302127408867</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.391190175673712</v>
+        <v>2.403548866283221</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.820220162177231</v>
+        <v>-4.818987494786841</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7826494800495281</v>
+        <v>0.7831425470056841</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.386751272252683</v>
+        <v>-0.366153454570168</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.479043205882558</v>
+        <v>2.491401896492067</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.865234375697836</v>
+        <v>-4.864001708307446</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7454512499728754</v>
+        <v>0.7459443169290314</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4171001675672876</v>
+        <v>-0.3965023498847726</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.441641324025385</v>
+        <v>2.454000014634894</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.132238885970271</v>
+        <v>-5.131006218579881</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6443410082028471</v>
+        <v>0.6448340751590034</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6114632056102363</v>
+        <v>-0.5908653879277213</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.330715063538562</v>
+        <v>2.343073754148071</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.233436667407444</v>
+        <v>-5.232204000017054</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6030658175244796</v>
+        <v>0.6035588844806354</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6798720191555554</v>
+        <v>-0.6592742014730404</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.288873697307872</v>
+        <v>2.301232387917381</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.200961081236672</v>
+        <v>-5.199728413846282</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.613656013547105</v>
+        <v>0.6141490805032612</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6798720191555554</v>
+        <v>-0.6592742014730404</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.286473658862188</v>
+        <v>2.298832349471697</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.181922953529375</v>
+        <v>-5.180690286138985</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6177959838382692</v>
+        <v>0.618289050794425</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.7380556304867499</v>
+        <v>-0.7174578128042349</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.248088211271717</v>
+        <v>2.260446901881226</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.213049584679993</v>
+        <v>-5.211816917289603</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7829272003167023</v>
+        <v>0.7834202672728581</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.7380556304867499</v>
+        <v>-0.7174578128042349</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.425670080210397</v>
+        <v>2.438028770819906</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.265369965280785</v>
+        <v>-5.264137297890395</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7628323770625189</v>
+        <v>0.7633254440186752</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7031087704778778</v>
+        <v>-0.6825109527953628</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.447471525201854</v>
+        <v>2.459830215811363</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.285627263809743</v>
+        <v>-5.284394596419353</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.760737988047862</v>
+        <v>0.7612310550040178</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7031087704778778</v>
+        <v>-0.6825109527953628</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.45348005559878</v>
+        <v>2.465838746208289</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.13788429357474</v>
+        <v>-5.13665162618435</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8989878239338847</v>
+        <v>0.8994808908900409</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5353014132429946</v>
+        <v>-0.5147035955604796</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.633317117731732</v>
+        <v>2.645675808341241</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.239898976105962</v>
+        <v>-5.238666308715572</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8609755724528774</v>
+        <v>0.8614686394090332</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5353014132429946</v>
+        <v>-0.5147035955604796</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.636110739263213</v>
+        <v>2.648469429872722</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.233746270053177</v>
+        <v>-5.232513602662787</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8640990032656495</v>
+        <v>0.8645920702218053</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5291487071902103</v>
+        <v>-0.5085508895076953</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.640464711286541</v>
+        <v>2.65282340189605</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.250555568203679</v>
+        <v>-5.249322900813289</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.856455760745559</v>
+        <v>0.8569488277017148</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.545958005340712</v>
+        <v>-0.525360187658197</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.629459609136351</v>
+        <v>2.64181829974586</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.188257569427557</v>
+        <v>-5.187024902037167</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9477105140528286</v>
+        <v>0.9482035810089844</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.545958005340712</v>
+        <v>-0.525360187658197</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.695795162933172</v>
+        <v>2.708153853542681</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.986467371762399</v>
+        <v>-4.985234704372009</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7370074655082899</v>
+        <v>0.7375005324644457</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3479398131715576</v>
+        <v>-0.3273419954890426</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.523186950624062</v>
+        <v>2.535545641233571</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.926576690119806</v>
+        <v>-4.925344022729416</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8312539704875024</v>
+        <v>0.8317470374436584</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2880491315289642</v>
+        <v>-0.2674513138464492</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.629411591931794</v>
+        <v>2.641770282541303</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.02431723474478</v>
+        <v>-5.02308456735439</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8067854887535564</v>
+        <v>0.8072785557097122</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3039384096619444</v>
+        <v>-0.2833405919794293</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.634505761168049</v>
+        <v>2.646864451777558</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.200654994867709</v>
+        <v>-5.199422327477319</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7347863655290561</v>
+        <v>0.7352794324852123</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4802761697848738</v>
+        <v>-0.4596783521023587</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.527239085918963</v>
+        <v>2.539597776528472</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.129108672090832</v>
+        <v>-5.127876004700442</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7618965126797357</v>
+        <v>0.7623895796358915</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4802761697848738</v>
+        <v>-0.4596783521023587</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.525730703958892</v>
+        <v>2.538089394568401</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.084735540452264</v>
+        <v>-5.083502873061874</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7795086327705993</v>
+        <v>0.7800016997267551</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4359030381463052</v>
+        <v>-0.4153052204637901</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.552217450377469</v>
+        <v>2.564576140986978</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.076781570157491</v>
+        <v>-5.075548902767101</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.782690220888508</v>
+        <v>0.7831832878446638</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4359030381463052</v>
+        <v>-0.4153052204637901</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.552217450377469</v>
+        <v>2.564576140986978</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.029125839596436</v>
+        <v>-5.027893172206046</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.808134270140735</v>
+        <v>0.8086273370968908</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3882473075852495</v>
+        <v>-0.3676494899027345</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.587192645741907</v>
+        <v>2.599551336351416</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.901441529802139</v>
+        <v>-4.900208862411749</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8641003674331784</v>
+        <v>0.8645934343893344</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.260562997790953</v>
+        <v>-0.239965180108438</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.66869560499321</v>
+        <v>2.681054295602719</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.851967351501232</v>
+        <v>-4.960875452814138</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8706447112294136</v>
+        <v>0.8270814707042511</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2214058373343013</v>
+        <v>-0.3216634968269717</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.678944573743073</v>
+        <v>2.618789978047471</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.786973491567586</v>
+        <v>-4.895881592880492</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9007399578135002</v>
+        <v>0.857176717288338</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1945752227301459</v>
+        <v>-0.2948328822228163</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.699140645116195</v>
+        <v>2.638986049420593</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.887732127324584</v>
+        <v>-4.99664022863749</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8645974431417791</v>
+        <v>0.8210342026166166</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2834007914571514</v>
+        <v>-0.3836584509498218</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.650006243511069</v>
+        <v>2.589851647815467</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.843529290238684</v>
+        <v>-4.95243739155159</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8881581805039764</v>
+        <v>0.844594939978814</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2391979543712509</v>
+        <v>-0.3394556138639213</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.682407548290447</v>
+        <v>2.622252952594845</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.880508317902127</v>
+        <v>-4.989416419215033</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8717765699078468</v>
+        <v>0.8282133293826845</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.2022240525799204</v>
+        <v>-0.3024817120725908</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.703001889834493</v>
+        <v>2.642847294138891</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.900566396766967</v>
+        <v>-5.009474498079873</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9150011035449503</v>
+        <v>0.8714378630197879</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.2022240525799204</v>
+        <v>-0.3024817120725908</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.754249655017532</v>
+        <v>2.69409505932193</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.860635723589077</v>
+        <v>-4.969543824901983</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9294140774103596</v>
+        <v>0.8858508368851972</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.16229337940203</v>
+        <v>-0.2625510388947004</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.77664876351852</v>
+        <v>2.716494167822918</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.820165376026372</v>
+        <v>-4.929073477339278</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9405504446737116</v>
+        <v>0.8969872041485492</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.1218230318393251</v>
+        <v>-0.2220806913319955</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.795879200294413</v>
+        <v>2.73572460459881</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.754941194899167</v>
+        <v>-4.863849296212073</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9838275212172987</v>
+        <v>0.9402642806921362</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.05659885071211945</v>
+        <v>-0.1568565102047899</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.852201113063441</v>
+        <v>2.792046517367839</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.805435485256223</v>
+        <v>-4.914343586569129</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9595907773737564</v>
+        <v>0.9160275368485942</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.1016195878381937</v>
+        <v>-0.2018772473308641</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.821149643087077</v>
+        <v>2.760995047391475</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.825547141290931</v>
+        <v>-4.934455242603837</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9528029072911135</v>
+        <v>0.909239666765951</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.0905922428407745</v>
+        <v>-0.1908499023334449</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.829022842416769</v>
+        <v>2.768868246721166</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.923227720563577</v>
+        <v>-5.032135821876484</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.074288446603266</v>
+        <v>1.030725206078103</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.2012954381809633</v>
+        <v>-0.3015530976736337</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.923158696233866</v>
+        <v>2.863004100538264</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.899436151957435</v>
+        <v>-5.008344253270341</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.20391798326354</v>
+        <v>1.160354742738378</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.177503869574821</v>
+        <v>-0.2777615290674914</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.057546546615369</v>
+        <v>2.997391950919767</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.936190570519157</v>
+        <v>-5.045098671832063</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.18092419185271</v>
+        <v>1.137360951327548</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.177503869574821</v>
+        <v>-0.2777615290674914</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.049254522629228</v>
+        <v>2.989099926933626</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654188</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.851694520338306</v>
+        <v>-5.040764368775015</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.21291580750883</v>
+        <v>1.137287868134147</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1953250127597008</v>
+        <v>-0.1261114257482875</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.27114504761372</v>
+        <v>3.078283184508928</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.502426013627459</v>
+        <v>3.50242601362746</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.839477010767837</v>
+        <v>-5.028439836978905</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.235357217063809</v>
+        <v>1.159772086579382</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2075425223301701</v>
+        <v>-0.1137868939521777</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.296029959082794</v>
+        <v>3.103232309313384</v>
       </c>
     </row>
   </sheetData>
